--- a/settlement-overseas-template.xlsx
+++ b/settlement-overseas-template.xlsx
@@ -17,8 +17,8 @@
     <sheet name="세틀" sheetId="10" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">검수원본!$A$1:$I$115</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">세틀!$A$1:$I$84</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'검수원본'!$A$1:$J$115</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'세틀'!$A$1:$J$84</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -2413,14 +2413,14 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:K156"/>
+  <dimension ref="A2:J156"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="5" width="16.08203125" style="1" customWidth="1"/>
     <col min="6" max="6" width="15.5" style="1" customWidth="1"/>
     <col min="7" max="8" width="16.08203125" style="1" customWidth="1"/>
     <col min="9" max="9" width="19.58203125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="7.58203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.58203125" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
@@ -2454,8 +2454,10 @@
       <c r="A5" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>21</v>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">donald</t>
+        </is>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
@@ -2464,46 +2466,40 @@
         <v>1</v>
       </c>
       <c r="G5" s="11">
-        <v>46157</v>
+        <v>46245</v>
       </c>
       <c r="I5" s="41"/>
     </row>
     <row r="6" spans="1:10" s="9" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="8"/>
-      <c r="B6" s="8" t="s">
-        <v>15</v>
-      </c>
+      <c r="B6" s="8"/>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
       <c r="F6" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="8" t="s">
-        <v>28</v>
-      </c>
+      <c r="G6" s="8"/>
       <c r="I6" s="41"/>
     </row>
     <row r="7" spans="1:10" s="9" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="8"/>
-      <c r="B7" s="8" t="s">
-        <v>16</v>
-      </c>
+      <c r="B7" s="8"/>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
       <c r="F7" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="G7" s="8" t="s">
-        <v>29</v>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">s01234</t>
+        </is>
       </c>
       <c r="I7" s="41"/>
     </row>
     <row r="8" spans="1:10" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B8" s="1" t="s">
-        <v>17</v>
-      </c>
+      <c r="B8" s="1"/>
       <c r="F8" s="3"/>
     </row>
     <row r="9" spans="1:10" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.45">
@@ -2553,54 +2549,50 @@
       <c r="I12" s="21" t="s">
         <v>22</v>
       </c>
+      <c r="J12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사진</t>
+        </is>
+      </c>
     </row>
     <row r="13" spans="1:10" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="21" t="s">
-        <v>30</v>
+      <c r="A13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">718 solids</t>
+        </is>
       </c>
       <c r="B13" s="18">
-        <v>10934</v>
-      </c>
-      <c r="C13" s="19">
-        <v>12</v>
-      </c>
+        <v>500</v>
+      </c>
+      <c r="C13" s="19"/>
       <c r="D13" s="20">
-        <f t="shared" ref="D13:D107" si="0">B13*C13</f>
-        <v>131208</v>
-      </c>
-      <c r="E13" s="21" t="s">
-        <v>30</v>
+        <v>0</v>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NI · IN 718 · VS</t>
+        </is>
       </c>
       <c r="F13" s="22">
-        <v>10472</v>
+        <v>500</v>
       </c>
       <c r="G13" s="49"/>
       <c r="H13" s="23">
-        <f t="shared" ref="H13:H107" si="1">F13*G13</f>
         <v>0</v>
       </c>
       <c r="I13" s="38"/>
-      <c r="J13" s="34"/>
+      <c r="J13" s="38"/>
     </row>
     <row r="14" spans="1:10" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="21"/>
       <c r="B14" s="18"/>
       <c r="C14" s="19"/>
       <c r="D14" s="20"/>
-      <c r="E14" s="21" t="s">
-        <v>44</v>
-      </c>
-      <c r="F14" s="22">
-        <v>107</v>
-      </c>
+      <c r="E14" s="21"/>
+      <c r="F14" s="22"/>
       <c r="G14" s="49"/>
-      <c r="H14" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I14" s="38" t="s">
-        <v>45</v>
-      </c>
+      <c r="H14" s="23"/>
+      <c r="I14" s="38"/>
       <c r="J14" s="34"/>
     </row>
     <row r="15" spans="1:10" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
@@ -2608,17 +2600,10 @@
       <c r="B15" s="18"/>
       <c r="C15" s="19"/>
       <c r="D15" s="20"/>
-      <c r="E15" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="F15" s="22">
-        <v>34</v>
-      </c>
+      <c r="E15" s="21"/>
+      <c r="F15" s="22"/>
       <c r="G15" s="49"/>
-      <c r="H15" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="H15" s="23"/>
       <c r="I15" s="38"/>
       <c r="J15" s="34"/>
     </row>
@@ -2627,17 +2612,10 @@
       <c r="B16" s="18"/>
       <c r="C16" s="19"/>
       <c r="D16" s="20"/>
-      <c r="E16" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="F16" s="22">
-        <v>12</v>
-      </c>
+      <c r="E16" s="21"/>
+      <c r="F16" s="22"/>
       <c r="G16" s="49"/>
-      <c r="H16" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="H16" s="23"/>
       <c r="I16" s="38"/>
       <c r="J16" s="34"/>
     </row>
@@ -2646,17 +2624,10 @@
       <c r="B17" s="18"/>
       <c r="C17" s="19"/>
       <c r="D17" s="20"/>
-      <c r="E17" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="F17" s="22">
-        <v>29</v>
-      </c>
+      <c r="E17" s="21"/>
+      <c r="F17" s="22"/>
       <c r="G17" s="49"/>
-      <c r="H17" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="H17" s="23"/>
       <c r="I17" s="38"/>
       <c r="J17" s="34"/>
     </row>
@@ -2665,48 +2636,22 @@
       <c r="B18" s="18"/>
       <c r="C18" s="19"/>
       <c r="D18" s="20"/>
-      <c r="E18" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="F18" s="22">
-        <v>2</v>
-      </c>
+      <c r="E18" s="21"/>
+      <c r="F18" s="22"/>
       <c r="G18" s="49"/>
-      <c r="H18" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="H18" s="23"/>
       <c r="I18" s="38"/>
-      <c r="J18" s="34">
-        <f>SUM(F13:F18)-B13</f>
-        <v>-278</v>
-      </c>
+      <c r="J18" s="34"/>
     </row>
     <row r="19" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="B19" s="18">
-        <v>1551</v>
-      </c>
-      <c r="C19" s="19">
-        <v>12.6</v>
-      </c>
-      <c r="D19" s="20">
-        <f t="shared" si="0"/>
-        <v>19542.599999999999</v>
-      </c>
-      <c r="E19" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="F19" s="22">
-        <v>367</v>
-      </c>
+      <c r="A19" s="21"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="21"/>
+      <c r="F19" s="22"/>
       <c r="G19" s="49"/>
-      <c r="H19" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="H19" s="23"/>
       <c r="I19" s="44"/>
       <c r="J19" s="34"/>
       <c r="K19" s="37"/>
@@ -2716,20 +2661,11 @@
       <c r="B20" s="18"/>
       <c r="C20" s="19"/>
       <c r="D20" s="20"/>
-      <c r="E20" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="F20" s="22">
-        <v>530</v>
-      </c>
+      <c r="E20" s="21"/>
+      <c r="F20" s="22"/>
       <c r="G20" s="49"/>
-      <c r="H20" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I20" s="50" t="s">
-        <v>53</v>
-      </c>
+      <c r="H20" s="23"/>
+      <c r="I20" s="50"/>
       <c r="J20" s="34"/>
       <c r="K20" s="37"/>
     </row>
@@ -2738,20 +2674,11 @@
       <c r="B21" s="18"/>
       <c r="C21" s="19"/>
       <c r="D21" s="20"/>
-      <c r="E21" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="F21" s="22">
-        <v>334</v>
-      </c>
+      <c r="E21" s="21"/>
+      <c r="F21" s="22"/>
       <c r="G21" s="49"/>
-      <c r="H21" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I21" s="50" t="s">
-        <v>55</v>
-      </c>
+      <c r="H21" s="23"/>
+      <c r="I21" s="50"/>
       <c r="J21" s="34"/>
       <c r="K21" s="37"/>
     </row>
@@ -2760,20 +2687,11 @@
       <c r="B22" s="18"/>
       <c r="C22" s="19"/>
       <c r="D22" s="20"/>
-      <c r="E22" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="F22" s="22">
-        <v>103</v>
-      </c>
+      <c r="E22" s="21"/>
+      <c r="F22" s="22"/>
       <c r="G22" s="49"/>
-      <c r="H22" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I22" s="50" t="s">
-        <v>56</v>
-      </c>
+      <c r="H22" s="23"/>
+      <c r="I22" s="50"/>
       <c r="J22" s="34"/>
       <c r="K22" s="37"/>
     </row>
@@ -2782,20 +2700,11 @@
       <c r="B23" s="18"/>
       <c r="C23" s="19"/>
       <c r="D23" s="20"/>
-      <c r="E23" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="F23" s="22">
-        <v>52</v>
-      </c>
+      <c r="E23" s="21"/>
+      <c r="F23" s="22"/>
       <c r="G23" s="49"/>
-      <c r="H23" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I23" s="50" t="s">
-        <v>53</v>
-      </c>
+      <c r="H23" s="23"/>
+      <c r="I23" s="50"/>
       <c r="J23" s="34"/>
       <c r="K23" s="37"/>
     </row>
@@ -2804,17 +2713,10 @@
       <c r="B24" s="18"/>
       <c r="C24" s="19"/>
       <c r="D24" s="20"/>
-      <c r="E24" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="F24" s="22">
-        <v>1</v>
-      </c>
+      <c r="E24" s="21"/>
+      <c r="F24" s="22"/>
       <c r="G24" s="49"/>
-      <c r="H24" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="H24" s="23"/>
       <c r="I24" s="50"/>
       <c r="J24" s="34"/>
       <c r="K24" s="37"/>
@@ -2824,20 +2726,11 @@
       <c r="B25" s="18"/>
       <c r="C25" s="19"/>
       <c r="D25" s="20"/>
-      <c r="E25" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="F25" s="22">
-        <v>38</v>
-      </c>
+      <c r="E25" s="21"/>
+      <c r="F25" s="22"/>
       <c r="G25" s="49"/>
-      <c r="H25" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I25" s="50" t="s">
-        <v>59</v>
-      </c>
+      <c r="H25" s="23"/>
+      <c r="I25" s="50"/>
       <c r="J25" s="34"/>
       <c r="K25" s="37"/>
     </row>
@@ -2846,54 +2739,24 @@
       <c r="B26" s="18"/>
       <c r="C26" s="19"/>
       <c r="D26" s="20"/>
-      <c r="E26" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="F26" s="22">
-        <v>60</v>
-      </c>
+      <c r="E26" s="21"/>
+      <c r="F26" s="22"/>
       <c r="G26" s="49"/>
-      <c r="H26" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I26" s="51" t="s">
-        <v>61</v>
-      </c>
-      <c r="J26" s="34">
-        <f>SUM(F19:F26)-B19</f>
-        <v>-66</v>
-      </c>
+      <c r="H26" s="23"/>
+      <c r="I26" s="51"/>
+      <c r="J26" s="34"/>
       <c r="K26" s="37"/>
     </row>
     <row r="27" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="B27" s="18">
-        <v>2511</v>
-      </c>
-      <c r="C27" s="19">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="D27" s="20">
-        <f t="shared" si="0"/>
-        <v>22096.800000000003</v>
-      </c>
-      <c r="E27" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="F27" s="22">
-        <v>2393</v>
-      </c>
+      <c r="A27" s="21"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="22"/>
       <c r="G27" s="49"/>
-      <c r="H27" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I27" s="50" t="s">
-        <v>53</v>
-      </c>
+      <c r="H27" s="23"/>
+      <c r="I27" s="50"/>
       <c r="J27" s="34"/>
     </row>
     <row r="28" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
@@ -2901,20 +2764,11 @@
       <c r="B28" s="18"/>
       <c r="C28" s="19"/>
       <c r="D28" s="20"/>
-      <c r="E28" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="F28" s="22">
-        <v>15</v>
-      </c>
+      <c r="E28" s="21"/>
+      <c r="F28" s="22"/>
       <c r="G28" s="49"/>
-      <c r="H28" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I28" s="52" t="s">
-        <v>62</v>
-      </c>
+      <c r="H28" s="23"/>
+      <c r="I28" s="52"/>
       <c r="J28" s="34"/>
     </row>
     <row r="29" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
@@ -2922,48 +2776,22 @@
       <c r="B29" s="18"/>
       <c r="C29" s="19"/>
       <c r="D29" s="20"/>
-      <c r="E29" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="F29" s="22">
-        <v>99</v>
-      </c>
+      <c r="E29" s="21"/>
+      <c r="F29" s="22"/>
       <c r="G29" s="49"/>
-      <c r="H29" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="H29" s="23"/>
       <c r="I29" s="40"/>
-      <c r="J29" s="34">
-        <f>SUM(F27:F29)-B27</f>
-        <v>-4</v>
-      </c>
+      <c r="J29" s="34"/>
     </row>
     <row r="30" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="B30" s="18">
-        <v>244</v>
-      </c>
-      <c r="C30" s="19">
-        <v>12</v>
-      </c>
-      <c r="D30" s="20">
-        <f t="shared" si="0"/>
-        <v>2928</v>
-      </c>
-      <c r="E30" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="F30" s="22">
-        <v>1</v>
-      </c>
+      <c r="A30" s="21"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="22"/>
       <c r="G30" s="49"/>
-      <c r="H30" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="H30" s="23"/>
       <c r="I30" s="38"/>
       <c r="J30" s="34"/>
     </row>
@@ -2972,20 +2800,11 @@
       <c r="B31" s="18"/>
       <c r="C31" s="19"/>
       <c r="D31" s="20"/>
-      <c r="E31" s="21" t="s">
-        <v>64</v>
-      </c>
-      <c r="F31" s="22">
-        <v>1</v>
-      </c>
+      <c r="E31" s="21"/>
+      <c r="F31" s="22"/>
       <c r="G31" s="49"/>
-      <c r="H31" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I31" s="38" t="s">
-        <v>65</v>
-      </c>
+      <c r="H31" s="23"/>
+      <c r="I31" s="38"/>
       <c r="J31" s="34"/>
     </row>
     <row r="32" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
@@ -2993,17 +2812,10 @@
       <c r="B32" s="18"/>
       <c r="C32" s="19"/>
       <c r="D32" s="20"/>
-      <c r="E32" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="F32" s="22">
-        <v>1</v>
-      </c>
+      <c r="E32" s="21"/>
+      <c r="F32" s="22"/>
       <c r="G32" s="49"/>
-      <c r="H32" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="H32" s="23"/>
       <c r="I32" s="38"/>
       <c r="J32" s="34"/>
     </row>
@@ -3012,17 +2824,10 @@
       <c r="B33" s="18"/>
       <c r="C33" s="19"/>
       <c r="D33" s="20"/>
-      <c r="E33" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="F33" s="22">
-        <v>9</v>
-      </c>
+      <c r="E33" s="21"/>
+      <c r="F33" s="22"/>
       <c r="G33" s="49"/>
-      <c r="H33" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="H33" s="23"/>
       <c r="I33" s="38"/>
       <c r="J33" s="34"/>
     </row>
@@ -3031,20 +2836,11 @@
       <c r="B34" s="18"/>
       <c r="C34" s="19"/>
       <c r="D34" s="20"/>
-      <c r="E34" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="F34" s="22">
-        <v>1</v>
-      </c>
+      <c r="E34" s="21"/>
+      <c r="F34" s="22"/>
       <c r="G34" s="49"/>
-      <c r="H34" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I34" s="38" t="s">
-        <v>70</v>
-      </c>
+      <c r="H34" s="23"/>
+      <c r="I34" s="38"/>
       <c r="J34" s="34"/>
     </row>
     <row r="35" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
@@ -3052,20 +2848,11 @@
       <c r="B35" s="18"/>
       <c r="C35" s="19"/>
       <c r="D35" s="20"/>
-      <c r="E35" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="F35" s="22">
-        <v>6</v>
-      </c>
+      <c r="E35" s="21"/>
+      <c r="F35" s="22"/>
       <c r="G35" s="49"/>
-      <c r="H35" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I35" s="54" t="s">
-        <v>72</v>
-      </c>
+      <c r="H35" s="23"/>
+      <c r="I35" s="54"/>
       <c r="J35" s="34"/>
     </row>
     <row r="36" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
@@ -3073,20 +2860,11 @@
       <c r="B36" s="18"/>
       <c r="C36" s="19"/>
       <c r="D36" s="20"/>
-      <c r="E36" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="F36" s="22">
-        <v>1</v>
-      </c>
+      <c r="E36" s="21"/>
+      <c r="F36" s="22"/>
       <c r="G36" s="49"/>
-      <c r="H36" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I36" s="53" t="s">
-        <v>74</v>
-      </c>
+      <c r="H36" s="23"/>
+      <c r="I36" s="53"/>
       <c r="J36" s="34"/>
     </row>
     <row r="37" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
@@ -3094,17 +2872,10 @@
       <c r="B37" s="18"/>
       <c r="C37" s="19"/>
       <c r="D37" s="20"/>
-      <c r="E37" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="F37" s="22">
-        <v>1</v>
-      </c>
+      <c r="E37" s="21"/>
+      <c r="F37" s="22"/>
       <c r="G37" s="49"/>
-      <c r="H37" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="H37" s="23"/>
       <c r="I37" s="38"/>
       <c r="J37" s="34"/>
     </row>
@@ -3113,20 +2884,11 @@
       <c r="B38" s="18"/>
       <c r="C38" s="19"/>
       <c r="D38" s="20"/>
-      <c r="E38" s="21" t="s">
-        <v>76</v>
-      </c>
-      <c r="F38" s="22">
-        <v>18</v>
-      </c>
+      <c r="E38" s="21"/>
+      <c r="F38" s="22"/>
       <c r="G38" s="49"/>
-      <c r="H38" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I38" s="53" t="s">
-        <v>77</v>
-      </c>
+      <c r="H38" s="23"/>
+      <c r="I38" s="53"/>
       <c r="J38" s="34"/>
     </row>
     <row r="39" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
@@ -3134,17 +2896,10 @@
       <c r="B39" s="18"/>
       <c r="C39" s="19"/>
       <c r="D39" s="20"/>
-      <c r="E39" s="21" t="s">
-        <v>76</v>
-      </c>
-      <c r="F39" s="22">
-        <v>209</v>
-      </c>
+      <c r="E39" s="21"/>
+      <c r="F39" s="22"/>
       <c r="G39" s="49"/>
-      <c r="H39" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="H39" s="23"/>
       <c r="I39" s="38"/>
       <c r="J39" s="34"/>
     </row>
@@ -3153,17 +2908,10 @@
       <c r="B40" s="18"/>
       <c r="C40" s="19"/>
       <c r="D40" s="20"/>
-      <c r="E40" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="F40" s="22">
-        <v>2</v>
-      </c>
+      <c r="E40" s="21"/>
+      <c r="F40" s="22"/>
       <c r="G40" s="49"/>
-      <c r="H40" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="H40" s="23"/>
       <c r="I40" s="38"/>
       <c r="J40" s="34"/>
     </row>
@@ -3172,48 +2920,22 @@
       <c r="B41" s="18"/>
       <c r="C41" s="19"/>
       <c r="D41" s="20"/>
-      <c r="E41" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="F41" s="22">
-        <v>4</v>
-      </c>
+      <c r="E41" s="21"/>
+      <c r="F41" s="22"/>
       <c r="G41" s="49"/>
-      <c r="H41" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="H41" s="23"/>
       <c r="I41" s="38"/>
-      <c r="J41" s="34">
-        <f>SUM(F30:F41)-B30</f>
-        <v>10</v>
-      </c>
+      <c r="J41" s="34"/>
     </row>
     <row r="42" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A42" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="B42" s="18">
-        <v>4731</v>
-      </c>
-      <c r="C42" s="19">
-        <v>11.2</v>
-      </c>
-      <c r="D42" s="20">
-        <f t="shared" si="0"/>
-        <v>52987.199999999997</v>
-      </c>
-      <c r="E42" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="F42" s="22">
-        <v>2762</v>
-      </c>
+      <c r="A42" s="21"/>
+      <c r="B42" s="18"/>
+      <c r="C42" s="19"/>
+      <c r="D42" s="20"/>
+      <c r="E42" s="21"/>
+      <c r="F42" s="22"/>
       <c r="G42" s="49"/>
-      <c r="H42" s="23">
-        <f>F42*G42</f>
-        <v>0</v>
-      </c>
+      <c r="H42" s="23"/>
       <c r="I42" s="38"/>
       <c r="J42" s="34"/>
       <c r="K42" s="45"/>
@@ -3223,113 +2945,49 @@
       <c r="B43" s="18"/>
       <c r="C43" s="19"/>
       <c r="D43" s="20"/>
-      <c r="E43" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="F43" s="22">
-        <v>1779</v>
-      </c>
+      <c r="E43" s="21"/>
+      <c r="F43" s="22"/>
       <c r="G43" s="49"/>
-      <c r="H43" s="23">
-        <f t="shared" ref="H43:H44" si="2">F43*G43</f>
-        <v>0</v>
-      </c>
+      <c r="H43" s="23"/>
       <c r="I43" s="38"/>
-      <c r="J43" s="34">
-        <f>F42+F43-B42</f>
-        <v>-190</v>
-      </c>
+      <c r="J43" s="34"/>
       <c r="K43" s="45"/>
     </row>
     <row r="44" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A44" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="B44" s="18">
-        <v>1609</v>
-      </c>
-      <c r="C44" s="19">
-        <v>6</v>
-      </c>
-      <c r="D44" s="20">
-        <f t="shared" si="0"/>
-        <v>9654</v>
-      </c>
-      <c r="E44" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="F44" s="22">
-        <v>1609</v>
-      </c>
+      <c r="A44" s="21"/>
+      <c r="B44" s="18"/>
+      <c r="C44" s="19"/>
+      <c r="D44" s="20"/>
+      <c r="E44" s="21"/>
+      <c r="F44" s="22"/>
       <c r="G44" s="49"/>
-      <c r="H44" s="23">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="H44" s="23"/>
       <c r="I44" s="38"/>
-      <c r="J44" s="34">
-        <f>F44-B44</f>
-        <v>0</v>
-      </c>
+      <c r="J44" s="34"/>
       <c r="K44" s="47"/>
     </row>
     <row r="45" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A45" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="B45" s="18">
-        <v>481</v>
-      </c>
-      <c r="C45" s="19">
-        <v>0.1</v>
-      </c>
-      <c r="D45" s="20">
-        <f t="shared" si="0"/>
-        <v>48.1</v>
-      </c>
-      <c r="E45" s="55" t="s">
-        <v>80</v>
-      </c>
-      <c r="F45" s="22">
-        <v>478</v>
-      </c>
+      <c r="A45" s="21"/>
+      <c r="B45" s="18"/>
+      <c r="C45" s="19"/>
+      <c r="D45" s="20"/>
+      <c r="E45" s="55"/>
+      <c r="F45" s="22"/>
       <c r="G45" s="49"/>
-      <c r="H45" s="23">
-        <f>F45*G45</f>
-        <v>0</v>
-      </c>
+      <c r="H45" s="23"/>
       <c r="I45" s="38"/>
-      <c r="J45" s="34">
-        <f>F45-B45</f>
-        <v>-3</v>
-      </c>
+      <c r="J45" s="34"/>
       <c r="K45" s="47"/>
     </row>
     <row r="46" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A46" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="B46" s="18">
-        <v>295</v>
-      </c>
-      <c r="C46" s="19">
-        <v>13.6</v>
-      </c>
-      <c r="D46" s="20">
-        <f t="shared" si="0"/>
-        <v>4012</v>
-      </c>
-      <c r="E46" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="F46" s="22">
-        <v>146</v>
-      </c>
+      <c r="A46" s="21"/>
+      <c r="B46" s="18"/>
+      <c r="C46" s="19"/>
+      <c r="D46" s="20"/>
+      <c r="E46" s="21"/>
+      <c r="F46" s="22"/>
       <c r="G46" s="49"/>
-      <c r="H46" s="23">
-        <f t="shared" ref="H46:H58" si="3">F46*G46</f>
-        <v>0</v>
-      </c>
+      <c r="H46" s="23"/>
       <c r="I46" s="38"/>
       <c r="J46" s="34"/>
       <c r="K46" s="1"/>
@@ -3339,17 +2997,10 @@
       <c r="B47" s="18"/>
       <c r="C47" s="19"/>
       <c r="D47" s="20"/>
-      <c r="E47" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="F47" s="22">
-        <v>35</v>
-      </c>
+      <c r="E47" s="21"/>
+      <c r="F47" s="22"/>
       <c r="G47" s="49"/>
-      <c r="H47" s="23">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="H47" s="23"/>
       <c r="I47" s="38"/>
       <c r="J47" s="34"/>
       <c r="K47" s="1"/>
@@ -3359,17 +3010,10 @@
       <c r="B48" s="18"/>
       <c r="C48" s="19"/>
       <c r="D48" s="20"/>
-      <c r="E48" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="F48" s="22">
-        <v>1</v>
-      </c>
+      <c r="E48" s="21"/>
+      <c r="F48" s="22"/>
       <c r="G48" s="49"/>
-      <c r="H48" s="23">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="H48" s="23"/>
       <c r="I48" s="38"/>
       <c r="J48" s="34"/>
       <c r="K48" s="1"/>
@@ -3379,17 +3023,10 @@
       <c r="B49" s="18"/>
       <c r="C49" s="19"/>
       <c r="D49" s="20"/>
-      <c r="E49" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="F49" s="22">
-        <v>1</v>
-      </c>
+      <c r="E49" s="21"/>
+      <c r="F49" s="22"/>
       <c r="G49" s="49"/>
-      <c r="H49" s="23">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="H49" s="23"/>
       <c r="I49" s="38"/>
       <c r="J49" s="34"/>
       <c r="K49" s="1"/>
@@ -3399,17 +3036,10 @@
       <c r="B50" s="18"/>
       <c r="C50" s="19"/>
       <c r="D50" s="20"/>
-      <c r="E50" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="F50" s="22">
-        <v>1</v>
-      </c>
+      <c r="E50" s="21"/>
+      <c r="F50" s="22"/>
       <c r="G50" s="49"/>
-      <c r="H50" s="23">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="H50" s="23"/>
       <c r="I50" s="38"/>
       <c r="J50" s="34"/>
       <c r="K50" s="1"/>
@@ -3419,20 +3049,11 @@
       <c r="B51" s="18"/>
       <c r="C51" s="19"/>
       <c r="D51" s="20"/>
-      <c r="E51" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="F51" s="22">
-        <v>16</v>
-      </c>
+      <c r="E51" s="21"/>
+      <c r="F51" s="22"/>
       <c r="G51" s="49"/>
-      <c r="H51" s="23">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I51" s="56" t="s">
-        <v>87</v>
-      </c>
+      <c r="H51" s="23"/>
+      <c r="I51" s="56"/>
       <c r="J51" s="34"/>
       <c r="K51" s="1"/>
     </row>
@@ -3441,20 +3062,11 @@
       <c r="B52" s="18"/>
       <c r="C52" s="19"/>
       <c r="D52" s="20"/>
-      <c r="E52" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="F52" s="22">
-        <v>12</v>
-      </c>
+      <c r="E52" s="21"/>
+      <c r="F52" s="22"/>
       <c r="G52" s="49"/>
-      <c r="H52" s="23">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I52" s="39" t="s">
-        <v>83</v>
-      </c>
+      <c r="H52" s="23"/>
+      <c r="I52" s="39"/>
       <c r="J52" s="34"/>
       <c r="K52" s="1"/>
     </row>
@@ -3463,20 +3075,11 @@
       <c r="B53" s="18"/>
       <c r="C53" s="19"/>
       <c r="D53" s="20"/>
-      <c r="E53" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="F53" s="22">
-        <v>7</v>
-      </c>
+      <c r="E53" s="21"/>
+      <c r="F53" s="22"/>
       <c r="G53" s="49"/>
-      <c r="H53" s="23">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I53" s="38" t="s">
-        <v>84</v>
-      </c>
+      <c r="H53" s="23"/>
+      <c r="I53" s="38"/>
       <c r="J53" s="34"/>
       <c r="K53" s="1"/>
     </row>
@@ -3485,20 +3088,11 @@
       <c r="B54" s="18"/>
       <c r="C54" s="19"/>
       <c r="D54" s="20"/>
-      <c r="E54" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="F54" s="22">
-        <v>25</v>
-      </c>
+      <c r="E54" s="21"/>
+      <c r="F54" s="22"/>
       <c r="G54" s="49"/>
-      <c r="H54" s="23">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I54" s="38" t="s">
-        <v>85</v>
-      </c>
+      <c r="H54" s="23"/>
+      <c r="I54" s="38"/>
       <c r="J54" s="34"/>
       <c r="K54" s="1"/>
     </row>
@@ -3507,20 +3101,11 @@
       <c r="B55" s="18"/>
       <c r="C55" s="19"/>
       <c r="D55" s="20"/>
-      <c r="E55" s="21" t="s">
-        <v>88</v>
-      </c>
-      <c r="F55" s="22">
-        <v>18</v>
-      </c>
+      <c r="E55" s="21"/>
+      <c r="F55" s="22"/>
       <c r="G55" s="49"/>
-      <c r="H55" s="23">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I55" s="38" t="s">
-        <v>89</v>
-      </c>
+      <c r="H55" s="23"/>
+      <c r="I55" s="38"/>
       <c r="J55" s="34"/>
       <c r="K55" s="1"/>
     </row>
@@ -3529,20 +3114,11 @@
       <c r="B56" s="18"/>
       <c r="C56" s="19"/>
       <c r="D56" s="20"/>
-      <c r="E56" s="21" t="s">
-        <v>88</v>
-      </c>
-      <c r="F56" s="22">
-        <v>5</v>
-      </c>
+      <c r="E56" s="21"/>
+      <c r="F56" s="22"/>
       <c r="G56" s="49"/>
-      <c r="H56" s="23">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I56" s="38" t="s">
-        <v>90</v>
-      </c>
+      <c r="H56" s="23"/>
+      <c r="I56" s="38"/>
       <c r="J56" s="34"/>
       <c r="K56" s="1"/>
     </row>
@@ -3551,17 +3127,10 @@
       <c r="B57" s="18"/>
       <c r="C57" s="19"/>
       <c r="D57" s="20"/>
-      <c r="E57" s="21" t="s">
-        <v>91</v>
-      </c>
-      <c r="F57" s="22">
-        <v>7</v>
-      </c>
+      <c r="E57" s="21"/>
+      <c r="F57" s="22"/>
       <c r="G57" s="49"/>
-      <c r="H57" s="23">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="H57" s="23"/>
       <c r="I57" s="38"/>
       <c r="J57" s="34"/>
       <c r="K57" s="1"/>
@@ -3571,49 +3140,23 @@
       <c r="B58" s="18"/>
       <c r="C58" s="19"/>
       <c r="D58" s="20"/>
-      <c r="E58" s="21" t="s">
-        <v>92</v>
-      </c>
-      <c r="F58" s="22">
-        <v>8</v>
-      </c>
+      <c r="E58" s="21"/>
+      <c r="F58" s="22"/>
       <c r="G58" s="49"/>
-      <c r="H58" s="23">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="H58" s="23"/>
       <c r="I58" s="38"/>
-      <c r="J58" s="34">
-        <f>SUM(F46:F58)-B46</f>
-        <v>-13</v>
-      </c>
+      <c r="J58" s="34"/>
       <c r="K58" s="1"/>
     </row>
     <row r="59" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A59" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="B59" s="18">
-        <v>2532</v>
-      </c>
-      <c r="C59" s="19">
-        <v>13.1</v>
-      </c>
-      <c r="D59" s="20">
-        <f t="shared" si="0"/>
-        <v>33169.199999999997</v>
-      </c>
-      <c r="E59" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="F59" s="22">
-        <v>2469</v>
-      </c>
+      <c r="A59" s="21"/>
+      <c r="B59" s="18"/>
+      <c r="C59" s="19"/>
+      <c r="D59" s="20"/>
+      <c r="E59" s="21"/>
+      <c r="F59" s="22"/>
       <c r="G59" s="49"/>
-      <c r="H59" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="H59" s="23"/>
       <c r="I59" s="38"/>
       <c r="J59" s="34"/>
       <c r="K59" s="1"/>
@@ -3623,49 +3166,23 @@
       <c r="B60" s="18"/>
       <c r="C60" s="19"/>
       <c r="D60" s="20"/>
-      <c r="E60" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="F60" s="22">
-        <v>10</v>
-      </c>
+      <c r="E60" s="21"/>
+      <c r="F60" s="22"/>
       <c r="G60" s="49"/>
-      <c r="H60" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="H60" s="23"/>
       <c r="I60" s="38"/>
-      <c r="J60" s="34">
-        <f>SUM(F59:F60)-B59</f>
-        <v>-53</v>
-      </c>
+      <c r="J60" s="34"/>
       <c r="K60" s="1"/>
     </row>
     <row r="61" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A61" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="B61" s="18">
-        <v>287</v>
-      </c>
-      <c r="C61" s="19">
-        <v>14.2</v>
-      </c>
-      <c r="D61" s="20">
-        <f t="shared" si="0"/>
-        <v>4075.3999999999996</v>
-      </c>
-      <c r="E61" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="F61" s="22">
-        <v>270</v>
-      </c>
+      <c r="A61" s="21"/>
+      <c r="B61" s="18"/>
+      <c r="C61" s="19"/>
+      <c r="D61" s="20"/>
+      <c r="E61" s="21"/>
+      <c r="F61" s="22"/>
       <c r="G61" s="49"/>
-      <c r="H61" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="H61" s="23"/>
       <c r="I61" s="38"/>
       <c r="J61" s="34"/>
       <c r="K61" s="46"/>
@@ -3675,17 +3192,10 @@
       <c r="B62" s="18"/>
       <c r="C62" s="19"/>
       <c r="D62" s="20"/>
-      <c r="E62" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="F62" s="22">
-        <v>40</v>
-      </c>
+      <c r="E62" s="21"/>
+      <c r="F62" s="22"/>
       <c r="G62" s="49"/>
-      <c r="H62" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="H62" s="23"/>
       <c r="I62" s="38"/>
       <c r="J62" s="34"/>
       <c r="K62" s="46"/>
@@ -3695,54 +3205,24 @@
       <c r="B63" s="18"/>
       <c r="C63" s="19"/>
       <c r="D63" s="20"/>
-      <c r="E63" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="F63" s="22">
-        <v>52</v>
-      </c>
+      <c r="E63" s="21"/>
+      <c r="F63" s="22"/>
       <c r="G63" s="49"/>
-      <c r="H63" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I63" s="53" t="s">
-        <v>95</v>
-      </c>
-      <c r="J63" s="34">
-        <f>SUM(F61:F63)-B61</f>
-        <v>75</v>
-      </c>
+      <c r="H63" s="23"/>
+      <c r="I63" s="53"/>
+      <c r="J63" s="34"/>
       <c r="K63" s="46"/>
     </row>
     <row r="64" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A64" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="B64" s="18">
-        <v>1171</v>
-      </c>
-      <c r="C64" s="19">
-        <v>13.6</v>
-      </c>
-      <c r="D64" s="20">
-        <f t="shared" si="0"/>
-        <v>15925.6</v>
-      </c>
-      <c r="E64" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="F64" s="22">
-        <v>1144</v>
-      </c>
+      <c r="A64" s="21"/>
+      <c r="B64" s="18"/>
+      <c r="C64" s="19"/>
+      <c r="D64" s="20"/>
+      <c r="E64" s="21"/>
+      <c r="F64" s="22"/>
       <c r="G64" s="49"/>
-      <c r="H64" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I64" s="58" t="s">
-        <v>96</v>
-      </c>
+      <c r="H64" s="23"/>
+      <c r="I64" s="58"/>
       <c r="J64" s="34"/>
       <c r="K64" s="1"/>
     </row>
@@ -3751,54 +3231,24 @@
       <c r="B65" s="18"/>
       <c r="C65" s="19"/>
       <c r="D65" s="20"/>
-      <c r="E65" s="21" t="s">
-        <v>97</v>
-      </c>
-      <c r="F65" s="22">
-        <v>18</v>
-      </c>
+      <c r="E65" s="21"/>
+      <c r="F65" s="22"/>
       <c r="G65" s="49"/>
-      <c r="H65" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I65" s="58" t="s">
-        <v>96</v>
-      </c>
-      <c r="J65" s="34">
-        <f>F64+F65-B64</f>
-        <v>-9</v>
-      </c>
+      <c r="H65" s="23"/>
+      <c r="I65" s="58"/>
+      <c r="J65" s="34"/>
       <c r="K65" s="1"/>
     </row>
     <row r="66" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A66" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="B66" s="18">
-        <v>95</v>
-      </c>
-      <c r="C66" s="19">
-        <v>12</v>
-      </c>
-      <c r="D66" s="20">
-        <f t="shared" si="0"/>
-        <v>1140</v>
-      </c>
-      <c r="E66" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="F66" s="22">
-        <v>40</v>
-      </c>
+      <c r="A66" s="21"/>
+      <c r="B66" s="18"/>
+      <c r="C66" s="19"/>
+      <c r="D66" s="20"/>
+      <c r="E66" s="21"/>
+      <c r="F66" s="22"/>
       <c r="G66" s="49"/>
-      <c r="H66" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I66" s="38" t="s">
-        <v>65</v>
-      </c>
+      <c r="H66" s="23"/>
+      <c r="I66" s="38"/>
       <c r="J66" s="34"/>
     </row>
     <row r="67" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
@@ -3806,20 +3256,11 @@
       <c r="B67" s="18"/>
       <c r="C67" s="19"/>
       <c r="D67" s="20"/>
-      <c r="E67" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="F67" s="22">
-        <v>20</v>
-      </c>
+      <c r="E67" s="21"/>
+      <c r="F67" s="22"/>
       <c r="G67" s="49"/>
-      <c r="H67" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I67" s="38" t="s">
-        <v>69</v>
-      </c>
+      <c r="H67" s="23"/>
+      <c r="I67" s="38"/>
       <c r="J67" s="34"/>
     </row>
     <row r="68" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
@@ -3827,50 +3268,22 @@
       <c r="B68" s="18"/>
       <c r="C68" s="19"/>
       <c r="D68" s="20"/>
-      <c r="E68" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="F68" s="22">
-        <v>32</v>
-      </c>
+      <c r="E68" s="21"/>
+      <c r="F68" s="22"/>
       <c r="G68" s="49"/>
-      <c r="H68" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I68" s="39" t="s">
-        <v>98</v>
-      </c>
-      <c r="J68" s="34">
-        <f>SUM(F66:F68)-B66</f>
-        <v>-3</v>
-      </c>
+      <c r="H68" s="23"/>
+      <c r="I68" s="39"/>
+      <c r="J68" s="34"/>
     </row>
     <row r="69" spans="1:11" s="4" customFormat="1" ht="35.15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A69" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="B69" s="18">
-        <v>496</v>
-      </c>
-      <c r="C69" s="19">
-        <v>9</v>
-      </c>
-      <c r="D69" s="20">
-        <f t="shared" si="0"/>
-        <v>4464</v>
-      </c>
-      <c r="E69" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="F69" s="22">
-        <v>44</v>
-      </c>
+      <c r="A69" s="21"/>
+      <c r="B69" s="18"/>
+      <c r="C69" s="19"/>
+      <c r="D69" s="20"/>
+      <c r="E69" s="21"/>
+      <c r="F69" s="22"/>
       <c r="G69" s="49"/>
-      <c r="H69" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="H69" s="23"/>
       <c r="I69" s="39"/>
       <c r="J69" s="34"/>
     </row>
@@ -3879,20 +3292,11 @@
       <c r="B70" s="18"/>
       <c r="C70" s="19"/>
       <c r="D70" s="20"/>
-      <c r="E70" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="F70" s="22">
-        <v>3</v>
-      </c>
+      <c r="E70" s="21"/>
+      <c r="F70" s="22"/>
       <c r="G70" s="49"/>
-      <c r="H70" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I70" s="59" t="s">
-        <v>100</v>
-      </c>
+      <c r="H70" s="23"/>
+      <c r="I70" s="59"/>
       <c r="J70" s="34"/>
     </row>
     <row r="71" spans="1:11" s="4" customFormat="1" ht="35.15" customHeight="1" x14ac:dyDescent="0.45">
@@ -3900,17 +3304,10 @@
       <c r="B71" s="18"/>
       <c r="C71" s="19"/>
       <c r="D71" s="20"/>
-      <c r="E71" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="F71" s="22">
-        <v>4</v>
-      </c>
+      <c r="E71" s="21"/>
+      <c r="F71" s="22"/>
       <c r="G71" s="49"/>
-      <c r="H71" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="H71" s="23"/>
       <c r="I71" s="39"/>
       <c r="J71" s="34"/>
     </row>
@@ -3919,17 +3316,10 @@
       <c r="B72" s="18"/>
       <c r="C72" s="19"/>
       <c r="D72" s="20"/>
-      <c r="E72" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="F72" s="22">
-        <v>2</v>
-      </c>
+      <c r="E72" s="21"/>
+      <c r="F72" s="22"/>
       <c r="G72" s="49"/>
-      <c r="H72" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="H72" s="23"/>
       <c r="I72" s="39"/>
       <c r="J72" s="34"/>
     </row>
@@ -3938,20 +3328,11 @@
       <c r="B73" s="18"/>
       <c r="C73" s="19"/>
       <c r="D73" s="20"/>
-      <c r="E73" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="F73" s="22">
-        <v>11</v>
-      </c>
+      <c r="E73" s="21"/>
+      <c r="F73" s="22"/>
       <c r="G73" s="49"/>
-      <c r="H73" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I73" s="39" t="s">
-        <v>65</v>
-      </c>
+      <c r="H73" s="23"/>
+      <c r="I73" s="39"/>
       <c r="J73" s="34"/>
     </row>
     <row r="74" spans="1:11" s="4" customFormat="1" ht="35.15" customHeight="1" x14ac:dyDescent="0.45">
@@ -3959,17 +3340,10 @@
       <c r="B74" s="18"/>
       <c r="C74" s="19"/>
       <c r="D74" s="20"/>
-      <c r="E74" s="21" t="s">
-        <v>101</v>
-      </c>
-      <c r="F74" s="22">
-        <v>18</v>
-      </c>
+      <c r="E74" s="21"/>
+      <c r="F74" s="22"/>
       <c r="G74" s="49"/>
-      <c r="H74" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="H74" s="23"/>
       <c r="I74" s="39"/>
       <c r="J74" s="34"/>
     </row>
@@ -3978,17 +3352,10 @@
       <c r="B75" s="18"/>
       <c r="C75" s="19"/>
       <c r="D75" s="20"/>
-      <c r="E75" s="21" t="s">
-        <v>102</v>
-      </c>
-      <c r="F75" s="22">
-        <v>15</v>
-      </c>
+      <c r="E75" s="21"/>
+      <c r="F75" s="22"/>
       <c r="G75" s="49"/>
-      <c r="H75" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="H75" s="23"/>
       <c r="I75" s="39"/>
       <c r="J75" s="34"/>
     </row>
@@ -3997,20 +3364,11 @@
       <c r="B76" s="18"/>
       <c r="C76" s="19"/>
       <c r="D76" s="20"/>
-      <c r="E76" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="F76" s="22">
-        <v>34</v>
-      </c>
+      <c r="E76" s="21"/>
+      <c r="F76" s="22"/>
       <c r="G76" s="49"/>
-      <c r="H76" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I76" s="60" t="s">
-        <v>104</v>
-      </c>
+      <c r="H76" s="23"/>
+      <c r="I76" s="60"/>
       <c r="J76" s="34"/>
     </row>
     <row r="77" spans="1:11" s="4" customFormat="1" ht="35.15" customHeight="1" x14ac:dyDescent="0.45">
@@ -4018,17 +3376,10 @@
       <c r="B77" s="18"/>
       <c r="C77" s="19"/>
       <c r="D77" s="20"/>
-      <c r="E77" s="21" t="s">
-        <v>103</v>
-      </c>
-      <c r="F77" s="22">
-        <v>1</v>
-      </c>
+      <c r="E77" s="21"/>
+      <c r="F77" s="22"/>
       <c r="G77" s="49"/>
-      <c r="H77" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="H77" s="23"/>
       <c r="I77" s="39"/>
       <c r="J77" s="34"/>
     </row>
@@ -4037,20 +3388,11 @@
       <c r="B78" s="18"/>
       <c r="C78" s="19"/>
       <c r="D78" s="20"/>
-      <c r="E78" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="F78" s="22">
-        <v>9</v>
-      </c>
+      <c r="E78" s="21"/>
+      <c r="F78" s="22"/>
       <c r="G78" s="49"/>
-      <c r="H78" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I78" s="59" t="s">
-        <v>105</v>
-      </c>
+      <c r="H78" s="23"/>
+      <c r="I78" s="59"/>
       <c r="J78" s="34"/>
     </row>
     <row r="79" spans="1:11" s="4" customFormat="1" ht="35.15" customHeight="1" x14ac:dyDescent="0.45">
@@ -4058,20 +3400,11 @@
       <c r="B79" s="18"/>
       <c r="C79" s="19"/>
       <c r="D79" s="20"/>
-      <c r="E79" s="21" t="s">
-        <v>106</v>
-      </c>
-      <c r="F79" s="22">
-        <v>25</v>
-      </c>
+      <c r="E79" s="21"/>
+      <c r="F79" s="22"/>
       <c r="G79" s="49"/>
-      <c r="H79" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I79" s="59" t="s">
-        <v>108</v>
-      </c>
+      <c r="H79" s="23"/>
+      <c r="I79" s="59"/>
       <c r="J79" s="34"/>
     </row>
     <row r="80" spans="1:11" s="4" customFormat="1" ht="35.15" customHeight="1" x14ac:dyDescent="0.45">
@@ -4079,17 +3412,10 @@
       <c r="B80" s="18"/>
       <c r="C80" s="19"/>
       <c r="D80" s="20"/>
-      <c r="E80" s="21" t="s">
-        <v>106</v>
-      </c>
-      <c r="F80" s="22">
-        <v>6</v>
-      </c>
+      <c r="E80" s="21"/>
+      <c r="F80" s="22"/>
       <c r="G80" s="49"/>
-      <c r="H80" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="H80" s="23"/>
       <c r="I80" s="59"/>
       <c r="J80" s="34"/>
     </row>
@@ -4098,17 +3424,10 @@
       <c r="B81" s="18"/>
       <c r="C81" s="19"/>
       <c r="D81" s="20"/>
-      <c r="E81" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="F81" s="22">
-        <v>2</v>
-      </c>
+      <c r="E81" s="21"/>
+      <c r="F81" s="22"/>
       <c r="G81" s="49"/>
-      <c r="H81" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="H81" s="23"/>
       <c r="I81" s="59"/>
       <c r="J81" s="34"/>
     </row>
@@ -4117,17 +3436,10 @@
       <c r="B82" s="18"/>
       <c r="C82" s="19"/>
       <c r="D82" s="20"/>
-      <c r="E82" s="21" t="s">
-        <v>76</v>
-      </c>
-      <c r="F82" s="22">
-        <v>108</v>
-      </c>
+      <c r="E82" s="21"/>
+      <c r="F82" s="22"/>
       <c r="G82" s="49"/>
-      <c r="H82" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="H82" s="23"/>
       <c r="I82" s="59"/>
       <c r="J82" s="34"/>
     </row>
@@ -4136,17 +3448,10 @@
       <c r="B83" s="18"/>
       <c r="C83" s="19"/>
       <c r="D83" s="20"/>
-      <c r="E83" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="F83" s="22">
-        <v>180</v>
-      </c>
+      <c r="E83" s="21"/>
+      <c r="F83" s="22"/>
       <c r="G83" s="49"/>
-      <c r="H83" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="H83" s="23"/>
       <c r="I83" s="59"/>
       <c r="J83" s="34"/>
     </row>
@@ -4155,20 +3460,11 @@
       <c r="B84" s="18"/>
       <c r="C84" s="19"/>
       <c r="D84" s="20"/>
-      <c r="E84" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="F84" s="22">
-        <v>22</v>
-      </c>
+      <c r="E84" s="21"/>
+      <c r="F84" s="22"/>
       <c r="G84" s="49"/>
-      <c r="H84" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I84" s="59" t="s">
-        <v>107</v>
-      </c>
+      <c r="H84" s="23"/>
+      <c r="I84" s="59"/>
       <c r="J84" s="34"/>
     </row>
     <row r="85" spans="1:11" s="4" customFormat="1" ht="35.15" customHeight="1" x14ac:dyDescent="0.45">
@@ -4176,48 +3472,22 @@
       <c r="B85" s="18"/>
       <c r="C85" s="19"/>
       <c r="D85" s="20"/>
-      <c r="E85" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="F85" s="22">
-        <v>18</v>
-      </c>
+      <c r="E85" s="21"/>
+      <c r="F85" s="22"/>
       <c r="G85" s="49"/>
-      <c r="H85" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="H85" s="23"/>
       <c r="I85" s="39"/>
-      <c r="J85" s="34">
-        <f>SUM(F69:F85)-B69</f>
-        <v>6</v>
-      </c>
+      <c r="J85" s="34"/>
     </row>
     <row r="86" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A86" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="B86" s="18">
-        <v>58</v>
-      </c>
-      <c r="C86" s="19">
-        <v>35</v>
-      </c>
-      <c r="D86" s="20">
-        <f t="shared" si="0"/>
-        <v>2030</v>
-      </c>
-      <c r="E86" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="F86" s="22">
-        <v>7</v>
-      </c>
+      <c r="A86" s="21"/>
+      <c r="B86" s="18"/>
+      <c r="C86" s="19"/>
+      <c r="D86" s="20"/>
+      <c r="E86" s="21"/>
+      <c r="F86" s="22"/>
       <c r="G86" s="49"/>
-      <c r="H86" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="H86" s="23"/>
       <c r="I86" s="39"/>
       <c r="J86" s="34"/>
       <c r="K86" s="48"/>
@@ -4227,17 +3497,10 @@
       <c r="B87" s="18"/>
       <c r="C87" s="19"/>
       <c r="D87" s="20"/>
-      <c r="E87" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="F87" s="22">
-        <v>1</v>
-      </c>
+      <c r="E87" s="21"/>
+      <c r="F87" s="22"/>
       <c r="G87" s="49"/>
-      <c r="H87" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="H87" s="23"/>
       <c r="I87" s="39"/>
       <c r="J87" s="34"/>
       <c r="K87" s="48"/>
@@ -4247,20 +3510,11 @@
       <c r="B88" s="18"/>
       <c r="C88" s="19"/>
       <c r="D88" s="20"/>
-      <c r="E88" s="21" t="s">
-        <v>109</v>
-      </c>
-      <c r="F88" s="22">
-        <v>14</v>
-      </c>
+      <c r="E88" s="21"/>
+      <c r="F88" s="22"/>
       <c r="G88" s="49"/>
-      <c r="H88" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I88" s="59" t="s">
-        <v>110</v>
-      </c>
+      <c r="H88" s="23"/>
+      <c r="I88" s="59"/>
       <c r="J88" s="34"/>
       <c r="K88" s="48"/>
     </row>
@@ -4269,20 +3523,11 @@
       <c r="B89" s="18"/>
       <c r="C89" s="19"/>
       <c r="D89" s="20"/>
-      <c r="E89" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="F89" s="22">
-        <v>14</v>
-      </c>
+      <c r="E89" s="21"/>
+      <c r="F89" s="22"/>
       <c r="G89" s="49"/>
-      <c r="H89" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I89" s="59" t="s">
-        <v>111</v>
-      </c>
+      <c r="H89" s="23"/>
+      <c r="I89" s="59"/>
       <c r="J89" s="34"/>
       <c r="K89" s="48"/>
     </row>
@@ -4291,17 +3536,10 @@
       <c r="B90" s="18"/>
       <c r="C90" s="19"/>
       <c r="D90" s="20"/>
-      <c r="E90" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="F90" s="22">
-        <v>6</v>
-      </c>
+      <c r="E90" s="21"/>
+      <c r="F90" s="22"/>
       <c r="G90" s="49"/>
-      <c r="H90" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="H90" s="23"/>
       <c r="I90" s="39"/>
       <c r="J90" s="34"/>
       <c r="K90" s="48"/>
@@ -4311,17 +3549,10 @@
       <c r="B91" s="18"/>
       <c r="C91" s="19"/>
       <c r="D91" s="20"/>
-      <c r="E91" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="F91" s="22">
-        <v>2</v>
-      </c>
+      <c r="E91" s="21"/>
+      <c r="F91" s="22"/>
       <c r="G91" s="49"/>
-      <c r="H91" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="H91" s="23"/>
       <c r="I91" s="39"/>
       <c r="J91" s="34"/>
       <c r="K91" s="48"/>
@@ -4331,17 +3562,10 @@
       <c r="B92" s="18"/>
       <c r="C92" s="19"/>
       <c r="D92" s="20"/>
-      <c r="E92" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="F92" s="22">
-        <v>1</v>
-      </c>
+      <c r="E92" s="21"/>
+      <c r="F92" s="22"/>
       <c r="G92" s="49"/>
-      <c r="H92" s="23">
-        <f t="shared" ref="H92" si="4">F92*G92</f>
-        <v>0</v>
-      </c>
+      <c r="H92" s="23"/>
       <c r="I92" s="59"/>
       <c r="J92" s="34"/>
     </row>
@@ -4350,49 +3574,23 @@
       <c r="B93" s="18"/>
       <c r="C93" s="19"/>
       <c r="D93" s="20"/>
-      <c r="E93" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="F93" s="22">
-        <v>11</v>
-      </c>
+      <c r="E93" s="21"/>
+      <c r="F93" s="22"/>
       <c r="G93" s="49"/>
-      <c r="H93" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="H93" s="23"/>
       <c r="I93" s="39"/>
-      <c r="J93" s="34">
-        <f>SUM(F86:F93)-B86</f>
-        <v>-2</v>
-      </c>
+      <c r="J93" s="34"/>
       <c r="K93" s="48"/>
     </row>
     <row r="94" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A94" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="B94" s="18">
-        <v>202</v>
-      </c>
-      <c r="C94" s="19">
-        <v>10.5</v>
-      </c>
-      <c r="D94" s="20">
-        <f t="shared" si="0"/>
-        <v>2121</v>
-      </c>
-      <c r="E94" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="F94" s="22">
-        <v>1</v>
-      </c>
+      <c r="A94" s="21"/>
+      <c r="B94" s="18"/>
+      <c r="C94" s="19"/>
+      <c r="D94" s="20"/>
+      <c r="E94" s="21"/>
+      <c r="F94" s="22"/>
       <c r="G94" s="49"/>
-      <c r="H94" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="H94" s="23"/>
       <c r="I94" s="39"/>
       <c r="J94" s="34"/>
       <c r="K94" s="1"/>
@@ -4402,20 +3600,11 @@
       <c r="B95" s="18"/>
       <c r="C95" s="19"/>
       <c r="D95" s="20"/>
-      <c r="E95" s="21" t="s">
-        <v>109</v>
-      </c>
-      <c r="F95" s="22">
-        <v>64</v>
-      </c>
+      <c r="E95" s="21"/>
+      <c r="F95" s="22"/>
       <c r="G95" s="49"/>
-      <c r="H95" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I95" s="61" t="s">
-        <v>113</v>
-      </c>
+      <c r="H95" s="23"/>
+      <c r="I95" s="61"/>
       <c r="J95" s="34"/>
       <c r="K95" s="1"/>
     </row>
@@ -4424,17 +3613,10 @@
       <c r="B96" s="18"/>
       <c r="C96" s="19"/>
       <c r="D96" s="20"/>
-      <c r="E96" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="F96" s="22">
-        <v>6</v>
-      </c>
+      <c r="E96" s="21"/>
+      <c r="F96" s="22"/>
       <c r="G96" s="49"/>
-      <c r="H96" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="H96" s="23"/>
       <c r="I96" s="39"/>
       <c r="J96" s="34"/>
       <c r="K96" s="1"/>
@@ -4444,17 +3626,10 @@
       <c r="B97" s="18"/>
       <c r="C97" s="19"/>
       <c r="D97" s="20"/>
-      <c r="E97" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="F97" s="22">
-        <v>5</v>
-      </c>
+      <c r="E97" s="21"/>
+      <c r="F97" s="22"/>
       <c r="G97" s="49"/>
-      <c r="H97" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="H97" s="23"/>
       <c r="I97" s="39"/>
       <c r="J97" s="34"/>
       <c r="K97" s="1"/>
@@ -4464,17 +3639,10 @@
       <c r="B98" s="18"/>
       <c r="C98" s="19"/>
       <c r="D98" s="20"/>
-      <c r="E98" s="21" t="s">
-        <v>76</v>
-      </c>
-      <c r="F98" s="22">
-        <v>51</v>
-      </c>
+      <c r="E98" s="21"/>
+      <c r="F98" s="22"/>
       <c r="G98" s="49"/>
-      <c r="H98" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="H98" s="23"/>
       <c r="I98" s="39"/>
       <c r="J98" s="34"/>
       <c r="K98" s="1"/>
@@ -4484,20 +3652,11 @@
       <c r="B99" s="18"/>
       <c r="C99" s="19"/>
       <c r="D99" s="20"/>
-      <c r="E99" s="21" t="s">
-        <v>76</v>
-      </c>
-      <c r="F99" s="22">
-        <v>22</v>
-      </c>
+      <c r="E99" s="21"/>
+      <c r="F99" s="22"/>
       <c r="G99" s="49"/>
-      <c r="H99" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I99" s="59" t="s">
-        <v>115</v>
-      </c>
+      <c r="H99" s="23"/>
+      <c r="I99" s="59"/>
       <c r="J99" s="34"/>
       <c r="K99" s="1"/>
     </row>
@@ -4506,20 +3665,11 @@
       <c r="B100" s="18"/>
       <c r="C100" s="19"/>
       <c r="D100" s="20"/>
-      <c r="E100" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="F100" s="22">
-        <v>25</v>
-      </c>
+      <c r="E100" s="21"/>
+      <c r="F100" s="22"/>
       <c r="G100" s="49"/>
-      <c r="H100" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I100" s="59" t="s">
-        <v>116</v>
-      </c>
+      <c r="H100" s="23"/>
+      <c r="I100" s="59"/>
       <c r="J100" s="34"/>
       <c r="K100" s="1"/>
     </row>
@@ -4528,83 +3678,36 @@
       <c r="B101" s="18"/>
       <c r="C101" s="19"/>
       <c r="D101" s="20"/>
-      <c r="E101" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="F101" s="22">
-        <v>23</v>
-      </c>
+      <c r="E101" s="21"/>
+      <c r="F101" s="22"/>
       <c r="G101" s="49"/>
-      <c r="H101" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="H101" s="23"/>
       <c r="I101" s="39"/>
-      <c r="J101" s="34">
-        <f>SUM(F94:F101)-B94</f>
-        <v>-5</v>
-      </c>
+      <c r="J101" s="34"/>
       <c r="K101" s="1"/>
     </row>
     <row r="102" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A102" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="B102" s="18">
-        <v>1443</v>
-      </c>
-      <c r="C102" s="19">
-        <v>3.3</v>
-      </c>
-      <c r="D102" s="20">
-        <f t="shared" si="0"/>
-        <v>4761.8999999999996</v>
-      </c>
-      <c r="E102" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="F102" s="22">
-        <v>1456</v>
-      </c>
+      <c r="A102" s="21"/>
+      <c r="B102" s="18"/>
+      <c r="C102" s="19"/>
+      <c r="D102" s="20"/>
+      <c r="E102" s="21"/>
+      <c r="F102" s="22"/>
       <c r="G102" s="49"/>
-      <c r="H102" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I102" s="62" t="s">
-        <v>118</v>
-      </c>
-      <c r="J102" s="34">
-        <f>F102-B102</f>
-        <v>13</v>
-      </c>
+      <c r="H102" s="23"/>
+      <c r="I102" s="62"/>
+      <c r="J102" s="34"/>
       <c r="K102" s="48"/>
     </row>
     <row r="103" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A103" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="B103" s="18">
-        <v>2609</v>
-      </c>
-      <c r="C103" s="19">
-        <v>5.2</v>
-      </c>
-      <c r="D103" s="20">
-        <f t="shared" si="0"/>
-        <v>13566.800000000001</v>
-      </c>
-      <c r="E103" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="F103" s="22">
-        <v>1965</v>
-      </c>
+      <c r="A103" s="21"/>
+      <c r="B103" s="18"/>
+      <c r="C103" s="19"/>
+      <c r="D103" s="20"/>
+      <c r="E103" s="21"/>
+      <c r="F103" s="22"/>
       <c r="G103" s="49"/>
-      <c r="H103" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="H103" s="23"/>
       <c r="I103" s="39"/>
       <c r="J103" s="34"/>
     </row>
@@ -4613,48 +3716,22 @@
       <c r="B104" s="18"/>
       <c r="C104" s="19"/>
       <c r="D104" s="20"/>
-      <c r="E104" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="F104" s="22">
-        <v>640</v>
-      </c>
+      <c r="E104" s="21"/>
+      <c r="F104" s="22"/>
       <c r="G104" s="49"/>
-      <c r="H104" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="H104" s="23"/>
       <c r="I104" s="39"/>
-      <c r="J104" s="34">
-        <f>SUM(F103:F104)-B103</f>
-        <v>-4</v>
-      </c>
+      <c r="J104" s="34"/>
     </row>
     <row r="105" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A105" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="B105" s="18">
-        <v>212</v>
-      </c>
-      <c r="C105" s="19">
-        <v>13</v>
-      </c>
-      <c r="D105" s="20">
-        <f t="shared" si="0"/>
-        <v>2756</v>
-      </c>
-      <c r="E105" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="F105" s="22">
-        <v>150</v>
-      </c>
+      <c r="A105" s="21"/>
+      <c r="B105" s="18"/>
+      <c r="C105" s="19"/>
+      <c r="D105" s="20"/>
+      <c r="E105" s="21"/>
+      <c r="F105" s="22"/>
       <c r="G105" s="49"/>
-      <c r="H105" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="H105" s="23"/>
       <c r="I105" s="39"/>
       <c r="J105" s="34"/>
     </row>
@@ -4663,88 +3740,52 @@
       <c r="B106" s="18"/>
       <c r="C106" s="19"/>
       <c r="D106" s="20"/>
-      <c r="E106" s="21" t="s">
-        <v>44</v>
-      </c>
-      <c r="F106" s="22">
-        <v>56</v>
-      </c>
+      <c r="E106" s="21"/>
+      <c r="F106" s="22"/>
       <c r="G106" s="49"/>
-      <c r="H106" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I106" s="39" t="s">
-        <v>50</v>
-      </c>
-      <c r="J106" s="34">
-        <f>SUM(F105:F106)-B105</f>
-        <v>-6</v>
-      </c>
+      <c r="H106" s="23"/>
+      <c r="I106" s="39"/>
+      <c r="J106" s="34"/>
     </row>
     <row r="107" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A107" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="B107" s="18">
-        <v>35</v>
-      </c>
-      <c r="C107" s="19">
-        <v>2.6</v>
-      </c>
-      <c r="D107" s="20">
-        <f t="shared" si="0"/>
-        <v>91</v>
-      </c>
-      <c r="E107" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="F107" s="22">
-        <v>36</v>
-      </c>
+      <c r="A107" s="21"/>
+      <c r="B107" s="18"/>
+      <c r="C107" s="19"/>
+      <c r="D107" s="20"/>
+      <c r="E107" s="21"/>
+      <c r="F107" s="22"/>
       <c r="G107" s="49"/>
-      <c r="H107" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I107" s="57" t="s">
-        <v>93</v>
-      </c>
-      <c r="J107" s="34">
-        <f>F107-B107</f>
-        <v>1</v>
-      </c>
+      <c r="H107" s="23"/>
+      <c r="I107" s="57"/>
+      <c r="J107" s="34"/>
     </row>
     <row r="108" spans="1:11" ht="35.15" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="A108" s="24" t="s">
-        <v>12</v>
+      <c r="A108" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TOTAL</t>
+        </is>
       </c>
       <c r="B108" s="25">
-        <f>SUM(B13:B107)</f>
-        <v>31496</v>
+        <v>500</v>
       </c>
       <c r="C108" s="26"/>
       <c r="D108" s="27">
-        <f>SUM(D13:D107)</f>
-        <v>326577.60000000003</v>
-      </c>
-      <c r="E108" s="28" t="s">
-        <v>12</v>
+        <v>0</v>
+      </c>
+      <c r="E108" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TOTAL</t>
+        </is>
       </c>
       <c r="F108" s="29">
-        <f>SUM(F13:F107)</f>
-        <v>30965</v>
+        <v>500</v>
       </c>
       <c r="G108" s="26"/>
       <c r="H108" s="26">
-        <f>SUM(H13:H107)</f>
         <v>0</v>
       </c>
       <c r="I108" s="12"/>
-      <c r="J108" s="35">
-        <f>SUM(J13:J107)</f>
-        <v>-531</v>
-      </c>
+      <c r="J108" s="35"/>
     </row>
     <row r="109" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A109" s="4"/>
@@ -4756,41 +3797,49 @@
       <c r="G109" s="6"/>
       <c r="H109" s="6"/>
       <c r="I109" s="15"/>
+      <c r="J109"/>
     </row>
     <row r="111" spans="1:11" ht="35.15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="E111" s="85" t="s">
-        <v>3</v>
+      <c r="E111" s="85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Actual value</t>
+        </is>
       </c>
       <c r="F111" s="86"/>
       <c r="G111" s="86"/>
       <c r="H111" s="87">
-        <f>H108</f>
         <v>0</v>
       </c>
       <c r="I111" s="88"/>
+      <c r="J111"/>
     </row>
     <row r="112" spans="1:11" ht="35.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="E112" s="68" t="s">
-        <v>14</v>
+      <c r="E112" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provisonal Payment ( 90% )</t>
+        </is>
       </c>
       <c r="F112" s="69"/>
       <c r="G112" s="69"/>
       <c r="H112" s="70">
-        <v>293919.84000000003</v>
+        <v>0</v>
       </c>
       <c r="I112" s="71"/>
+      <c r="J112"/>
     </row>
     <row r="113" spans="1:11" ht="35.15" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="E113" s="72" t="s">
-        <v>4</v>
+      <c r="E113" s="72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Balance</t>
+        </is>
       </c>
       <c r="F113" s="73"/>
       <c r="G113" s="73"/>
       <c r="H113" s="74">
-        <f>H111-H112</f>
-        <v>-293919.84000000003</v>
+        <v>0</v>
       </c>
       <c r="I113" s="75"/>
+      <c r="J113"/>
     </row>
     <row r="114" spans="1:11" s="13" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I114" s="42"/>
@@ -4811,6 +3860,7 @@
       <c r="G115" s="17"/>
       <c r="H115" s="17"/>
       <c r="I115" s="43"/>
+      <c r="J115"/>
     </row>
     <row r="116" spans="1:11" ht="26.15" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="117" spans="1:11" ht="26.15" customHeight="1" x14ac:dyDescent="0.45"/>
@@ -4869,6 +3919,9 @@
     <row r="154" ht="26.15" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="155" ht="26.15" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="156" ht="26.15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="110">
+      <c r="J110"/>
+    </row>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="E112:G112"/>
@@ -4885,7 +3938,7 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="54" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait" r:id="rId1" fitToWidth="1"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="115" max="16383" man="1"/>
   </rowBreaks>
@@ -4898,14 +3951,14 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:K125"/>
+  <dimension ref="A2:J156"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="5" width="16.08203125" style="1" customWidth="1"/>
     <col min="6" max="6" width="15.5" style="1" customWidth="1"/>
     <col min="7" max="8" width="16.08203125" style="1" customWidth="1"/>
     <col min="9" max="9" width="19.58203125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="7.58203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.58203125" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
@@ -4939,8 +3992,10 @@
       <c r="A5" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>21</v>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">donald</t>
+        </is>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
@@ -4949,46 +4004,40 @@
         <v>1</v>
       </c>
       <c r="G5" s="11">
-        <v>46185</v>
+        <v>46245</v>
       </c>
       <c r="I5" s="41"/>
     </row>
     <row r="6" spans="1:10" s="9" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="8"/>
-      <c r="B6" s="8" t="s">
-        <v>15</v>
-      </c>
+      <c r="B6" s="8"/>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
       <c r="F6" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="8" t="s">
-        <v>28</v>
-      </c>
+      <c r="G6" s="8"/>
       <c r="I6" s="41"/>
     </row>
     <row r="7" spans="1:10" s="9" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="8"/>
-      <c r="B7" s="8" t="s">
-        <v>16</v>
-      </c>
+      <c r="B7" s="8"/>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
       <c r="F7" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="G7" s="8" t="s">
-        <v>29</v>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">s01234</t>
+        </is>
       </c>
       <c r="I7" s="41"/>
     </row>
     <row r="8" spans="1:10" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B8" s="1" t="s">
-        <v>17</v>
-      </c>
+      <c r="B8" s="1"/>
       <c r="F8" s="3"/>
     </row>
     <row r="9" spans="1:10" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.45">
@@ -5038,58 +4087,50 @@
       <c r="I12" s="21" t="s">
         <v>22</v>
       </c>
+      <c r="J12" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사진</t>
+        </is>
+      </c>
     </row>
     <row r="13" spans="1:10" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="21" t="s">
-        <v>30</v>
+      <c r="A13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">718 solids</t>
+        </is>
       </c>
       <c r="B13" s="18">
-        <v>10934</v>
-      </c>
-      <c r="C13" s="19">
-        <v>12</v>
-      </c>
+        <v>500</v>
+      </c>
+      <c r="C13" s="19"/>
       <c r="D13" s="20">
-        <f t="shared" ref="D13:D76" si="0">B13*C13</f>
-        <v>131208</v>
-      </c>
-      <c r="E13" s="21" t="s">
-        <v>30</v>
+        <v>0</v>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NI · IN 718 · VS</t>
+        </is>
       </c>
       <c r="F13" s="22">
-        <v>10501</v>
-      </c>
-      <c r="G13" s="49">
-        <v>12</v>
-      </c>
+        <v>500</v>
+      </c>
+      <c r="G13" s="49"/>
       <c r="H13" s="23">
-        <f t="shared" ref="H13:H76" si="1">F13*G13</f>
-        <v>126012</v>
+        <v>0</v>
       </c>
       <c r="I13" s="38"/>
-      <c r="J13" s="34"/>
+      <c r="J13" s="38"/>
     </row>
     <row r="14" spans="1:10" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="21"/>
       <c r="B14" s="18"/>
       <c r="C14" s="19"/>
       <c r="D14" s="20"/>
-      <c r="E14" s="63" t="s">
-        <v>44</v>
-      </c>
-      <c r="F14" s="22">
-        <v>107</v>
-      </c>
-      <c r="G14" s="49">
-        <v>5.5</v>
-      </c>
-      <c r="H14" s="23">
-        <f t="shared" si="1"/>
-        <v>588.5</v>
-      </c>
-      <c r="I14" s="64" t="s">
-        <v>45</v>
-      </c>
+      <c r="E14" s="63"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="49"/>
+      <c r="H14" s="23"/>
+      <c r="I14" s="64"/>
       <c r="J14" s="34"/>
     </row>
     <row r="15" spans="1:10" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
@@ -5097,19 +4138,10 @@
       <c r="B15" s="18"/>
       <c r="C15" s="19"/>
       <c r="D15" s="20"/>
-      <c r="E15" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="F15" s="22">
-        <v>34</v>
-      </c>
-      <c r="G15" s="49">
-        <v>12.6</v>
-      </c>
-      <c r="H15" s="23">
-        <f t="shared" si="1"/>
-        <v>428.4</v>
-      </c>
+      <c r="E15" s="21"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="49"/>
+      <c r="H15" s="23"/>
       <c r="I15" s="64"/>
       <c r="J15" s="34"/>
     </row>
@@ -5118,19 +4150,10 @@
       <c r="B16" s="18"/>
       <c r="C16" s="19"/>
       <c r="D16" s="20"/>
-      <c r="E16" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="F16" s="22">
-        <v>12</v>
-      </c>
-      <c r="G16" s="49">
-        <v>8.5</v>
-      </c>
-      <c r="H16" s="23">
-        <f t="shared" si="1"/>
-        <v>102</v>
-      </c>
+      <c r="E16" s="21"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="49"/>
+      <c r="H16" s="23"/>
       <c r="I16" s="64"/>
       <c r="J16" s="34"/>
     </row>
@@ -5139,47 +4162,22 @@
       <c r="B17" s="18"/>
       <c r="C17" s="19"/>
       <c r="D17" s="20"/>
-      <c r="E17" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="F17" s="22">
-        <v>2</v>
-      </c>
+      <c r="E17" s="21"/>
+      <c r="F17" s="22"/>
       <c r="G17" s="49"/>
       <c r="H17" s="23"/>
       <c r="I17" s="64"/>
-      <c r="J17" s="34">
-        <f>SUM(F13:F17)-B13</f>
-        <v>-278</v>
-      </c>
+      <c r="J17" s="34"/>
     </row>
     <row r="18" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="B18" s="18">
-        <v>1551</v>
-      </c>
-      <c r="C18" s="19">
-        <v>12.6</v>
-      </c>
-      <c r="D18" s="20">
-        <f t="shared" si="0"/>
-        <v>19542.599999999999</v>
-      </c>
-      <c r="E18" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="F18" s="22">
-        <v>754</v>
-      </c>
-      <c r="G18" s="49">
-        <v>12.6</v>
-      </c>
-      <c r="H18" s="23">
-        <f t="shared" si="1"/>
-        <v>9500.4</v>
-      </c>
+      <c r="A18" s="21"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="49"/>
+      <c r="H18" s="23"/>
       <c r="I18" s="64"/>
       <c r="J18" s="34"/>
       <c r="K18" s="37"/>
@@ -5189,22 +4187,11 @@
       <c r="B19" s="18"/>
       <c r="C19" s="19"/>
       <c r="D19" s="20"/>
-      <c r="E19" s="63" t="s">
-        <v>31</v>
-      </c>
-      <c r="F19" s="22">
-        <v>530</v>
-      </c>
-      <c r="G19" s="49">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="H19" s="23">
-        <f t="shared" si="1"/>
-        <v>4664</v>
-      </c>
-      <c r="I19" s="64" t="s">
-        <v>121</v>
-      </c>
+      <c r="E19" s="63"/>
+      <c r="F19" s="22"/>
+      <c r="G19" s="49"/>
+      <c r="H19" s="23"/>
+      <c r="I19" s="64"/>
       <c r="J19" s="34"/>
       <c r="K19" s="37"/>
     </row>
@@ -5213,22 +4200,11 @@
       <c r="B20" s="18"/>
       <c r="C20" s="19"/>
       <c r="D20" s="20"/>
-      <c r="E20" s="63" t="s">
-        <v>31</v>
-      </c>
-      <c r="F20" s="22">
-        <v>103</v>
-      </c>
-      <c r="G20" s="49">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="H20" s="23">
-        <f t="shared" si="1"/>
-        <v>906.40000000000009</v>
-      </c>
-      <c r="I20" s="64" t="s">
-        <v>119</v>
-      </c>
+      <c r="E20" s="63"/>
+      <c r="F20" s="22"/>
+      <c r="G20" s="49"/>
+      <c r="H20" s="23"/>
+      <c r="I20" s="64"/>
       <c r="J20" s="34"/>
       <c r="K20" s="37"/>
     </row>
@@ -5237,22 +4213,11 @@
       <c r="B21" s="18"/>
       <c r="C21" s="19"/>
       <c r="D21" s="20"/>
-      <c r="E21" s="63" t="s">
-        <v>58</v>
-      </c>
-      <c r="F21" s="22">
-        <v>38</v>
-      </c>
-      <c r="G21" s="49">
-        <v>4.5</v>
-      </c>
-      <c r="H21" s="23">
-        <f t="shared" si="1"/>
-        <v>171</v>
-      </c>
-      <c r="I21" s="64" t="s">
-        <v>120</v>
-      </c>
+      <c r="E21" s="63"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="49"/>
+      <c r="H21" s="23"/>
+      <c r="I21" s="64"/>
       <c r="J21" s="34"/>
       <c r="K21" s="37"/>
     </row>
@@ -5261,53 +4226,23 @@
       <c r="B22" s="18"/>
       <c r="C22" s="19"/>
       <c r="D22" s="20"/>
-      <c r="E22" s="63" t="s">
-        <v>60</v>
-      </c>
-      <c r="F22" s="22">
-        <v>60</v>
-      </c>
-      <c r="G22" s="49">
-        <v>6.5</v>
-      </c>
-      <c r="H22" s="23">
-        <f t="shared" si="1"/>
-        <v>390</v>
-      </c>
+      <c r="E22" s="63"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="49"/>
+      <c r="H22" s="23"/>
       <c r="I22" s="65"/>
-      <c r="J22" s="34">
-        <f>SUM(F18:F22)-B18</f>
-        <v>-66</v>
-      </c>
+      <c r="J22" s="34"/>
       <c r="K22" s="37"/>
     </row>
     <row r="23" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="B23" s="18">
-        <v>2511</v>
-      </c>
-      <c r="C23" s="19">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="D23" s="20">
-        <f t="shared" si="0"/>
-        <v>22096.800000000003</v>
-      </c>
-      <c r="E23" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="F23" s="22">
-        <v>2408</v>
-      </c>
-      <c r="G23" s="49">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="H23" s="23">
-        <f t="shared" si="1"/>
-        <v>21190.400000000001</v>
-      </c>
+      <c r="A23" s="21"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="49"/>
+      <c r="H23" s="23"/>
       <c r="I23" s="38"/>
       <c r="J23" s="34"/>
     </row>
@@ -5316,52 +4251,22 @@
       <c r="B24" s="18"/>
       <c r="C24" s="19"/>
       <c r="D24" s="20"/>
-      <c r="E24" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="F24" s="22">
-        <v>99</v>
-      </c>
-      <c r="G24" s="49">
-        <v>12.6</v>
-      </c>
-      <c r="H24" s="23">
-        <f t="shared" si="1"/>
-        <v>1247.3999999999999</v>
-      </c>
+      <c r="E24" s="21"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="49"/>
+      <c r="H24" s="23"/>
       <c r="I24" s="40"/>
-      <c r="J24" s="34">
-        <f>SUM(F23:F24)-B23</f>
-        <v>-4</v>
-      </c>
+      <c r="J24" s="34"/>
     </row>
     <row r="25" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="B25" s="18">
-        <v>244</v>
-      </c>
-      <c r="C25" s="19">
-        <v>12</v>
-      </c>
-      <c r="D25" s="20">
-        <f t="shared" si="0"/>
-        <v>2928</v>
-      </c>
-      <c r="E25" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="F25" s="22">
-        <v>1</v>
-      </c>
-      <c r="G25" s="49">
-        <v>12</v>
-      </c>
-      <c r="H25" s="23">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
+      <c r="A25" s="21"/>
+      <c r="B25" s="18"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="49"/>
+      <c r="H25" s="23"/>
       <c r="I25" s="38"/>
       <c r="J25" s="34"/>
     </row>
@@ -5370,19 +4275,10 @@
       <c r="B26" s="18"/>
       <c r="C26" s="19"/>
       <c r="D26" s="20"/>
-      <c r="E26" s="21" t="s">
-        <v>64</v>
-      </c>
-      <c r="F26" s="22">
-        <v>1</v>
-      </c>
-      <c r="G26" s="49">
-        <v>12</v>
-      </c>
-      <c r="H26" s="23">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
+      <c r="E26" s="21"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="49"/>
+      <c r="H26" s="23"/>
       <c r="I26" s="38"/>
       <c r="J26" s="34"/>
     </row>
@@ -5391,19 +4287,10 @@
       <c r="B27" s="18"/>
       <c r="C27" s="19"/>
       <c r="D27" s="20"/>
-      <c r="E27" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="F27" s="22">
-        <v>1</v>
-      </c>
-      <c r="G27" s="49">
-        <v>12</v>
-      </c>
-      <c r="H27" s="23">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
+      <c r="E27" s="21"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="49"/>
+      <c r="H27" s="23"/>
       <c r="I27" s="38"/>
       <c r="J27" s="34"/>
     </row>
@@ -5412,19 +4299,10 @@
       <c r="B28" s="18"/>
       <c r="C28" s="19"/>
       <c r="D28" s="20"/>
-      <c r="E28" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="F28" s="22">
-        <v>9</v>
-      </c>
-      <c r="G28" s="49">
-        <v>12</v>
-      </c>
-      <c r="H28" s="23">
-        <f t="shared" si="1"/>
-        <v>108</v>
-      </c>
+      <c r="E28" s="21"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="49"/>
+      <c r="H28" s="23"/>
       <c r="I28" s="38"/>
       <c r="J28" s="34"/>
     </row>
@@ -5433,19 +4311,10 @@
       <c r="B29" s="18"/>
       <c r="C29" s="19"/>
       <c r="D29" s="20"/>
-      <c r="E29" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="F29" s="22">
-        <v>1</v>
-      </c>
-      <c r="G29" s="49">
-        <v>12</v>
-      </c>
-      <c r="H29" s="23">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
+      <c r="E29" s="21"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="49"/>
+      <c r="H29" s="23"/>
       <c r="I29" s="38"/>
       <c r="J29" s="34"/>
     </row>
@@ -5454,19 +4323,10 @@
       <c r="B30" s="18"/>
       <c r="C30" s="19"/>
       <c r="D30" s="20"/>
-      <c r="E30" s="21" t="s">
-        <v>71</v>
-      </c>
-      <c r="F30" s="22">
-        <v>6</v>
-      </c>
-      <c r="G30" s="49">
-        <v>12</v>
-      </c>
-      <c r="H30" s="23">
-        <f t="shared" si="1"/>
-        <v>72</v>
-      </c>
+      <c r="E30" s="21"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="49"/>
+      <c r="H30" s="23"/>
       <c r="I30" s="39"/>
       <c r="J30" s="34"/>
     </row>
@@ -5475,19 +4335,10 @@
       <c r="B31" s="18"/>
       <c r="C31" s="19"/>
       <c r="D31" s="20"/>
-      <c r="E31" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="F31" s="22">
-        <v>1</v>
-      </c>
-      <c r="G31" s="49">
-        <v>12</v>
-      </c>
-      <c r="H31" s="23">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
+      <c r="E31" s="21"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="49"/>
+      <c r="H31" s="23"/>
       <c r="I31" s="38"/>
       <c r="J31" s="34"/>
     </row>
@@ -5496,19 +4347,10 @@
       <c r="B32" s="18"/>
       <c r="C32" s="19"/>
       <c r="D32" s="20"/>
-      <c r="E32" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="F32" s="22">
-        <v>1</v>
-      </c>
-      <c r="G32" s="49">
-        <v>12</v>
-      </c>
-      <c r="H32" s="23">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
+      <c r="E32" s="21"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="49"/>
+      <c r="H32" s="23"/>
       <c r="I32" s="38"/>
       <c r="J32" s="34"/>
     </row>
@@ -5517,19 +4359,10 @@
       <c r="B33" s="18"/>
       <c r="C33" s="19"/>
       <c r="D33" s="20"/>
-      <c r="E33" s="21" t="s">
-        <v>76</v>
-      </c>
-      <c r="F33" s="22">
-        <v>227</v>
-      </c>
-      <c r="G33" s="49">
-        <v>12</v>
-      </c>
-      <c r="H33" s="23">
-        <f t="shared" si="1"/>
-        <v>2724</v>
-      </c>
+      <c r="E33" s="21"/>
+      <c r="F33" s="22"/>
+      <c r="G33" s="49"/>
+      <c r="H33" s="23"/>
       <c r="I33" s="38"/>
       <c r="J33" s="34"/>
     </row>
@@ -5538,19 +4371,10 @@
       <c r="B34" s="18"/>
       <c r="C34" s="19"/>
       <c r="D34" s="20"/>
-      <c r="E34" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="F34" s="22">
-        <v>2</v>
-      </c>
-      <c r="G34" s="49">
-        <v>12</v>
-      </c>
-      <c r="H34" s="23">
-        <f t="shared" si="1"/>
-        <v>24</v>
-      </c>
+      <c r="E34" s="21"/>
+      <c r="F34" s="22"/>
+      <c r="G34" s="49"/>
+      <c r="H34" s="23"/>
       <c r="I34" s="38"/>
       <c r="J34" s="34"/>
     </row>
@@ -5559,52 +4383,22 @@
       <c r="B35" s="18"/>
       <c r="C35" s="19"/>
       <c r="D35" s="20"/>
-      <c r="E35" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="F35" s="22">
-        <v>4</v>
-      </c>
-      <c r="G35" s="49">
-        <v>12</v>
-      </c>
-      <c r="H35" s="23">
-        <f t="shared" si="1"/>
-        <v>48</v>
-      </c>
+      <c r="E35" s="21"/>
+      <c r="F35" s="22"/>
+      <c r="G35" s="49"/>
+      <c r="H35" s="23"/>
       <c r="I35" s="38"/>
-      <c r="J35" s="34">
-        <f>SUM(F25:F35)-B25</f>
-        <v>10</v>
-      </c>
+      <c r="J35" s="34"/>
     </row>
     <row r="36" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="B36" s="18">
-        <v>4731</v>
-      </c>
-      <c r="C36" s="19">
-        <v>11.2</v>
-      </c>
-      <c r="D36" s="20">
-        <f t="shared" si="0"/>
-        <v>52987.199999999997</v>
-      </c>
-      <c r="E36" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="F36" s="22">
-        <v>2762</v>
-      </c>
-      <c r="G36" s="49">
-        <v>11.2</v>
-      </c>
-      <c r="H36" s="23">
-        <f>F36*G36</f>
-        <v>30934.399999999998</v>
-      </c>
+      <c r="A36" s="21"/>
+      <c r="B36" s="18"/>
+      <c r="C36" s="19"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="21"/>
+      <c r="F36" s="22"/>
+      <c r="G36" s="49"/>
+      <c r="H36" s="23"/>
       <c r="I36" s="38"/>
       <c r="J36" s="34"/>
       <c r="K36" s="45"/>
@@ -5614,126 +4408,49 @@
       <c r="B37" s="18"/>
       <c r="C37" s="19"/>
       <c r="D37" s="20"/>
-      <c r="E37" s="63" t="s">
-        <v>52</v>
-      </c>
-      <c r="F37" s="22">
-        <v>1779</v>
-      </c>
-      <c r="G37" s="49">
-        <v>6</v>
-      </c>
-      <c r="H37" s="23">
-        <f t="shared" ref="H37:H38" si="2">F37*G37</f>
-        <v>10674</v>
-      </c>
-      <c r="I37" s="64" t="s">
-        <v>128</v>
-      </c>
-      <c r="J37" s="34">
-        <f>F36+F37-B36</f>
-        <v>-190</v>
-      </c>
+      <c r="E37" s="63"/>
+      <c r="F37" s="22"/>
+      <c r="G37" s="49"/>
+      <c r="H37" s="23"/>
+      <c r="I37" s="64"/>
+      <c r="J37" s="34"/>
       <c r="K37" s="45"/>
     </row>
     <row r="38" spans="1:11" s="4" customFormat="1" ht="63" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="B38" s="18">
-        <v>1609</v>
-      </c>
-      <c r="C38" s="19">
-        <v>6</v>
-      </c>
-      <c r="D38" s="20">
-        <f>B38*C38</f>
-        <v>9654</v>
-      </c>
-      <c r="E38" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="F38" s="22">
-        <v>1609</v>
-      </c>
-      <c r="G38" s="49">
-        <v>6</v>
-      </c>
-      <c r="H38" s="23">
-        <f t="shared" si="2"/>
-        <v>9654</v>
-      </c>
-      <c r="I38" s="64" t="s">
-        <v>128</v>
-      </c>
-      <c r="J38" s="34">
-        <f>F38-B38</f>
-        <v>0</v>
-      </c>
+      <c r="A38" s="21"/>
+      <c r="B38" s="18"/>
+      <c r="C38" s="19"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="21"/>
+      <c r="F38" s="22"/>
+      <c r="G38" s="49"/>
+      <c r="H38" s="23"/>
+      <c r="I38" s="64"/>
+      <c r="J38" s="34"/>
       <c r="K38" s="47"/>
     </row>
     <row r="39" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A39" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="B39" s="18">
-        <v>481</v>
-      </c>
-      <c r="C39" s="19">
-        <v>0.1</v>
-      </c>
-      <c r="D39" s="20">
-        <f t="shared" si="0"/>
-        <v>48.1</v>
-      </c>
-      <c r="E39" s="21" t="str">
-        <f>A39</f>
-        <v>Ni Powder</v>
-      </c>
-      <c r="F39" s="22">
-        <v>478</v>
-      </c>
-      <c r="G39" s="49">
-        <v>0.1</v>
-      </c>
-      <c r="H39" s="23">
-        <f>F39*G39</f>
-        <v>47.800000000000004</v>
-      </c>
+      <c r="A39" s="21"/>
+      <c r="B39" s="18"/>
+      <c r="C39" s="19"/>
+      <c r="D39" s="20"/>
+      <c r="E39" s="21"/>
+      <c r="F39" s="22"/>
+      <c r="G39" s="49"/>
+      <c r="H39" s="23"/>
       <c r="I39" s="64"/>
-      <c r="J39" s="34">
-        <f>F39-B39</f>
-        <v>-3</v>
-      </c>
+      <c r="J39" s="34"/>
       <c r="K39" s="47"/>
     </row>
     <row r="40" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A40" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="B40" s="18">
-        <v>295</v>
-      </c>
-      <c r="C40" s="19">
-        <v>13.6</v>
-      </c>
-      <c r="D40" s="20">
-        <f t="shared" si="0"/>
-        <v>4012</v>
-      </c>
-      <c r="E40" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="F40" s="22">
-        <v>146</v>
-      </c>
-      <c r="G40" s="49">
-        <v>13.6</v>
-      </c>
-      <c r="H40" s="23">
-        <f t="shared" ref="H40:H52" si="3">F40*G40</f>
-        <v>1985.6</v>
-      </c>
+      <c r="A40" s="21"/>
+      <c r="B40" s="18"/>
+      <c r="C40" s="19"/>
+      <c r="D40" s="20"/>
+      <c r="E40" s="21"/>
+      <c r="F40" s="22"/>
+      <c r="G40" s="49"/>
+      <c r="H40" s="23"/>
       <c r="I40" s="64"/>
       <c r="J40" s="34"/>
       <c r="K40" s="1"/>
@@ -5743,19 +4460,10 @@
       <c r="B41" s="18"/>
       <c r="C41" s="19"/>
       <c r="D41" s="20"/>
-      <c r="E41" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="F41" s="22">
-        <v>35</v>
-      </c>
-      <c r="G41" s="49">
-        <v>14.2</v>
-      </c>
-      <c r="H41" s="23">
-        <f t="shared" si="3"/>
-        <v>497</v>
-      </c>
+      <c r="E41" s="21"/>
+      <c r="F41" s="22"/>
+      <c r="G41" s="49"/>
+      <c r="H41" s="23"/>
       <c r="I41" s="64"/>
       <c r="J41" s="34"/>
       <c r="K41" s="1"/>
@@ -5765,19 +4473,10 @@
       <c r="B42" s="18"/>
       <c r="C42" s="19"/>
       <c r="D42" s="20"/>
-      <c r="E42" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="F42" s="22">
-        <v>1</v>
-      </c>
-      <c r="G42" s="49">
-        <v>10</v>
-      </c>
-      <c r="H42" s="23">
-        <f t="shared" si="3"/>
-        <v>10</v>
-      </c>
+      <c r="E42" s="21"/>
+      <c r="F42" s="22"/>
+      <c r="G42" s="49"/>
+      <c r="H42" s="23"/>
       <c r="I42" s="64"/>
       <c r="J42" s="34"/>
       <c r="K42" s="1"/>
@@ -5787,19 +4486,10 @@
       <c r="B43" s="18"/>
       <c r="C43" s="19"/>
       <c r="D43" s="20"/>
-      <c r="E43" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="F43" s="22">
-        <v>1</v>
-      </c>
-      <c r="G43" s="49">
-        <v>10</v>
-      </c>
-      <c r="H43" s="23">
-        <f t="shared" si="3"/>
-        <v>10</v>
-      </c>
+      <c r="E43" s="21"/>
+      <c r="F43" s="22"/>
+      <c r="G43" s="49"/>
+      <c r="H43" s="23"/>
       <c r="I43" s="64"/>
       <c r="J43" s="34"/>
       <c r="K43" s="1"/>
@@ -5809,19 +4499,10 @@
       <c r="B44" s="18"/>
       <c r="C44" s="19"/>
       <c r="D44" s="20"/>
-      <c r="E44" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="F44" s="22">
-        <v>1</v>
-      </c>
-      <c r="G44" s="49">
-        <v>10</v>
-      </c>
-      <c r="H44" s="23">
-        <f t="shared" si="3"/>
-        <v>10</v>
-      </c>
+      <c r="E44" s="21"/>
+      <c r="F44" s="22"/>
+      <c r="G44" s="49"/>
+      <c r="H44" s="23"/>
       <c r="I44" s="64"/>
       <c r="J44" s="34"/>
       <c r="K44" s="1"/>
@@ -5831,22 +4512,11 @@
       <c r="B45" s="18"/>
       <c r="C45" s="19"/>
       <c r="D45" s="20"/>
-      <c r="E45" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="F45" s="22">
-        <v>16</v>
-      </c>
-      <c r="G45" s="49">
-        <v>6</v>
-      </c>
-      <c r="H45" s="23">
-        <f t="shared" si="3"/>
-        <v>96</v>
-      </c>
-      <c r="I45" s="64" t="s">
-        <v>129</v>
-      </c>
+      <c r="E45" s="21"/>
+      <c r="F45" s="22"/>
+      <c r="G45" s="49"/>
+      <c r="H45" s="23"/>
+      <c r="I45" s="64"/>
       <c r="J45" s="34"/>
       <c r="K45" s="1"/>
     </row>
@@ -5855,22 +4525,11 @@
       <c r="B46" s="18"/>
       <c r="C46" s="19"/>
       <c r="D46" s="20"/>
-      <c r="E46" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="F46" s="22">
-        <v>12</v>
-      </c>
-      <c r="G46" s="49">
-        <v>3</v>
-      </c>
-      <c r="H46" s="23">
-        <f t="shared" si="3"/>
-        <v>36</v>
-      </c>
-      <c r="I46" s="65" t="s">
-        <v>122</v>
-      </c>
+      <c r="E46" s="21"/>
+      <c r="F46" s="22"/>
+      <c r="G46" s="49"/>
+      <c r="H46" s="23"/>
+      <c r="I46" s="65"/>
       <c r="J46" s="34"/>
       <c r="K46" s="1"/>
     </row>
@@ -5879,22 +4538,11 @@
       <c r="B47" s="18"/>
       <c r="C47" s="19"/>
       <c r="D47" s="20"/>
-      <c r="E47" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="F47" s="22">
-        <v>7</v>
-      </c>
-      <c r="G47" s="49">
-        <v>3</v>
-      </c>
-      <c r="H47" s="23">
-        <f t="shared" si="3"/>
-        <v>21</v>
-      </c>
-      <c r="I47" s="64" t="s">
-        <v>123</v>
-      </c>
+      <c r="E47" s="21"/>
+      <c r="F47" s="22"/>
+      <c r="G47" s="49"/>
+      <c r="H47" s="23"/>
+      <c r="I47" s="64"/>
       <c r="J47" s="34"/>
       <c r="K47" s="1"/>
     </row>
@@ -5903,22 +4551,11 @@
       <c r="B48" s="18"/>
       <c r="C48" s="19"/>
       <c r="D48" s="20"/>
-      <c r="E48" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="F48" s="22">
-        <v>25</v>
-      </c>
-      <c r="G48" s="49">
-        <v>3</v>
-      </c>
-      <c r="H48" s="23">
-        <f t="shared" si="3"/>
-        <v>75</v>
-      </c>
-      <c r="I48" s="64" t="s">
-        <v>124</v>
-      </c>
+      <c r="E48" s="21"/>
+      <c r="F48" s="22"/>
+      <c r="G48" s="49"/>
+      <c r="H48" s="23"/>
+      <c r="I48" s="64"/>
       <c r="J48" s="34"/>
       <c r="K48" s="1"/>
     </row>
@@ -5927,22 +4564,11 @@
       <c r="B49" s="18"/>
       <c r="C49" s="19"/>
       <c r="D49" s="20"/>
-      <c r="E49" s="21" t="s">
-        <v>88</v>
-      </c>
-      <c r="F49" s="22">
-        <v>18</v>
-      </c>
-      <c r="G49" s="49">
-        <v>1.5</v>
-      </c>
-      <c r="H49" s="23">
-        <f t="shared" si="3"/>
-        <v>27</v>
-      </c>
-      <c r="I49" s="64" t="s">
-        <v>125</v>
-      </c>
+      <c r="E49" s="21"/>
+      <c r="F49" s="22"/>
+      <c r="G49" s="49"/>
+      <c r="H49" s="23"/>
+      <c r="I49" s="64"/>
       <c r="J49" s="34"/>
       <c r="K49" s="1"/>
     </row>
@@ -5951,22 +4577,11 @@
       <c r="B50" s="18"/>
       <c r="C50" s="19"/>
       <c r="D50" s="20"/>
-      <c r="E50" s="21" t="s">
-        <v>88</v>
-      </c>
-      <c r="F50" s="22">
-        <v>5</v>
-      </c>
-      <c r="G50" s="49">
-        <v>1.5</v>
-      </c>
-      <c r="H50" s="23">
-        <f t="shared" si="3"/>
-        <v>7.5</v>
-      </c>
-      <c r="I50" s="64" t="s">
-        <v>126</v>
-      </c>
+      <c r="E50" s="21"/>
+      <c r="F50" s="22"/>
+      <c r="G50" s="49"/>
+      <c r="H50" s="23"/>
+      <c r="I50" s="64"/>
       <c r="J50" s="34"/>
       <c r="K50" s="1"/>
     </row>
@@ -5975,19 +4590,10 @@
       <c r="B51" s="18"/>
       <c r="C51" s="19"/>
       <c r="D51" s="20"/>
-      <c r="E51" s="21" t="s">
-        <v>91</v>
-      </c>
-      <c r="F51" s="22">
-        <v>7</v>
-      </c>
-      <c r="G51" s="49">
-        <v>1.2</v>
-      </c>
-      <c r="H51" s="23">
-        <f t="shared" si="3"/>
-        <v>8.4</v>
-      </c>
+      <c r="E51" s="21"/>
+      <c r="F51" s="22"/>
+      <c r="G51" s="49"/>
+      <c r="H51" s="23"/>
       <c r="I51" s="64"/>
       <c r="J51" s="34"/>
       <c r="K51" s="1"/>
@@ -5997,53 +4603,23 @@
       <c r="B52" s="18"/>
       <c r="C52" s="19"/>
       <c r="D52" s="20"/>
-      <c r="E52" s="21" t="s">
-        <v>92</v>
-      </c>
-      <c r="F52" s="22">
-        <v>8</v>
-      </c>
-      <c r="G52" s="49">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="H52" s="23">
-        <f t="shared" si="3"/>
-        <v>17.600000000000001</v>
-      </c>
+      <c r="E52" s="21"/>
+      <c r="F52" s="22"/>
+      <c r="G52" s="49"/>
+      <c r="H52" s="23"/>
       <c r="I52" s="64"/>
-      <c r="J52" s="34">
-        <f>SUM(F40:F52)-B40</f>
-        <v>-13</v>
-      </c>
+      <c r="J52" s="34"/>
       <c r="K52" s="1"/>
     </row>
     <row r="53" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A53" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="B53" s="18">
-        <v>2532</v>
-      </c>
-      <c r="C53" s="19">
-        <v>13.1</v>
-      </c>
-      <c r="D53" s="20">
-        <f t="shared" si="0"/>
-        <v>33169.199999999997</v>
-      </c>
-      <c r="E53" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="F53" s="22">
-        <v>2469</v>
-      </c>
-      <c r="G53" s="49">
-        <v>13.1</v>
-      </c>
-      <c r="H53" s="23">
-        <f t="shared" si="1"/>
-        <v>32343.899999999998</v>
-      </c>
+      <c r="A53" s="21"/>
+      <c r="B53" s="18"/>
+      <c r="C53" s="19"/>
+      <c r="D53" s="20"/>
+      <c r="E53" s="21"/>
+      <c r="F53" s="22"/>
+      <c r="G53" s="49"/>
+      <c r="H53" s="23"/>
       <c r="I53" s="64"/>
       <c r="J53" s="34"/>
       <c r="K53" s="1"/>
@@ -6053,51 +4629,23 @@
       <c r="B54" s="18"/>
       <c r="C54" s="19"/>
       <c r="D54" s="20"/>
-      <c r="E54" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="F54" s="22">
-        <v>10</v>
-      </c>
+      <c r="E54" s="21"/>
+      <c r="F54" s="22"/>
       <c r="G54" s="49"/>
-      <c r="H54" s="23">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="H54" s="23"/>
       <c r="I54" s="64"/>
-      <c r="J54" s="34">
-        <f>SUM(F53:F54)-B53</f>
-        <v>-53</v>
-      </c>
+      <c r="J54" s="34"/>
       <c r="K54" s="1"/>
     </row>
     <row r="55" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A55" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="B55" s="18">
-        <v>287</v>
-      </c>
-      <c r="C55" s="19">
-        <v>14.2</v>
-      </c>
-      <c r="D55" s="20">
-        <f t="shared" si="0"/>
-        <v>4075.3999999999996</v>
-      </c>
-      <c r="E55" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="F55" s="22">
-        <v>270</v>
-      </c>
-      <c r="G55" s="49">
-        <v>14.2</v>
-      </c>
-      <c r="H55" s="23">
-        <f t="shared" si="1"/>
-        <v>3834</v>
-      </c>
+      <c r="A55" s="21"/>
+      <c r="B55" s="18"/>
+      <c r="C55" s="19"/>
+      <c r="D55" s="20"/>
+      <c r="E55" s="21"/>
+      <c r="F55" s="22"/>
+      <c r="G55" s="49"/>
+      <c r="H55" s="23"/>
       <c r="I55" s="64"/>
       <c r="J55" s="34"/>
       <c r="K55" s="46"/>
@@ -6107,19 +4655,10 @@
       <c r="B56" s="18"/>
       <c r="C56" s="19"/>
       <c r="D56" s="20"/>
-      <c r="E56" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="F56" s="22">
-        <v>40</v>
-      </c>
-      <c r="G56" s="49">
-        <v>13.6</v>
-      </c>
-      <c r="H56" s="23">
-        <f t="shared" si="1"/>
-        <v>544</v>
-      </c>
+      <c r="E56" s="21"/>
+      <c r="F56" s="22"/>
+      <c r="G56" s="49"/>
+      <c r="H56" s="23"/>
       <c r="I56" s="64"/>
       <c r="J56" s="34"/>
       <c r="K56" s="46"/>
@@ -6129,56 +4668,23 @@
       <c r="B57" s="18"/>
       <c r="C57" s="19"/>
       <c r="D57" s="20"/>
-      <c r="E57" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="F57" s="22">
-        <v>52</v>
-      </c>
-      <c r="G57" s="49">
-        <v>6</v>
-      </c>
-      <c r="H57" s="23">
-        <f t="shared" si="1"/>
-        <v>312</v>
-      </c>
-      <c r="I57" s="64" t="s">
-        <v>127</v>
-      </c>
-      <c r="J57" s="34">
-        <f>SUM(F55:F57)-B55</f>
-        <v>75</v>
-      </c>
+      <c r="E57" s="21"/>
+      <c r="F57" s="22"/>
+      <c r="G57" s="49"/>
+      <c r="H57" s="23"/>
+      <c r="I57" s="64"/>
+      <c r="J57" s="34"/>
       <c r="K57" s="46"/>
     </row>
     <row r="58" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A58" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="B58" s="18">
-        <v>1171</v>
-      </c>
-      <c r="C58" s="19">
-        <v>13.6</v>
-      </c>
-      <c r="D58" s="20">
-        <f t="shared" si="0"/>
-        <v>15925.6</v>
-      </c>
-      <c r="E58" s="21" t="str">
-        <f>A58</f>
-        <v>625 Solid</v>
-      </c>
-      <c r="F58" s="22">
-        <v>1144</v>
-      </c>
-      <c r="G58" s="49">
-        <v>13.6</v>
-      </c>
-      <c r="H58" s="23">
-        <f t="shared" si="1"/>
-        <v>15558.4</v>
-      </c>
+      <c r="A58" s="21"/>
+      <c r="B58" s="18"/>
+      <c r="C58" s="19"/>
+      <c r="D58" s="20"/>
+      <c r="E58" s="21"/>
+      <c r="F58" s="22"/>
+      <c r="G58" s="49"/>
+      <c r="H58" s="23"/>
       <c r="I58" s="64"/>
       <c r="J58" s="34"/>
       <c r="K58" s="1"/>
@@ -6188,120 +4694,47 @@
       <c r="B59" s="18"/>
       <c r="C59" s="19"/>
       <c r="D59" s="20"/>
-      <c r="E59" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="F59" s="22">
-        <v>18</v>
-      </c>
-      <c r="G59" s="49">
-        <v>12</v>
-      </c>
-      <c r="H59" s="23">
-        <f t="shared" si="1"/>
-        <v>216</v>
-      </c>
+      <c r="E59" s="21"/>
+      <c r="F59" s="22"/>
+      <c r="G59" s="49"/>
+      <c r="H59" s="23"/>
       <c r="I59" s="64"/>
-      <c r="J59" s="34">
-        <f>F58+F59-B58</f>
-        <v>-9</v>
-      </c>
+      <c r="J59" s="34"/>
       <c r="K59" s="1"/>
     </row>
     <row r="60" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A60" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="B60" s="18">
-        <v>95</v>
-      </c>
-      <c r="C60" s="19">
-        <v>12</v>
-      </c>
-      <c r="D60" s="20">
-        <f t="shared" si="0"/>
-        <v>1140</v>
-      </c>
-      <c r="E60" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="F60" s="22">
-        <v>92</v>
-      </c>
-      <c r="G60" s="49">
-        <v>12</v>
-      </c>
-      <c r="H60" s="23">
-        <f t="shared" si="1"/>
-        <v>1104</v>
-      </c>
+      <c r="A60" s="21"/>
+      <c r="B60" s="18"/>
+      <c r="C60" s="19"/>
+      <c r="D60" s="20"/>
+      <c r="E60" s="21"/>
+      <c r="F60" s="22"/>
+      <c r="G60" s="49"/>
+      <c r="H60" s="23"/>
       <c r="I60" s="64"/>
-      <c r="J60" s="34">
-        <f>F60-B60</f>
-        <v>-3</v>
-      </c>
+      <c r="J60" s="34"/>
     </row>
     <row r="61" spans="1:11" s="4" customFormat="1" ht="35.15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A61" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="B61" s="18">
-        <v>496</v>
-      </c>
-      <c r="C61" s="19">
-        <v>9</v>
-      </c>
-      <c r="D61" s="20">
-        <f t="shared" si="0"/>
-        <v>4464</v>
-      </c>
-      <c r="E61" s="21" t="str">
-        <f>A61</f>
-        <v>713 Mix Blade</v>
-      </c>
-      <c r="F61" s="22">
-        <v>502</v>
-      </c>
-      <c r="G61" s="49">
-        <v>9</v>
-      </c>
-      <c r="H61" s="23">
-        <f t="shared" si="1"/>
-        <v>4518</v>
-      </c>
+      <c r="A61" s="21"/>
+      <c r="B61" s="18"/>
+      <c r="C61" s="19"/>
+      <c r="D61" s="20"/>
+      <c r="E61" s="21"/>
+      <c r="F61" s="22"/>
+      <c r="G61" s="49"/>
+      <c r="H61" s="23"/>
       <c r="I61" s="65"/>
-      <c r="J61" s="34">
-        <f>F61-B61</f>
-        <v>6</v>
-      </c>
+      <c r="J61" s="34"/>
     </row>
     <row r="62" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A62" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="B62" s="18">
-        <v>58</v>
-      </c>
-      <c r="C62" s="19">
-        <v>35</v>
-      </c>
-      <c r="D62" s="20">
-        <f t="shared" si="0"/>
-        <v>2030</v>
-      </c>
-      <c r="E62" s="21" t="s">
-        <v>63</v>
-      </c>
-      <c r="F62" s="22">
-        <v>7</v>
-      </c>
-      <c r="G62" s="49">
-        <v>10.5</v>
-      </c>
-      <c r="H62" s="23">
-        <f t="shared" si="1"/>
-        <v>73.5</v>
-      </c>
+      <c r="A62" s="21"/>
+      <c r="B62" s="18"/>
+      <c r="C62" s="19"/>
+      <c r="D62" s="20"/>
+      <c r="E62" s="21"/>
+      <c r="F62" s="22"/>
+      <c r="G62" s="49"/>
+      <c r="H62" s="23"/>
       <c r="I62" s="65"/>
       <c r="J62" s="34"/>
       <c r="K62" s="48"/>
@@ -6311,19 +4744,10 @@
       <c r="B63" s="18"/>
       <c r="C63" s="19"/>
       <c r="D63" s="20"/>
-      <c r="E63" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="F63" s="22">
-        <v>1</v>
-      </c>
-      <c r="G63" s="49">
-        <v>10.5</v>
-      </c>
-      <c r="H63" s="23">
-        <f t="shared" si="1"/>
-        <v>10.5</v>
-      </c>
+      <c r="E63" s="21"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="49"/>
+      <c r="H63" s="23"/>
       <c r="I63" s="65"/>
       <c r="J63" s="34"/>
       <c r="K63" s="48"/>
@@ -6333,19 +4757,10 @@
       <c r="B64" s="18"/>
       <c r="C64" s="19"/>
       <c r="D64" s="20"/>
-      <c r="E64" s="63" t="s">
-        <v>109</v>
-      </c>
-      <c r="F64" s="22">
-        <v>14</v>
-      </c>
-      <c r="G64" s="49">
-        <v>6</v>
-      </c>
-      <c r="H64" s="23">
-        <f t="shared" si="1"/>
-        <v>84</v>
-      </c>
+      <c r="E64" s="63"/>
+      <c r="F64" s="22"/>
+      <c r="G64" s="49"/>
+      <c r="H64" s="23"/>
       <c r="I64" s="65"/>
       <c r="J64" s="34"/>
       <c r="K64" s="48"/>
@@ -6355,19 +4770,10 @@
       <c r="B65" s="18"/>
       <c r="C65" s="19"/>
       <c r="D65" s="20"/>
-      <c r="E65" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="F65" s="22">
-        <v>14</v>
-      </c>
-      <c r="G65" s="49">
-        <v>35</v>
-      </c>
-      <c r="H65" s="23">
-        <f t="shared" si="1"/>
-        <v>490</v>
-      </c>
+      <c r="E65" s="21"/>
+      <c r="F65" s="22"/>
+      <c r="G65" s="49"/>
+      <c r="H65" s="23"/>
       <c r="I65" s="65"/>
       <c r="J65" s="34"/>
       <c r="K65" s="48"/>
@@ -6377,19 +4783,10 @@
       <c r="B66" s="18"/>
       <c r="C66" s="19"/>
       <c r="D66" s="20"/>
-      <c r="E66" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="F66" s="22">
-        <v>6</v>
-      </c>
-      <c r="G66" s="49">
-        <v>35</v>
-      </c>
-      <c r="H66" s="23">
-        <f t="shared" si="1"/>
-        <v>210</v>
-      </c>
+      <c r="E66" s="21"/>
+      <c r="F66" s="22"/>
+      <c r="G66" s="49"/>
+      <c r="H66" s="23"/>
       <c r="I66" s="65"/>
       <c r="J66" s="34"/>
       <c r="K66" s="48"/>
@@ -6399,19 +4796,10 @@
       <c r="B67" s="18"/>
       <c r="C67" s="19"/>
       <c r="D67" s="20"/>
-      <c r="E67" s="21" t="s">
-        <v>75</v>
-      </c>
-      <c r="F67" s="22">
-        <v>2</v>
-      </c>
-      <c r="G67" s="49">
-        <v>10.5</v>
-      </c>
-      <c r="H67" s="23">
-        <f t="shared" si="1"/>
-        <v>21</v>
-      </c>
+      <c r="E67" s="21"/>
+      <c r="F67" s="22"/>
+      <c r="G67" s="49"/>
+      <c r="H67" s="23"/>
       <c r="I67" s="65"/>
       <c r="J67" s="34"/>
       <c r="K67" s="48"/>
@@ -6421,19 +4809,10 @@
       <c r="B68" s="18"/>
       <c r="C68" s="19"/>
       <c r="D68" s="20"/>
-      <c r="E68" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="F68" s="22">
-        <v>1</v>
-      </c>
-      <c r="G68" s="49">
-        <v>10.5</v>
-      </c>
-      <c r="H68" s="23">
-        <f t="shared" si="1"/>
-        <v>10.5</v>
-      </c>
+      <c r="E68" s="21"/>
+      <c r="F68" s="22"/>
+      <c r="G68" s="49"/>
+      <c r="H68" s="23"/>
       <c r="I68" s="65"/>
       <c r="J68" s="34"/>
     </row>
@@ -6442,54 +4821,23 @@
       <c r="B69" s="18"/>
       <c r="C69" s="19"/>
       <c r="D69" s="20"/>
-      <c r="E69" s="21" t="s">
-        <v>79</v>
-      </c>
-      <c r="F69" s="22">
-        <v>11</v>
-      </c>
-      <c r="G69" s="49">
-        <v>10.5</v>
-      </c>
-      <c r="H69" s="23">
-        <f t="shared" si="1"/>
-        <v>115.5</v>
-      </c>
+      <c r="E69" s="21"/>
+      <c r="F69" s="22"/>
+      <c r="G69" s="49"/>
+      <c r="H69" s="23"/>
       <c r="I69" s="65"/>
-      <c r="J69" s="34">
-        <f>SUM(F62:F69)-B62</f>
-        <v>-2</v>
-      </c>
+      <c r="J69" s="34"/>
       <c r="K69" s="48"/>
     </row>
     <row r="70" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A70" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="B70" s="18">
-        <v>202</v>
-      </c>
-      <c r="C70" s="19">
-        <v>10.5</v>
-      </c>
-      <c r="D70" s="20">
-        <f t="shared" si="0"/>
-        <v>2121</v>
-      </c>
-      <c r="E70" s="21" t="str">
-        <f>A70</f>
-        <v>Rene77 Blade</v>
-      </c>
-      <c r="F70" s="22">
-        <v>133</v>
-      </c>
-      <c r="G70" s="49">
-        <v>10.5</v>
-      </c>
-      <c r="H70" s="23">
-        <f t="shared" si="1"/>
-        <v>1396.5</v>
-      </c>
+      <c r="A70" s="21"/>
+      <c r="B70" s="18"/>
+      <c r="C70" s="19"/>
+      <c r="D70" s="20"/>
+      <c r="E70" s="21"/>
+      <c r="F70" s="22"/>
+      <c r="G70" s="49"/>
+      <c r="H70" s="23"/>
       <c r="I70" s="65"/>
       <c r="J70" s="34"/>
       <c r="K70" s="1"/>
@@ -6499,124 +4847,48 @@
       <c r="B71" s="18"/>
       <c r="C71" s="19"/>
       <c r="D71" s="20"/>
-      <c r="E71" s="63" t="s">
-        <v>109</v>
-      </c>
-      <c r="F71" s="22">
-        <v>64</v>
-      </c>
-      <c r="G71" s="49">
-        <v>6</v>
-      </c>
-      <c r="H71" s="23">
-        <f t="shared" si="1"/>
-        <v>384</v>
-      </c>
-      <c r="I71" s="66" t="s">
-        <v>130</v>
-      </c>
-      <c r="J71" s="34">
-        <f>F70+F71-B70</f>
-        <v>-5</v>
-      </c>
+      <c r="E71" s="63"/>
+      <c r="F71" s="22"/>
+      <c r="G71" s="49"/>
+      <c r="H71" s="23"/>
+      <c r="I71" s="66"/>
+      <c r="J71" s="34"/>
       <c r="K71" s="1"/>
     </row>
     <row r="72" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A72" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="B72" s="18">
-        <v>1443</v>
-      </c>
-      <c r="C72" s="19">
-        <v>3.3</v>
-      </c>
-      <c r="D72" s="20">
-        <f t="shared" si="0"/>
-        <v>4761.8999999999996</v>
-      </c>
-      <c r="E72" s="21" t="str">
-        <f>A72</f>
-        <v>Wco with SKD</v>
-      </c>
-      <c r="F72" s="22">
-        <v>1456</v>
-      </c>
-      <c r="G72" s="49">
-        <v>3.3</v>
-      </c>
-      <c r="H72" s="23">
-        <f t="shared" si="1"/>
-        <v>4804.8</v>
-      </c>
+      <c r="A72" s="21"/>
+      <c r="B72" s="18"/>
+      <c r="C72" s="19"/>
+      <c r="D72" s="20"/>
+      <c r="E72" s="21"/>
+      <c r="F72" s="22"/>
+      <c r="G72" s="49"/>
+      <c r="H72" s="23"/>
       <c r="I72" s="67"/>
-      <c r="J72" s="34">
-        <f>F72-B72</f>
-        <v>13</v>
-      </c>
+      <c r="J72" s="34"/>
       <c r="K72" s="48"/>
     </row>
     <row r="73" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A73" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="B73" s="18">
-        <v>2609</v>
-      </c>
-      <c r="C73" s="19">
-        <v>5.2</v>
-      </c>
-      <c r="D73" s="20">
-        <f t="shared" si="0"/>
-        <v>13566.800000000001</v>
-      </c>
-      <c r="E73" s="21" t="str">
-        <f>A73</f>
-        <v>Ni-B Turning</v>
-      </c>
-      <c r="F73" s="22">
-        <v>2605</v>
-      </c>
-      <c r="G73" s="49">
-        <v>5.2</v>
-      </c>
-      <c r="H73" s="23">
-        <f t="shared" si="1"/>
-        <v>13546</v>
-      </c>
+      <c r="A73" s="21"/>
+      <c r="B73" s="18"/>
+      <c r="C73" s="19"/>
+      <c r="D73" s="20"/>
+      <c r="E73" s="21"/>
+      <c r="F73" s="22"/>
+      <c r="G73" s="49"/>
+      <c r="H73" s="23"/>
       <c r="I73" s="65"/>
-      <c r="J73" s="34">
-        <f>F73-B73</f>
-        <v>-4</v>
-      </c>
+      <c r="J73" s="34"/>
     </row>
     <row r="74" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A74" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="B74" s="18">
-        <v>212</v>
-      </c>
-      <c r="C74" s="19">
-        <v>13</v>
-      </c>
-      <c r="D74" s="20">
-        <f t="shared" si="0"/>
-        <v>2756</v>
-      </c>
-      <c r="E74" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="F74" s="22">
-        <v>150</v>
-      </c>
-      <c r="G74" s="49">
-        <v>13</v>
-      </c>
-      <c r="H74" s="23">
-        <f t="shared" si="1"/>
-        <v>1950</v>
-      </c>
+      <c r="A74" s="21"/>
+      <c r="B74" s="18"/>
+      <c r="C74" s="19"/>
+      <c r="D74" s="20"/>
+      <c r="E74" s="21"/>
+      <c r="F74" s="22"/>
+      <c r="G74" s="49"/>
+      <c r="H74" s="23"/>
       <c r="I74" s="65"/>
       <c r="J74" s="34"/>
     </row>
@@ -6625,90 +4897,52 @@
       <c r="B75" s="18"/>
       <c r="C75" s="19"/>
       <c r="D75" s="20"/>
-      <c r="E75" s="21" t="s">
-        <v>44</v>
-      </c>
-      <c r="F75" s="22">
-        <v>56</v>
-      </c>
-      <c r="G75" s="49">
-        <v>5.5</v>
-      </c>
-      <c r="H75" s="23">
-        <f t="shared" si="1"/>
-        <v>308</v>
-      </c>
-      <c r="I75" s="65" t="s">
-        <v>50</v>
-      </c>
-      <c r="J75" s="34">
-        <f>SUM(F74:F75)-B74</f>
-        <v>-6</v>
-      </c>
+      <c r="E75" s="21"/>
+      <c r="F75" s="22"/>
+      <c r="G75" s="49"/>
+      <c r="H75" s="23"/>
+      <c r="I75" s="65"/>
+      <c r="J75" s="34"/>
     </row>
     <row r="76" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A76" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="B76" s="18">
-        <v>35</v>
-      </c>
-      <c r="C76" s="19">
-        <v>2.6</v>
-      </c>
-      <c r="D76" s="20">
-        <f t="shared" si="0"/>
-        <v>91</v>
-      </c>
-      <c r="E76" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="F76" s="22">
-        <v>36</v>
-      </c>
-      <c r="G76" s="49">
-        <v>2.6</v>
-      </c>
-      <c r="H76" s="23">
-        <f t="shared" si="1"/>
-        <v>93.600000000000009</v>
-      </c>
+      <c r="A76" s="21"/>
+      <c r="B76" s="18"/>
+      <c r="C76" s="19"/>
+      <c r="D76" s="20"/>
+      <c r="E76" s="21"/>
+      <c r="F76" s="22"/>
+      <c r="G76" s="49"/>
+      <c r="H76" s="23"/>
       <c r="I76" s="65"/>
-      <c r="J76" s="34">
-        <f>F76-B76</f>
-        <v>1</v>
-      </c>
+      <c r="J76" s="34"/>
     </row>
     <row r="77" spans="1:11" ht="35.15" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="A77" s="24" t="s">
-        <v>12</v>
+      <c r="A77" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TOTAL</t>
+        </is>
       </c>
       <c r="B77" s="25">
-        <f>SUM(B13:B76)</f>
-        <v>31496</v>
+        <v>500</v>
       </c>
       <c r="C77" s="26"/>
       <c r="D77" s="27">
-        <f>SUM(D13:D76)</f>
-        <v>326577.60000000003</v>
-      </c>
-      <c r="E77" s="28" t="s">
-        <v>12</v>
+        <v>0</v>
+      </c>
+      <c r="E77" s="28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TOTAL</t>
+        </is>
       </c>
       <c r="F77" s="29">
-        <f>SUM(F13:F76)</f>
-        <v>30965</v>
+        <v>500</v>
       </c>
       <c r="G77" s="26"/>
       <c r="H77" s="26">
-        <f>SUM(H13:H76)</f>
-        <v>304287.99999999994</v>
+        <v>0</v>
       </c>
       <c r="I77" s="12"/>
-      <c r="J77" s="35">
-        <f>SUM(J13:J76)</f>
-        <v>-531</v>
-      </c>
+      <c r="J77" s="35"/>
     </row>
     <row r="78" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A78" s="4"/>
@@ -6720,41 +4954,49 @@
       <c r="G78" s="6"/>
       <c r="H78" s="6"/>
       <c r="I78" s="15"/>
+      <c r="J78"/>
     </row>
     <row r="80" spans="1:11" ht="35.15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="E80" s="85" t="s">
-        <v>3</v>
+      <c r="E80" s="85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Actual value</t>
+        </is>
       </c>
       <c r="F80" s="86"/>
       <c r="G80" s="86"/>
       <c r="H80" s="87">
-        <f>H77</f>
-        <v>304287.99999999994</v>
+        <v>0</v>
       </c>
       <c r="I80" s="88"/>
+      <c r="J80"/>
     </row>
     <row r="81" spans="1:11" ht="35.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="E81" s="68" t="s">
-        <v>14</v>
+      <c r="E81" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provisonal Payment ( 90% )</t>
+        </is>
       </c>
       <c r="F81" s="69"/>
       <c r="G81" s="69"/>
       <c r="H81" s="70">
-        <v>293919.84000000003</v>
+        <v>0</v>
       </c>
       <c r="I81" s="71"/>
+      <c r="J81"/>
     </row>
     <row r="82" spans="1:11" ht="35.15" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="E82" s="72" t="s">
-        <v>4</v>
+      <c r="E82" s="72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Balance</t>
+        </is>
       </c>
       <c r="F82" s="73"/>
       <c r="G82" s="73"/>
       <c r="H82" s="74">
-        <f>H80-H81</f>
-        <v>10368.159999999916</v>
+        <v>0</v>
       </c>
       <c r="I82" s="75"/>
+      <c r="J82"/>
     </row>
     <row r="83" spans="1:11" s="13" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I83" s="42"/>
@@ -6775,6 +5017,7 @@
       <c r="G84" s="17"/>
       <c r="H84" s="17"/>
       <c r="I84" s="43"/>
+      <c r="J84"/>
     </row>
     <row r="85" spans="1:11" ht="26.15" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="86" spans="1:11" ht="26.15" customHeight="1" x14ac:dyDescent="0.45"/>
@@ -6833,6 +5076,9 @@
     <row r="123" ht="26.15" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="124" ht="26.15" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="125" ht="26.15" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="79">
+      <c r="J79"/>
+    </row>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A2:D2"/>
@@ -6849,7 +5095,7 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="61" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait" r:id="rId1" fitToWidth="1"/>
   <rowBreaks count="3" manualBreakCount="3">
     <brk id="35" max="8" man="1"/>
     <brk id="61" max="8" man="1"/>

--- a/settlement-overseas-template.xlsx
+++ b/settlement-overseas-template.xlsx
@@ -17,8 +17,8 @@
     <sheet name="세틀" sheetId="10" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'검수원본'!$A$1:$J$115</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'세틀'!$A$1:$J$84</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">검수원본!$A$1:$I$115</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">세틀!$A$1:$I$84</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -2413,14 +2413,14 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:J156"/>
+  <dimension ref="A2:K156"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="5" width="16.08203125" style="1" customWidth="1"/>
     <col min="6" max="6" width="15.5" style="1" customWidth="1"/>
     <col min="7" max="8" width="16.08203125" style="1" customWidth="1"/>
     <col min="9" max="9" width="19.58203125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="4" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.58203125" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.58203125" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
@@ -2454,10 +2454,8 @@
       <c r="A5" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">donald</t>
-        </is>
+      <c r="B5" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
@@ -2466,40 +2464,46 @@
         <v>1</v>
       </c>
       <c r="G5" s="11">
-        <v>46245</v>
+        <v>46157</v>
       </c>
       <c r="I5" s="41"/>
     </row>
     <row r="6" spans="1:10" s="9" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
+      <c r="B6" s="8" t="s">
+        <v>15</v>
+      </c>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
       <c r="F6" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="8"/>
+      <c r="G6" s="8" t="s">
+        <v>28</v>
+      </c>
       <c r="I6" s="41"/>
     </row>
     <row r="7" spans="1:10" s="9" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
+      <c r="B7" s="8" t="s">
+        <v>16</v>
+      </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
       <c r="F7" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">s01234</t>
-        </is>
+      <c r="G7" s="8" t="s">
+        <v>29</v>
       </c>
       <c r="I7" s="41"/>
     </row>
     <row r="8" spans="1:10" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B8" s="1"/>
+      <c r="B8" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="F8" s="3"/>
     </row>
     <row r="9" spans="1:10" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.45">
@@ -2549,50 +2553,54 @@
       <c r="I12" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="J12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">사진</t>
-        </is>
-      </c>
     </row>
     <row r="13" spans="1:10" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">718 solids</t>
-        </is>
+      <c r="A13" s="21" t="s">
+        <v>30</v>
       </c>
       <c r="B13" s="18">
-        <v>500</v>
-      </c>
-      <c r="C13" s="19"/>
+        <v>10934</v>
+      </c>
+      <c r="C13" s="19">
+        <v>12</v>
+      </c>
       <c r="D13" s="20">
-        <v>0</v>
-      </c>
-      <c r="E13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NI · IN 718 · VS</t>
-        </is>
+        <f t="shared" ref="D13:D107" si="0">B13*C13</f>
+        <v>131208</v>
+      </c>
+      <c r="E13" s="21" t="s">
+        <v>30</v>
       </c>
       <c r="F13" s="22">
-        <v>500</v>
+        <v>10472</v>
       </c>
       <c r="G13" s="49"/>
       <c r="H13" s="23">
+        <f t="shared" ref="H13:H107" si="1">F13*G13</f>
         <v>0</v>
       </c>
       <c r="I13" s="38"/>
-      <c r="J13" s="38"/>
+      <c r="J13" s="34"/>
     </row>
     <row r="14" spans="1:10" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="21"/>
       <c r="B14" s="18"/>
       <c r="C14" s="19"/>
       <c r="D14" s="20"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="22"/>
+      <c r="E14" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="F14" s="22">
+        <v>107</v>
+      </c>
       <c r="G14" s="49"/>
-      <c r="H14" s="23"/>
-      <c r="I14" s="38"/>
+      <c r="H14" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I14" s="38" t="s">
+        <v>45</v>
+      </c>
       <c r="J14" s="34"/>
     </row>
     <row r="15" spans="1:10" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
@@ -2600,10 +2608,17 @@
       <c r="B15" s="18"/>
       <c r="C15" s="19"/>
       <c r="D15" s="20"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="22"/>
+      <c r="E15" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="F15" s="22">
+        <v>34</v>
+      </c>
       <c r="G15" s="49"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="I15" s="38"/>
       <c r="J15" s="34"/>
     </row>
@@ -2612,10 +2627,17 @@
       <c r="B16" s="18"/>
       <c r="C16" s="19"/>
       <c r="D16" s="20"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="22"/>
+      <c r="E16" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="F16" s="22">
+        <v>12</v>
+      </c>
       <c r="G16" s="49"/>
-      <c r="H16" s="23"/>
+      <c r="H16" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="I16" s="38"/>
       <c r="J16" s="34"/>
     </row>
@@ -2624,10 +2646,17 @@
       <c r="B17" s="18"/>
       <c r="C17" s="19"/>
       <c r="D17" s="20"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="22"/>
+      <c r="E17" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="F17" s="22">
+        <v>29</v>
+      </c>
       <c r="G17" s="49"/>
-      <c r="H17" s="23"/>
+      <c r="H17" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="I17" s="38"/>
       <c r="J17" s="34"/>
     </row>
@@ -2636,22 +2665,48 @@
       <c r="B18" s="18"/>
       <c r="C18" s="19"/>
       <c r="D18" s="20"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="22"/>
+      <c r="E18" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="F18" s="22">
+        <v>2</v>
+      </c>
       <c r="G18" s="49"/>
-      <c r="H18" s="23"/>
+      <c r="H18" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="I18" s="38"/>
-      <c r="J18" s="34"/>
+      <c r="J18" s="34">
+        <f>SUM(F13:F18)-B13</f>
+        <v>-278</v>
+      </c>
     </row>
     <row r="19" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="21"/>
-      <c r="B19" s="18"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="21"/>
-      <c r="F19" s="22"/>
+      <c r="A19" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="18">
+        <v>1551</v>
+      </c>
+      <c r="C19" s="19">
+        <v>12.6</v>
+      </c>
+      <c r="D19" s="20">
+        <f t="shared" si="0"/>
+        <v>19542.599999999999</v>
+      </c>
+      <c r="E19" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="F19" s="22">
+        <v>367</v>
+      </c>
       <c r="G19" s="49"/>
-      <c r="H19" s="23"/>
+      <c r="H19" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="I19" s="44"/>
       <c r="J19" s="34"/>
       <c r="K19" s="37"/>
@@ -2661,11 +2716,20 @@
       <c r="B20" s="18"/>
       <c r="C20" s="19"/>
       <c r="D20" s="20"/>
-      <c r="E20" s="21"/>
-      <c r="F20" s="22"/>
+      <c r="E20" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="F20" s="22">
+        <v>530</v>
+      </c>
       <c r="G20" s="49"/>
-      <c r="H20" s="23"/>
-      <c r="I20" s="50"/>
+      <c r="H20" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I20" s="50" t="s">
+        <v>53</v>
+      </c>
       <c r="J20" s="34"/>
       <c r="K20" s="37"/>
     </row>
@@ -2674,11 +2738,20 @@
       <c r="B21" s="18"/>
       <c r="C21" s="19"/>
       <c r="D21" s="20"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="22"/>
+      <c r="E21" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="F21" s="22">
+        <v>334</v>
+      </c>
       <c r="G21" s="49"/>
-      <c r="H21" s="23"/>
-      <c r="I21" s="50"/>
+      <c r="H21" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I21" s="50" t="s">
+        <v>55</v>
+      </c>
       <c r="J21" s="34"/>
       <c r="K21" s="37"/>
     </row>
@@ -2687,11 +2760,20 @@
       <c r="B22" s="18"/>
       <c r="C22" s="19"/>
       <c r="D22" s="20"/>
-      <c r="E22" s="21"/>
-      <c r="F22" s="22"/>
+      <c r="E22" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="F22" s="22">
+        <v>103</v>
+      </c>
       <c r="G22" s="49"/>
-      <c r="H22" s="23"/>
-      <c r="I22" s="50"/>
+      <c r="H22" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I22" s="50" t="s">
+        <v>56</v>
+      </c>
       <c r="J22" s="34"/>
       <c r="K22" s="37"/>
     </row>
@@ -2700,11 +2782,20 @@
       <c r="B23" s="18"/>
       <c r="C23" s="19"/>
       <c r="D23" s="20"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="22"/>
+      <c r="E23" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="F23" s="22">
+        <v>52</v>
+      </c>
       <c r="G23" s="49"/>
-      <c r="H23" s="23"/>
-      <c r="I23" s="50"/>
+      <c r="H23" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I23" s="50" t="s">
+        <v>53</v>
+      </c>
       <c r="J23" s="34"/>
       <c r="K23" s="37"/>
     </row>
@@ -2713,10 +2804,17 @@
       <c r="B24" s="18"/>
       <c r="C24" s="19"/>
       <c r="D24" s="20"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="22"/>
+      <c r="E24" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="F24" s="22">
+        <v>1</v>
+      </c>
       <c r="G24" s="49"/>
-      <c r="H24" s="23"/>
+      <c r="H24" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="I24" s="50"/>
       <c r="J24" s="34"/>
       <c r="K24" s="37"/>
@@ -2726,11 +2824,20 @@
       <c r="B25" s="18"/>
       <c r="C25" s="19"/>
       <c r="D25" s="20"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="22"/>
+      <c r="E25" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="F25" s="22">
+        <v>38</v>
+      </c>
       <c r="G25" s="49"/>
-      <c r="H25" s="23"/>
-      <c r="I25" s="50"/>
+      <c r="H25" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I25" s="50" t="s">
+        <v>59</v>
+      </c>
       <c r="J25" s="34"/>
       <c r="K25" s="37"/>
     </row>
@@ -2739,24 +2846,54 @@
       <c r="B26" s="18"/>
       <c r="C26" s="19"/>
       <c r="D26" s="20"/>
-      <c r="E26" s="21"/>
-      <c r="F26" s="22"/>
+      <c r="E26" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="F26" s="22">
+        <v>60</v>
+      </c>
       <c r="G26" s="49"/>
-      <c r="H26" s="23"/>
-      <c r="I26" s="51"/>
-      <c r="J26" s="34"/>
+      <c r="H26" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I26" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="J26" s="34">
+        <f>SUM(F19:F26)-B19</f>
+        <v>-66</v>
+      </c>
       <c r="K26" s="37"/>
     </row>
     <row r="27" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="21"/>
-      <c r="B27" s="18"/>
-      <c r="C27" s="19"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="22"/>
+      <c r="A27" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" s="18">
+        <v>2511</v>
+      </c>
+      <c r="C27" s="19">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="D27" s="20">
+        <f t="shared" si="0"/>
+        <v>22096.800000000003</v>
+      </c>
+      <c r="E27" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="F27" s="22">
+        <v>2393</v>
+      </c>
       <c r="G27" s="49"/>
-      <c r="H27" s="23"/>
-      <c r="I27" s="50"/>
+      <c r="H27" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I27" s="50" t="s">
+        <v>53</v>
+      </c>
       <c r="J27" s="34"/>
     </row>
     <row r="28" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
@@ -2764,11 +2901,20 @@
       <c r="B28" s="18"/>
       <c r="C28" s="19"/>
       <c r="D28" s="20"/>
-      <c r="E28" s="21"/>
-      <c r="F28" s="22"/>
+      <c r="E28" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="F28" s="22">
+        <v>15</v>
+      </c>
       <c r="G28" s="49"/>
-      <c r="H28" s="23"/>
-      <c r="I28" s="52"/>
+      <c r="H28" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I28" s="52" t="s">
+        <v>62</v>
+      </c>
       <c r="J28" s="34"/>
     </row>
     <row r="29" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
@@ -2776,22 +2922,48 @@
       <c r="B29" s="18"/>
       <c r="C29" s="19"/>
       <c r="D29" s="20"/>
-      <c r="E29" s="21"/>
-      <c r="F29" s="22"/>
+      <c r="E29" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="F29" s="22">
+        <v>99</v>
+      </c>
       <c r="G29" s="49"/>
-      <c r="H29" s="23"/>
+      <c r="H29" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="I29" s="40"/>
-      <c r="J29" s="34"/>
+      <c r="J29" s="34">
+        <f>SUM(F27:F29)-B27</f>
+        <v>-4</v>
+      </c>
     </row>
     <row r="30" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="21"/>
-      <c r="B30" s="18"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="20"/>
-      <c r="E30" s="21"/>
-      <c r="F30" s="22"/>
+      <c r="A30" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30" s="18">
+        <v>244</v>
+      </c>
+      <c r="C30" s="19">
+        <v>12</v>
+      </c>
+      <c r="D30" s="20">
+        <f t="shared" si="0"/>
+        <v>2928</v>
+      </c>
+      <c r="E30" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="F30" s="22">
+        <v>1</v>
+      </c>
       <c r="G30" s="49"/>
-      <c r="H30" s="23"/>
+      <c r="H30" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="I30" s="38"/>
       <c r="J30" s="34"/>
     </row>
@@ -2800,11 +2972,20 @@
       <c r="B31" s="18"/>
       <c r="C31" s="19"/>
       <c r="D31" s="20"/>
-      <c r="E31" s="21"/>
-      <c r="F31" s="22"/>
+      <c r="E31" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="F31" s="22">
+        <v>1</v>
+      </c>
       <c r="G31" s="49"/>
-      <c r="H31" s="23"/>
-      <c r="I31" s="38"/>
+      <c r="H31" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I31" s="38" t="s">
+        <v>65</v>
+      </c>
       <c r="J31" s="34"/>
     </row>
     <row r="32" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
@@ -2812,10 +2993,17 @@
       <c r="B32" s="18"/>
       <c r="C32" s="19"/>
       <c r="D32" s="20"/>
-      <c r="E32" s="21"/>
-      <c r="F32" s="22"/>
+      <c r="E32" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="F32" s="22">
+        <v>1</v>
+      </c>
       <c r="G32" s="49"/>
-      <c r="H32" s="23"/>
+      <c r="H32" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="I32" s="38"/>
       <c r="J32" s="34"/>
     </row>
@@ -2824,10 +3012,17 @@
       <c r="B33" s="18"/>
       <c r="C33" s="19"/>
       <c r="D33" s="20"/>
-      <c r="E33" s="21"/>
-      <c r="F33" s="22"/>
+      <c r="E33" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="F33" s="22">
+        <v>9</v>
+      </c>
       <c r="G33" s="49"/>
-      <c r="H33" s="23"/>
+      <c r="H33" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="I33" s="38"/>
       <c r="J33" s="34"/>
     </row>
@@ -2836,11 +3031,20 @@
       <c r="B34" s="18"/>
       <c r="C34" s="19"/>
       <c r="D34" s="20"/>
-      <c r="E34" s="21"/>
-      <c r="F34" s="22"/>
+      <c r="E34" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="F34" s="22">
+        <v>1</v>
+      </c>
       <c r="G34" s="49"/>
-      <c r="H34" s="23"/>
-      <c r="I34" s="38"/>
+      <c r="H34" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I34" s="38" t="s">
+        <v>70</v>
+      </c>
       <c r="J34" s="34"/>
     </row>
     <row r="35" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
@@ -2848,11 +3052,20 @@
       <c r="B35" s="18"/>
       <c r="C35" s="19"/>
       <c r="D35" s="20"/>
-      <c r="E35" s="21"/>
-      <c r="F35" s="22"/>
+      <c r="E35" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="F35" s="22">
+        <v>6</v>
+      </c>
       <c r="G35" s="49"/>
-      <c r="H35" s="23"/>
-      <c r="I35" s="54"/>
+      <c r="H35" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I35" s="54" t="s">
+        <v>72</v>
+      </c>
       <c r="J35" s="34"/>
     </row>
     <row r="36" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
@@ -2860,11 +3073,20 @@
       <c r="B36" s="18"/>
       <c r="C36" s="19"/>
       <c r="D36" s="20"/>
-      <c r="E36" s="21"/>
-      <c r="F36" s="22"/>
+      <c r="E36" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="F36" s="22">
+        <v>1</v>
+      </c>
       <c r="G36" s="49"/>
-      <c r="H36" s="23"/>
-      <c r="I36" s="53"/>
+      <c r="H36" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I36" s="53" t="s">
+        <v>74</v>
+      </c>
       <c r="J36" s="34"/>
     </row>
     <row r="37" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
@@ -2872,10 +3094,17 @@
       <c r="B37" s="18"/>
       <c r="C37" s="19"/>
       <c r="D37" s="20"/>
-      <c r="E37" s="21"/>
-      <c r="F37" s="22"/>
+      <c r="E37" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="F37" s="22">
+        <v>1</v>
+      </c>
       <c r="G37" s="49"/>
-      <c r="H37" s="23"/>
+      <c r="H37" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="I37" s="38"/>
       <c r="J37" s="34"/>
     </row>
@@ -2884,11 +3113,20 @@
       <c r="B38" s="18"/>
       <c r="C38" s="19"/>
       <c r="D38" s="20"/>
-      <c r="E38" s="21"/>
-      <c r="F38" s="22"/>
+      <c r="E38" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="F38" s="22">
+        <v>18</v>
+      </c>
       <c r="G38" s="49"/>
-      <c r="H38" s="23"/>
-      <c r="I38" s="53"/>
+      <c r="H38" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I38" s="53" t="s">
+        <v>77</v>
+      </c>
       <c r="J38" s="34"/>
     </row>
     <row r="39" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
@@ -2896,10 +3134,17 @@
       <c r="B39" s="18"/>
       <c r="C39" s="19"/>
       <c r="D39" s="20"/>
-      <c r="E39" s="21"/>
-      <c r="F39" s="22"/>
+      <c r="E39" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="F39" s="22">
+        <v>209</v>
+      </c>
       <c r="G39" s="49"/>
-      <c r="H39" s="23"/>
+      <c r="H39" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="I39" s="38"/>
       <c r="J39" s="34"/>
     </row>
@@ -2908,10 +3153,17 @@
       <c r="B40" s="18"/>
       <c r="C40" s="19"/>
       <c r="D40" s="20"/>
-      <c r="E40" s="21"/>
-      <c r="F40" s="22"/>
+      <c r="E40" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="F40" s="22">
+        <v>2</v>
+      </c>
       <c r="G40" s="49"/>
-      <c r="H40" s="23"/>
+      <c r="H40" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="I40" s="38"/>
       <c r="J40" s="34"/>
     </row>
@@ -2920,22 +3172,48 @@
       <c r="B41" s="18"/>
       <c r="C41" s="19"/>
       <c r="D41" s="20"/>
-      <c r="E41" s="21"/>
-      <c r="F41" s="22"/>
+      <c r="E41" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="F41" s="22">
+        <v>4</v>
+      </c>
       <c r="G41" s="49"/>
-      <c r="H41" s="23"/>
+      <c r="H41" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="I41" s="38"/>
-      <c r="J41" s="34"/>
+      <c r="J41" s="34">
+        <f>SUM(F30:F41)-B30</f>
+        <v>10</v>
+      </c>
     </row>
     <row r="42" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A42" s="21"/>
-      <c r="B42" s="18"/>
-      <c r="C42" s="19"/>
-      <c r="D42" s="20"/>
-      <c r="E42" s="21"/>
-      <c r="F42" s="22"/>
+      <c r="A42" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B42" s="18">
+        <v>4731</v>
+      </c>
+      <c r="C42" s="19">
+        <v>11.2</v>
+      </c>
+      <c r="D42" s="20">
+        <f t="shared" si="0"/>
+        <v>52987.199999999997</v>
+      </c>
+      <c r="E42" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="F42" s="22">
+        <v>2762</v>
+      </c>
       <c r="G42" s="49"/>
-      <c r="H42" s="23"/>
+      <c r="H42" s="23">
+        <f>F42*G42</f>
+        <v>0</v>
+      </c>
       <c r="I42" s="38"/>
       <c r="J42" s="34"/>
       <c r="K42" s="45"/>
@@ -2945,49 +3223,113 @@
       <c r="B43" s="18"/>
       <c r="C43" s="19"/>
       <c r="D43" s="20"/>
-      <c r="E43" s="21"/>
-      <c r="F43" s="22"/>
+      <c r="E43" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="F43" s="22">
+        <v>1779</v>
+      </c>
       <c r="G43" s="49"/>
-      <c r="H43" s="23"/>
+      <c r="H43" s="23">
+        <f t="shared" ref="H43:H44" si="2">F43*G43</f>
+        <v>0</v>
+      </c>
       <c r="I43" s="38"/>
-      <c r="J43" s="34"/>
+      <c r="J43" s="34">
+        <f>F42+F43-B42</f>
+        <v>-190</v>
+      </c>
       <c r="K43" s="45"/>
     </row>
     <row r="44" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A44" s="21"/>
-      <c r="B44" s="18"/>
-      <c r="C44" s="19"/>
-      <c r="D44" s="20"/>
-      <c r="E44" s="21"/>
-      <c r="F44" s="22"/>
+      <c r="A44" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="B44" s="18">
+        <v>1609</v>
+      </c>
+      <c r="C44" s="19">
+        <v>6</v>
+      </c>
+      <c r="D44" s="20">
+        <f t="shared" si="0"/>
+        <v>9654</v>
+      </c>
+      <c r="E44" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="F44" s="22">
+        <v>1609</v>
+      </c>
       <c r="G44" s="49"/>
-      <c r="H44" s="23"/>
+      <c r="H44" s="23">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="I44" s="38"/>
-      <c r="J44" s="34"/>
+      <c r="J44" s="34">
+        <f>F44-B44</f>
+        <v>0</v>
+      </c>
       <c r="K44" s="47"/>
     </row>
     <row r="45" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A45" s="21"/>
-      <c r="B45" s="18"/>
-      <c r="C45" s="19"/>
-      <c r="D45" s="20"/>
-      <c r="E45" s="55"/>
-      <c r="F45" s="22"/>
+      <c r="A45" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="B45" s="18">
+        <v>481</v>
+      </c>
+      <c r="C45" s="19">
+        <v>0.1</v>
+      </c>
+      <c r="D45" s="20">
+        <f t="shared" si="0"/>
+        <v>48.1</v>
+      </c>
+      <c r="E45" s="55" t="s">
+        <v>80</v>
+      </c>
+      <c r="F45" s="22">
+        <v>478</v>
+      </c>
       <c r="G45" s="49"/>
-      <c r="H45" s="23"/>
+      <c r="H45" s="23">
+        <f>F45*G45</f>
+        <v>0</v>
+      </c>
       <c r="I45" s="38"/>
-      <c r="J45" s="34"/>
+      <c r="J45" s="34">
+        <f>F45-B45</f>
+        <v>-3</v>
+      </c>
       <c r="K45" s="47"/>
     </row>
     <row r="46" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A46" s="21"/>
-      <c r="B46" s="18"/>
-      <c r="C46" s="19"/>
-      <c r="D46" s="20"/>
-      <c r="E46" s="21"/>
-      <c r="F46" s="22"/>
+      <c r="A46" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="B46" s="18">
+        <v>295</v>
+      </c>
+      <c r="C46" s="19">
+        <v>13.6</v>
+      </c>
+      <c r="D46" s="20">
+        <f t="shared" si="0"/>
+        <v>4012</v>
+      </c>
+      <c r="E46" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="F46" s="22">
+        <v>146</v>
+      </c>
       <c r="G46" s="49"/>
-      <c r="H46" s="23"/>
+      <c r="H46" s="23">
+        <f t="shared" ref="H46:H58" si="3">F46*G46</f>
+        <v>0</v>
+      </c>
       <c r="I46" s="38"/>
       <c r="J46" s="34"/>
       <c r="K46" s="1"/>
@@ -2997,10 +3339,17 @@
       <c r="B47" s="18"/>
       <c r="C47" s="19"/>
       <c r="D47" s="20"/>
-      <c r="E47" s="21"/>
-      <c r="F47" s="22"/>
+      <c r="E47" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F47" s="22">
+        <v>35</v>
+      </c>
       <c r="G47" s="49"/>
-      <c r="H47" s="23"/>
+      <c r="H47" s="23">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="I47" s="38"/>
       <c r="J47" s="34"/>
       <c r="K47" s="1"/>
@@ -3010,10 +3359,17 @@
       <c r="B48" s="18"/>
       <c r="C48" s="19"/>
       <c r="D48" s="20"/>
-      <c r="E48" s="21"/>
-      <c r="F48" s="22"/>
+      <c r="E48" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="F48" s="22">
+        <v>1</v>
+      </c>
       <c r="G48" s="49"/>
-      <c r="H48" s="23"/>
+      <c r="H48" s="23">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="I48" s="38"/>
       <c r="J48" s="34"/>
       <c r="K48" s="1"/>
@@ -3023,10 +3379,17 @@
       <c r="B49" s="18"/>
       <c r="C49" s="19"/>
       <c r="D49" s="20"/>
-      <c r="E49" s="21"/>
-      <c r="F49" s="22"/>
+      <c r="E49" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="F49" s="22">
+        <v>1</v>
+      </c>
       <c r="G49" s="49"/>
-      <c r="H49" s="23"/>
+      <c r="H49" s="23">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="I49" s="38"/>
       <c r="J49" s="34"/>
       <c r="K49" s="1"/>
@@ -3036,10 +3399,17 @@
       <c r="B50" s="18"/>
       <c r="C50" s="19"/>
       <c r="D50" s="20"/>
-      <c r="E50" s="21"/>
-      <c r="F50" s="22"/>
+      <c r="E50" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="F50" s="22">
+        <v>1</v>
+      </c>
       <c r="G50" s="49"/>
-      <c r="H50" s="23"/>
+      <c r="H50" s="23">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="I50" s="38"/>
       <c r="J50" s="34"/>
       <c r="K50" s="1"/>
@@ -3049,11 +3419,20 @@
       <c r="B51" s="18"/>
       <c r="C51" s="19"/>
       <c r="D51" s="20"/>
-      <c r="E51" s="21"/>
-      <c r="F51" s="22"/>
+      <c r="E51" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="F51" s="22">
+        <v>16</v>
+      </c>
       <c r="G51" s="49"/>
-      <c r="H51" s="23"/>
-      <c r="I51" s="56"/>
+      <c r="H51" s="23">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I51" s="56" t="s">
+        <v>87</v>
+      </c>
       <c r="J51" s="34"/>
       <c r="K51" s="1"/>
     </row>
@@ -3062,11 +3441,20 @@
       <c r="B52" s="18"/>
       <c r="C52" s="19"/>
       <c r="D52" s="20"/>
-      <c r="E52" s="21"/>
-      <c r="F52" s="22"/>
+      <c r="E52" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="F52" s="22">
+        <v>12</v>
+      </c>
       <c r="G52" s="49"/>
-      <c r="H52" s="23"/>
-      <c r="I52" s="39"/>
+      <c r="H52" s="23">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I52" s="39" t="s">
+        <v>83</v>
+      </c>
       <c r="J52" s="34"/>
       <c r="K52" s="1"/>
     </row>
@@ -3075,11 +3463,20 @@
       <c r="B53" s="18"/>
       <c r="C53" s="19"/>
       <c r="D53" s="20"/>
-      <c r="E53" s="21"/>
-      <c r="F53" s="22"/>
+      <c r="E53" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="F53" s="22">
+        <v>7</v>
+      </c>
       <c r="G53" s="49"/>
-      <c r="H53" s="23"/>
-      <c r="I53" s="38"/>
+      <c r="H53" s="23">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I53" s="38" t="s">
+        <v>84</v>
+      </c>
       <c r="J53" s="34"/>
       <c r="K53" s="1"/>
     </row>
@@ -3088,11 +3485,20 @@
       <c r="B54" s="18"/>
       <c r="C54" s="19"/>
       <c r="D54" s="20"/>
-      <c r="E54" s="21"/>
-      <c r="F54" s="22"/>
+      <c r="E54" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="F54" s="22">
+        <v>25</v>
+      </c>
       <c r="G54" s="49"/>
-      <c r="H54" s="23"/>
-      <c r="I54" s="38"/>
+      <c r="H54" s="23">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I54" s="38" t="s">
+        <v>85</v>
+      </c>
       <c r="J54" s="34"/>
       <c r="K54" s="1"/>
     </row>
@@ -3101,11 +3507,20 @@
       <c r="B55" s="18"/>
       <c r="C55" s="19"/>
       <c r="D55" s="20"/>
-      <c r="E55" s="21"/>
-      <c r="F55" s="22"/>
+      <c r="E55" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="F55" s="22">
+        <v>18</v>
+      </c>
       <c r="G55" s="49"/>
-      <c r="H55" s="23"/>
-      <c r="I55" s="38"/>
+      <c r="H55" s="23">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I55" s="38" t="s">
+        <v>89</v>
+      </c>
       <c r="J55" s="34"/>
       <c r="K55" s="1"/>
     </row>
@@ -3114,11 +3529,20 @@
       <c r="B56" s="18"/>
       <c r="C56" s="19"/>
       <c r="D56" s="20"/>
-      <c r="E56" s="21"/>
-      <c r="F56" s="22"/>
+      <c r="E56" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="F56" s="22">
+        <v>5</v>
+      </c>
       <c r="G56" s="49"/>
-      <c r="H56" s="23"/>
-      <c r="I56" s="38"/>
+      <c r="H56" s="23">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I56" s="38" t="s">
+        <v>90</v>
+      </c>
       <c r="J56" s="34"/>
       <c r="K56" s="1"/>
     </row>
@@ -3127,10 +3551,17 @@
       <c r="B57" s="18"/>
       <c r="C57" s="19"/>
       <c r="D57" s="20"/>
-      <c r="E57" s="21"/>
-      <c r="F57" s="22"/>
+      <c r="E57" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="F57" s="22">
+        <v>7</v>
+      </c>
       <c r="G57" s="49"/>
-      <c r="H57" s="23"/>
+      <c r="H57" s="23">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="I57" s="38"/>
       <c r="J57" s="34"/>
       <c r="K57" s="1"/>
@@ -3140,23 +3571,49 @@
       <c r="B58" s="18"/>
       <c r="C58" s="19"/>
       <c r="D58" s="20"/>
-      <c r="E58" s="21"/>
-      <c r="F58" s="22"/>
+      <c r="E58" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="F58" s="22">
+        <v>8</v>
+      </c>
       <c r="G58" s="49"/>
-      <c r="H58" s="23"/>
+      <c r="H58" s="23">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="I58" s="38"/>
-      <c r="J58" s="34"/>
+      <c r="J58" s="34">
+        <f>SUM(F46:F58)-B46</f>
+        <v>-13</v>
+      </c>
       <c r="K58" s="1"/>
     </row>
     <row r="59" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A59" s="21"/>
-      <c r="B59" s="18"/>
-      <c r="C59" s="19"/>
-      <c r="D59" s="20"/>
-      <c r="E59" s="21"/>
-      <c r="F59" s="22"/>
+      <c r="A59" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B59" s="18">
+        <v>2532</v>
+      </c>
+      <c r="C59" s="19">
+        <v>13.1</v>
+      </c>
+      <c r="D59" s="20">
+        <f t="shared" si="0"/>
+        <v>33169.199999999997</v>
+      </c>
+      <c r="E59" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="F59" s="22">
+        <v>2469</v>
+      </c>
       <c r="G59" s="49"/>
-      <c r="H59" s="23"/>
+      <c r="H59" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="I59" s="38"/>
       <c r="J59" s="34"/>
       <c r="K59" s="1"/>
@@ -3166,23 +3623,49 @@
       <c r="B60" s="18"/>
       <c r="C60" s="19"/>
       <c r="D60" s="20"/>
-      <c r="E60" s="21"/>
-      <c r="F60" s="22"/>
+      <c r="E60" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="F60" s="22">
+        <v>10</v>
+      </c>
       <c r="G60" s="49"/>
-      <c r="H60" s="23"/>
+      <c r="H60" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="I60" s="38"/>
-      <c r="J60" s="34"/>
+      <c r="J60" s="34">
+        <f>SUM(F59:F60)-B59</f>
+        <v>-53</v>
+      </c>
       <c r="K60" s="1"/>
     </row>
     <row r="61" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A61" s="21"/>
-      <c r="B61" s="18"/>
-      <c r="C61" s="19"/>
-      <c r="D61" s="20"/>
-      <c r="E61" s="21"/>
-      <c r="F61" s="22"/>
+      <c r="A61" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B61" s="18">
+        <v>287</v>
+      </c>
+      <c r="C61" s="19">
+        <v>14.2</v>
+      </c>
+      <c r="D61" s="20">
+        <f t="shared" si="0"/>
+        <v>4075.3999999999996</v>
+      </c>
+      <c r="E61" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F61" s="22">
+        <v>270</v>
+      </c>
       <c r="G61" s="49"/>
-      <c r="H61" s="23"/>
+      <c r="H61" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="I61" s="38"/>
       <c r="J61" s="34"/>
       <c r="K61" s="46"/>
@@ -3192,10 +3675,17 @@
       <c r="B62" s="18"/>
       <c r="C62" s="19"/>
       <c r="D62" s="20"/>
-      <c r="E62" s="21"/>
-      <c r="F62" s="22"/>
+      <c r="E62" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="F62" s="22">
+        <v>40</v>
+      </c>
       <c r="G62" s="49"/>
-      <c r="H62" s="23"/>
+      <c r="H62" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="I62" s="38"/>
       <c r="J62" s="34"/>
       <c r="K62" s="46"/>
@@ -3205,24 +3695,54 @@
       <c r="B63" s="18"/>
       <c r="C63" s="19"/>
       <c r="D63" s="20"/>
-      <c r="E63" s="21"/>
-      <c r="F63" s="22"/>
+      <c r="E63" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="F63" s="22">
+        <v>52</v>
+      </c>
       <c r="G63" s="49"/>
-      <c r="H63" s="23"/>
-      <c r="I63" s="53"/>
-      <c r="J63" s="34"/>
+      <c r="H63" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I63" s="53" t="s">
+        <v>95</v>
+      </c>
+      <c r="J63" s="34">
+        <f>SUM(F61:F63)-B61</f>
+        <v>75</v>
+      </c>
       <c r="K63" s="46"/>
     </row>
     <row r="64" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A64" s="21"/>
-      <c r="B64" s="18"/>
-      <c r="C64" s="19"/>
-      <c r="D64" s="20"/>
-      <c r="E64" s="21"/>
-      <c r="F64" s="22"/>
+      <c r="A64" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B64" s="18">
+        <v>1171</v>
+      </c>
+      <c r="C64" s="19">
+        <v>13.6</v>
+      </c>
+      <c r="D64" s="20">
+        <f t="shared" si="0"/>
+        <v>15925.6</v>
+      </c>
+      <c r="E64" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="F64" s="22">
+        <v>1144</v>
+      </c>
       <c r="G64" s="49"/>
-      <c r="H64" s="23"/>
-      <c r="I64" s="58"/>
+      <c r="H64" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I64" s="58" t="s">
+        <v>96</v>
+      </c>
       <c r="J64" s="34"/>
       <c r="K64" s="1"/>
     </row>
@@ -3231,24 +3751,54 @@
       <c r="B65" s="18"/>
       <c r="C65" s="19"/>
       <c r="D65" s="20"/>
-      <c r="E65" s="21"/>
-      <c r="F65" s="22"/>
+      <c r="E65" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="F65" s="22">
+        <v>18</v>
+      </c>
       <c r="G65" s="49"/>
-      <c r="H65" s="23"/>
-      <c r="I65" s="58"/>
-      <c r="J65" s="34"/>
+      <c r="H65" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I65" s="58" t="s">
+        <v>96</v>
+      </c>
+      <c r="J65" s="34">
+        <f>F64+F65-B64</f>
+        <v>-9</v>
+      </c>
       <c r="K65" s="1"/>
     </row>
     <row r="66" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A66" s="21"/>
-      <c r="B66" s="18"/>
-      <c r="C66" s="19"/>
-      <c r="D66" s="20"/>
-      <c r="E66" s="21"/>
-      <c r="F66" s="22"/>
+      <c r="A66" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="B66" s="18">
+        <v>95</v>
+      </c>
+      <c r="C66" s="19">
+        <v>12</v>
+      </c>
+      <c r="D66" s="20">
+        <f t="shared" si="0"/>
+        <v>1140</v>
+      </c>
+      <c r="E66" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="F66" s="22">
+        <v>40</v>
+      </c>
       <c r="G66" s="49"/>
-      <c r="H66" s="23"/>
-      <c r="I66" s="38"/>
+      <c r="H66" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I66" s="38" t="s">
+        <v>65</v>
+      </c>
       <c r="J66" s="34"/>
     </row>
     <row r="67" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
@@ -3256,11 +3806,20 @@
       <c r="B67" s="18"/>
       <c r="C67" s="19"/>
       <c r="D67" s="20"/>
-      <c r="E67" s="21"/>
-      <c r="F67" s="22"/>
+      <c r="E67" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="F67" s="22">
+        <v>20</v>
+      </c>
       <c r="G67" s="49"/>
-      <c r="H67" s="23"/>
-      <c r="I67" s="38"/>
+      <c r="H67" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I67" s="38" t="s">
+        <v>69</v>
+      </c>
       <c r="J67" s="34"/>
     </row>
     <row r="68" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
@@ -3268,22 +3827,50 @@
       <c r="B68" s="18"/>
       <c r="C68" s="19"/>
       <c r="D68" s="20"/>
-      <c r="E68" s="21"/>
-      <c r="F68" s="22"/>
+      <c r="E68" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="F68" s="22">
+        <v>32</v>
+      </c>
       <c r="G68" s="49"/>
-      <c r="H68" s="23"/>
-      <c r="I68" s="39"/>
-      <c r="J68" s="34"/>
+      <c r="H68" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I68" s="39" t="s">
+        <v>98</v>
+      </c>
+      <c r="J68" s="34">
+        <f>SUM(F66:F68)-B66</f>
+        <v>-3</v>
+      </c>
     </row>
     <row r="69" spans="1:11" s="4" customFormat="1" ht="35.15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A69" s="21"/>
-      <c r="B69" s="18"/>
-      <c r="C69" s="19"/>
-      <c r="D69" s="20"/>
-      <c r="E69" s="21"/>
-      <c r="F69" s="22"/>
+      <c r="A69" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="B69" s="18">
+        <v>496</v>
+      </c>
+      <c r="C69" s="19">
+        <v>9</v>
+      </c>
+      <c r="D69" s="20">
+        <f t="shared" si="0"/>
+        <v>4464</v>
+      </c>
+      <c r="E69" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="F69" s="22">
+        <v>44</v>
+      </c>
       <c r="G69" s="49"/>
-      <c r="H69" s="23"/>
+      <c r="H69" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="I69" s="39"/>
       <c r="J69" s="34"/>
     </row>
@@ -3292,11 +3879,20 @@
       <c r="B70" s="18"/>
       <c r="C70" s="19"/>
       <c r="D70" s="20"/>
-      <c r="E70" s="21"/>
-      <c r="F70" s="22"/>
+      <c r="E70" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="F70" s="22">
+        <v>3</v>
+      </c>
       <c r="G70" s="49"/>
-      <c r="H70" s="23"/>
-      <c r="I70" s="59"/>
+      <c r="H70" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I70" s="59" t="s">
+        <v>100</v>
+      </c>
       <c r="J70" s="34"/>
     </row>
     <row r="71" spans="1:11" s="4" customFormat="1" ht="35.15" customHeight="1" x14ac:dyDescent="0.45">
@@ -3304,10 +3900,17 @@
       <c r="B71" s="18"/>
       <c r="C71" s="19"/>
       <c r="D71" s="20"/>
-      <c r="E71" s="21"/>
-      <c r="F71" s="22"/>
+      <c r="E71" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="F71" s="22">
+        <v>4</v>
+      </c>
       <c r="G71" s="49"/>
-      <c r="H71" s="23"/>
+      <c r="H71" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="I71" s="39"/>
       <c r="J71" s="34"/>
     </row>
@@ -3316,10 +3919,17 @@
       <c r="B72" s="18"/>
       <c r="C72" s="19"/>
       <c r="D72" s="20"/>
-      <c r="E72" s="21"/>
-      <c r="F72" s="22"/>
+      <c r="E72" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="F72" s="22">
+        <v>2</v>
+      </c>
       <c r="G72" s="49"/>
-      <c r="H72" s="23"/>
+      <c r="H72" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="I72" s="39"/>
       <c r="J72" s="34"/>
     </row>
@@ -3328,11 +3938,20 @@
       <c r="B73" s="18"/>
       <c r="C73" s="19"/>
       <c r="D73" s="20"/>
-      <c r="E73" s="21"/>
-      <c r="F73" s="22"/>
+      <c r="E73" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="F73" s="22">
+        <v>11</v>
+      </c>
       <c r="G73" s="49"/>
-      <c r="H73" s="23"/>
-      <c r="I73" s="39"/>
+      <c r="H73" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I73" s="39" t="s">
+        <v>65</v>
+      </c>
       <c r="J73" s="34"/>
     </row>
     <row r="74" spans="1:11" s="4" customFormat="1" ht="35.15" customHeight="1" x14ac:dyDescent="0.45">
@@ -3340,10 +3959,17 @@
       <c r="B74" s="18"/>
       <c r="C74" s="19"/>
       <c r="D74" s="20"/>
-      <c r="E74" s="21"/>
-      <c r="F74" s="22"/>
+      <c r="E74" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="F74" s="22">
+        <v>18</v>
+      </c>
       <c r="G74" s="49"/>
-      <c r="H74" s="23"/>
+      <c r="H74" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="I74" s="39"/>
       <c r="J74" s="34"/>
     </row>
@@ -3352,10 +3978,17 @@
       <c r="B75" s="18"/>
       <c r="C75" s="19"/>
       <c r="D75" s="20"/>
-      <c r="E75" s="21"/>
-      <c r="F75" s="22"/>
+      <c r="E75" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="F75" s="22">
+        <v>15</v>
+      </c>
       <c r="G75" s="49"/>
-      <c r="H75" s="23"/>
+      <c r="H75" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="I75" s="39"/>
       <c r="J75" s="34"/>
     </row>
@@ -3364,11 +3997,20 @@
       <c r="B76" s="18"/>
       <c r="C76" s="19"/>
       <c r="D76" s="20"/>
-      <c r="E76" s="21"/>
-      <c r="F76" s="22"/>
+      <c r="E76" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="F76" s="22">
+        <v>34</v>
+      </c>
       <c r="G76" s="49"/>
-      <c r="H76" s="23"/>
-      <c r="I76" s="60"/>
+      <c r="H76" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I76" s="60" t="s">
+        <v>104</v>
+      </c>
       <c r="J76" s="34"/>
     </row>
     <row r="77" spans="1:11" s="4" customFormat="1" ht="35.15" customHeight="1" x14ac:dyDescent="0.45">
@@ -3376,10 +4018,17 @@
       <c r="B77" s="18"/>
       <c r="C77" s="19"/>
       <c r="D77" s="20"/>
-      <c r="E77" s="21"/>
-      <c r="F77" s="22"/>
+      <c r="E77" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="F77" s="22">
+        <v>1</v>
+      </c>
       <c r="G77" s="49"/>
-      <c r="H77" s="23"/>
+      <c r="H77" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="I77" s="39"/>
       <c r="J77" s="34"/>
     </row>
@@ -3388,11 +4037,20 @@
       <c r="B78" s="18"/>
       <c r="C78" s="19"/>
       <c r="D78" s="20"/>
-      <c r="E78" s="21"/>
-      <c r="F78" s="22"/>
+      <c r="E78" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="F78" s="22">
+        <v>9</v>
+      </c>
       <c r="G78" s="49"/>
-      <c r="H78" s="23"/>
-      <c r="I78" s="59"/>
+      <c r="H78" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I78" s="59" t="s">
+        <v>105</v>
+      </c>
       <c r="J78" s="34"/>
     </row>
     <row r="79" spans="1:11" s="4" customFormat="1" ht="35.15" customHeight="1" x14ac:dyDescent="0.45">
@@ -3400,11 +4058,20 @@
       <c r="B79" s="18"/>
       <c r="C79" s="19"/>
       <c r="D79" s="20"/>
-      <c r="E79" s="21"/>
-      <c r="F79" s="22"/>
+      <c r="E79" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="F79" s="22">
+        <v>25</v>
+      </c>
       <c r="G79" s="49"/>
-      <c r="H79" s="23"/>
-      <c r="I79" s="59"/>
+      <c r="H79" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I79" s="59" t="s">
+        <v>108</v>
+      </c>
       <c r="J79" s="34"/>
     </row>
     <row r="80" spans="1:11" s="4" customFormat="1" ht="35.15" customHeight="1" x14ac:dyDescent="0.45">
@@ -3412,10 +4079,17 @@
       <c r="B80" s="18"/>
       <c r="C80" s="19"/>
       <c r="D80" s="20"/>
-      <c r="E80" s="21"/>
-      <c r="F80" s="22"/>
+      <c r="E80" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="F80" s="22">
+        <v>6</v>
+      </c>
       <c r="G80" s="49"/>
-      <c r="H80" s="23"/>
+      <c r="H80" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="I80" s="59"/>
       <c r="J80" s="34"/>
     </row>
@@ -3424,10 +4098,17 @@
       <c r="B81" s="18"/>
       <c r="C81" s="19"/>
       <c r="D81" s="20"/>
-      <c r="E81" s="21"/>
-      <c r="F81" s="22"/>
+      <c r="E81" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="F81" s="22">
+        <v>2</v>
+      </c>
       <c r="G81" s="49"/>
-      <c r="H81" s="23"/>
+      <c r="H81" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="I81" s="59"/>
       <c r="J81" s="34"/>
     </row>
@@ -3436,10 +4117,17 @@
       <c r="B82" s="18"/>
       <c r="C82" s="19"/>
       <c r="D82" s="20"/>
-      <c r="E82" s="21"/>
-      <c r="F82" s="22"/>
+      <c r="E82" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="F82" s="22">
+        <v>108</v>
+      </c>
       <c r="G82" s="49"/>
-      <c r="H82" s="23"/>
+      <c r="H82" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="I82" s="59"/>
       <c r="J82" s="34"/>
     </row>
@@ -3448,10 +4136,17 @@
       <c r="B83" s="18"/>
       <c r="C83" s="19"/>
       <c r="D83" s="20"/>
-      <c r="E83" s="21"/>
-      <c r="F83" s="22"/>
+      <c r="E83" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="F83" s="22">
+        <v>180</v>
+      </c>
       <c r="G83" s="49"/>
-      <c r="H83" s="23"/>
+      <c r="H83" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="I83" s="59"/>
       <c r="J83" s="34"/>
     </row>
@@ -3460,11 +4155,20 @@
       <c r="B84" s="18"/>
       <c r="C84" s="19"/>
       <c r="D84" s="20"/>
-      <c r="E84" s="21"/>
-      <c r="F84" s="22"/>
+      <c r="E84" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="F84" s="22">
+        <v>22</v>
+      </c>
       <c r="G84" s="49"/>
-      <c r="H84" s="23"/>
-      <c r="I84" s="59"/>
+      <c r="H84" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I84" s="59" t="s">
+        <v>107</v>
+      </c>
       <c r="J84" s="34"/>
     </row>
     <row r="85" spans="1:11" s="4" customFormat="1" ht="35.15" customHeight="1" x14ac:dyDescent="0.45">
@@ -3472,22 +4176,48 @@
       <c r="B85" s="18"/>
       <c r="C85" s="19"/>
       <c r="D85" s="20"/>
-      <c r="E85" s="21"/>
-      <c r="F85" s="22"/>
+      <c r="E85" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="F85" s="22">
+        <v>18</v>
+      </c>
       <c r="G85" s="49"/>
-      <c r="H85" s="23"/>
+      <c r="H85" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="I85" s="39"/>
-      <c r="J85" s="34"/>
+      <c r="J85" s="34">
+        <f>SUM(F69:F85)-B69</f>
+        <v>6</v>
+      </c>
     </row>
     <row r="86" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A86" s="21"/>
-      <c r="B86" s="18"/>
-      <c r="C86" s="19"/>
-      <c r="D86" s="20"/>
-      <c r="E86" s="21"/>
-      <c r="F86" s="22"/>
+      <c r="A86" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="B86" s="18">
+        <v>58</v>
+      </c>
+      <c r="C86" s="19">
+        <v>35</v>
+      </c>
+      <c r="D86" s="20">
+        <f t="shared" si="0"/>
+        <v>2030</v>
+      </c>
+      <c r="E86" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="F86" s="22">
+        <v>7</v>
+      </c>
       <c r="G86" s="49"/>
-      <c r="H86" s="23"/>
+      <c r="H86" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="I86" s="39"/>
       <c r="J86" s="34"/>
       <c r="K86" s="48"/>
@@ -3497,10 +4227,17 @@
       <c r="B87" s="18"/>
       <c r="C87" s="19"/>
       <c r="D87" s="20"/>
-      <c r="E87" s="21"/>
-      <c r="F87" s="22"/>
+      <c r="E87" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="F87" s="22">
+        <v>1</v>
+      </c>
       <c r="G87" s="49"/>
-      <c r="H87" s="23"/>
+      <c r="H87" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="I87" s="39"/>
       <c r="J87" s="34"/>
       <c r="K87" s="48"/>
@@ -3510,11 +4247,20 @@
       <c r="B88" s="18"/>
       <c r="C88" s="19"/>
       <c r="D88" s="20"/>
-      <c r="E88" s="21"/>
-      <c r="F88" s="22"/>
+      <c r="E88" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="F88" s="22">
+        <v>14</v>
+      </c>
       <c r="G88" s="49"/>
-      <c r="H88" s="23"/>
-      <c r="I88" s="59"/>
+      <c r="H88" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I88" s="59" t="s">
+        <v>110</v>
+      </c>
       <c r="J88" s="34"/>
       <c r="K88" s="48"/>
     </row>
@@ -3523,11 +4269,20 @@
       <c r="B89" s="18"/>
       <c r="C89" s="19"/>
       <c r="D89" s="20"/>
-      <c r="E89" s="21"/>
-      <c r="F89" s="22"/>
+      <c r="E89" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="F89" s="22">
+        <v>14</v>
+      </c>
       <c r="G89" s="49"/>
-      <c r="H89" s="23"/>
-      <c r="I89" s="59"/>
+      <c r="H89" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I89" s="59" t="s">
+        <v>111</v>
+      </c>
       <c r="J89" s="34"/>
       <c r="K89" s="48"/>
     </row>
@@ -3536,10 +4291,17 @@
       <c r="B90" s="18"/>
       <c r="C90" s="19"/>
       <c r="D90" s="20"/>
-      <c r="E90" s="21"/>
-      <c r="F90" s="22"/>
+      <c r="E90" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="F90" s="22">
+        <v>6</v>
+      </c>
       <c r="G90" s="49"/>
-      <c r="H90" s="23"/>
+      <c r="H90" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="I90" s="39"/>
       <c r="J90" s="34"/>
       <c r="K90" s="48"/>
@@ -3549,10 +4311,17 @@
       <c r="B91" s="18"/>
       <c r="C91" s="19"/>
       <c r="D91" s="20"/>
-      <c r="E91" s="21"/>
-      <c r="F91" s="22"/>
+      <c r="E91" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="F91" s="22">
+        <v>2</v>
+      </c>
       <c r="G91" s="49"/>
-      <c r="H91" s="23"/>
+      <c r="H91" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="I91" s="39"/>
       <c r="J91" s="34"/>
       <c r="K91" s="48"/>
@@ -3562,10 +4331,17 @@
       <c r="B92" s="18"/>
       <c r="C92" s="19"/>
       <c r="D92" s="20"/>
-      <c r="E92" s="21"/>
-      <c r="F92" s="22"/>
+      <c r="E92" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="F92" s="22">
+        <v>1</v>
+      </c>
       <c r="G92" s="49"/>
-      <c r="H92" s="23"/>
+      <c r="H92" s="23">
+        <f t="shared" ref="H92" si="4">F92*G92</f>
+        <v>0</v>
+      </c>
       <c r="I92" s="59"/>
       <c r="J92" s="34"/>
     </row>
@@ -3574,23 +4350,49 @@
       <c r="B93" s="18"/>
       <c r="C93" s="19"/>
       <c r="D93" s="20"/>
-      <c r="E93" s="21"/>
-      <c r="F93" s="22"/>
+      <c r="E93" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="F93" s="22">
+        <v>11</v>
+      </c>
       <c r="G93" s="49"/>
-      <c r="H93" s="23"/>
+      <c r="H93" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="I93" s="39"/>
-      <c r="J93" s="34"/>
+      <c r="J93" s="34">
+        <f>SUM(F86:F93)-B86</f>
+        <v>-2</v>
+      </c>
       <c r="K93" s="48"/>
     </row>
     <row r="94" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A94" s="21"/>
-      <c r="B94" s="18"/>
-      <c r="C94" s="19"/>
-      <c r="D94" s="20"/>
-      <c r="E94" s="21"/>
-      <c r="F94" s="22"/>
+      <c r="A94" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B94" s="18">
+        <v>202</v>
+      </c>
+      <c r="C94" s="19">
+        <v>10.5</v>
+      </c>
+      <c r="D94" s="20">
+        <f t="shared" si="0"/>
+        <v>2121</v>
+      </c>
+      <c r="E94" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="F94" s="22">
+        <v>1</v>
+      </c>
       <c r="G94" s="49"/>
-      <c r="H94" s="23"/>
+      <c r="H94" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="I94" s="39"/>
       <c r="J94" s="34"/>
       <c r="K94" s="1"/>
@@ -3600,11 +4402,20 @@
       <c r="B95" s="18"/>
       <c r="C95" s="19"/>
       <c r="D95" s="20"/>
-      <c r="E95" s="21"/>
-      <c r="F95" s="22"/>
+      <c r="E95" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="F95" s="22">
+        <v>64</v>
+      </c>
       <c r="G95" s="49"/>
-      <c r="H95" s="23"/>
-      <c r="I95" s="61"/>
+      <c r="H95" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I95" s="61" t="s">
+        <v>113</v>
+      </c>
       <c r="J95" s="34"/>
       <c r="K95" s="1"/>
     </row>
@@ -3613,10 +4424,17 @@
       <c r="B96" s="18"/>
       <c r="C96" s="19"/>
       <c r="D96" s="20"/>
-      <c r="E96" s="21"/>
-      <c r="F96" s="22"/>
+      <c r="E96" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="F96" s="22">
+        <v>6</v>
+      </c>
       <c r="G96" s="49"/>
-      <c r="H96" s="23"/>
+      <c r="H96" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="I96" s="39"/>
       <c r="J96" s="34"/>
       <c r="K96" s="1"/>
@@ -3626,10 +4444,17 @@
       <c r="B97" s="18"/>
       <c r="C97" s="19"/>
       <c r="D97" s="20"/>
-      <c r="E97" s="21"/>
-      <c r="F97" s="22"/>
+      <c r="E97" s="21" t="s">
+        <v>114</v>
+      </c>
+      <c r="F97" s="22">
+        <v>5</v>
+      </c>
       <c r="G97" s="49"/>
-      <c r="H97" s="23"/>
+      <c r="H97" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="I97" s="39"/>
       <c r="J97" s="34"/>
       <c r="K97" s="1"/>
@@ -3639,10 +4464,17 @@
       <c r="B98" s="18"/>
       <c r="C98" s="19"/>
       <c r="D98" s="20"/>
-      <c r="E98" s="21"/>
-      <c r="F98" s="22"/>
+      <c r="E98" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="F98" s="22">
+        <v>51</v>
+      </c>
       <c r="G98" s="49"/>
-      <c r="H98" s="23"/>
+      <c r="H98" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="I98" s="39"/>
       <c r="J98" s="34"/>
       <c r="K98" s="1"/>
@@ -3652,11 +4484,20 @@
       <c r="B99" s="18"/>
       <c r="C99" s="19"/>
       <c r="D99" s="20"/>
-      <c r="E99" s="21"/>
-      <c r="F99" s="22"/>
+      <c r="E99" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="F99" s="22">
+        <v>22</v>
+      </c>
       <c r="G99" s="49"/>
-      <c r="H99" s="23"/>
-      <c r="I99" s="59"/>
+      <c r="H99" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I99" s="59" t="s">
+        <v>115</v>
+      </c>
       <c r="J99" s="34"/>
       <c r="K99" s="1"/>
     </row>
@@ -3665,11 +4506,20 @@
       <c r="B100" s="18"/>
       <c r="C100" s="19"/>
       <c r="D100" s="20"/>
-      <c r="E100" s="21"/>
-      <c r="F100" s="22"/>
+      <c r="E100" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="F100" s="22">
+        <v>25</v>
+      </c>
       <c r="G100" s="49"/>
-      <c r="H100" s="23"/>
-      <c r="I100" s="59"/>
+      <c r="H100" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I100" s="59" t="s">
+        <v>116</v>
+      </c>
       <c r="J100" s="34"/>
       <c r="K100" s="1"/>
     </row>
@@ -3678,36 +4528,83 @@
       <c r="B101" s="18"/>
       <c r="C101" s="19"/>
       <c r="D101" s="20"/>
-      <c r="E101" s="21"/>
-      <c r="F101" s="22"/>
+      <c r="E101" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="F101" s="22">
+        <v>23</v>
+      </c>
       <c r="G101" s="49"/>
-      <c r="H101" s="23"/>
+      <c r="H101" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="I101" s="39"/>
-      <c r="J101" s="34"/>
+      <c r="J101" s="34">
+        <f>SUM(F94:F101)-B94</f>
+        <v>-5</v>
+      </c>
       <c r="K101" s="1"/>
     </row>
     <row r="102" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A102" s="21"/>
-      <c r="B102" s="18"/>
-      <c r="C102" s="19"/>
-      <c r="D102" s="20"/>
-      <c r="E102" s="21"/>
-      <c r="F102" s="22"/>
+      <c r="A102" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="B102" s="18">
+        <v>1443</v>
+      </c>
+      <c r="C102" s="19">
+        <v>3.3</v>
+      </c>
+      <c r="D102" s="20">
+        <f t="shared" si="0"/>
+        <v>4761.8999999999996</v>
+      </c>
+      <c r="E102" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="F102" s="22">
+        <v>1456</v>
+      </c>
       <c r="G102" s="49"/>
-      <c r="H102" s="23"/>
-      <c r="I102" s="62"/>
-      <c r="J102" s="34"/>
+      <c r="H102" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I102" s="62" t="s">
+        <v>118</v>
+      </c>
+      <c r="J102" s="34">
+        <f>F102-B102</f>
+        <v>13</v>
+      </c>
       <c r="K102" s="48"/>
     </row>
     <row r="103" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A103" s="21"/>
-      <c r="B103" s="18"/>
-      <c r="C103" s="19"/>
-      <c r="D103" s="20"/>
-      <c r="E103" s="21"/>
-      <c r="F103" s="22"/>
+      <c r="A103" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="B103" s="18">
+        <v>2609</v>
+      </c>
+      <c r="C103" s="19">
+        <v>5.2</v>
+      </c>
+      <c r="D103" s="20">
+        <f t="shared" si="0"/>
+        <v>13566.800000000001</v>
+      </c>
+      <c r="E103" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="F103" s="22">
+        <v>1965</v>
+      </c>
       <c r="G103" s="49"/>
-      <c r="H103" s="23"/>
+      <c r="H103" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="I103" s="39"/>
       <c r="J103" s="34"/>
     </row>
@@ -3716,22 +4613,48 @@
       <c r="B104" s="18"/>
       <c r="C104" s="19"/>
       <c r="D104" s="20"/>
-      <c r="E104" s="21"/>
-      <c r="F104" s="22"/>
+      <c r="E104" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="F104" s="22">
+        <v>640</v>
+      </c>
       <c r="G104" s="49"/>
-      <c r="H104" s="23"/>
+      <c r="H104" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="I104" s="39"/>
-      <c r="J104" s="34"/>
+      <c r="J104" s="34">
+        <f>SUM(F103:F104)-B103</f>
+        <v>-4</v>
+      </c>
     </row>
     <row r="105" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A105" s="21"/>
-      <c r="B105" s="18"/>
-      <c r="C105" s="19"/>
-      <c r="D105" s="20"/>
-      <c r="E105" s="21"/>
-      <c r="F105" s="22"/>
+      <c r="A105" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B105" s="18">
+        <v>212</v>
+      </c>
+      <c r="C105" s="19">
+        <v>13</v>
+      </c>
+      <c r="D105" s="20">
+        <f t="shared" si="0"/>
+        <v>2756</v>
+      </c>
+      <c r="E105" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="F105" s="22">
+        <v>150</v>
+      </c>
       <c r="G105" s="49"/>
-      <c r="H105" s="23"/>
+      <c r="H105" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="I105" s="39"/>
       <c r="J105" s="34"/>
     </row>
@@ -3740,52 +4663,88 @@
       <c r="B106" s="18"/>
       <c r="C106" s="19"/>
       <c r="D106" s="20"/>
-      <c r="E106" s="21"/>
-      <c r="F106" s="22"/>
+      <c r="E106" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="F106" s="22">
+        <v>56</v>
+      </c>
       <c r="G106" s="49"/>
-      <c r="H106" s="23"/>
-      <c r="I106" s="39"/>
-      <c r="J106" s="34"/>
+      <c r="H106" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I106" s="39" t="s">
+        <v>50</v>
+      </c>
+      <c r="J106" s="34">
+        <f>SUM(F105:F106)-B105</f>
+        <v>-6</v>
+      </c>
     </row>
     <row r="107" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A107" s="21"/>
-      <c r="B107" s="18"/>
-      <c r="C107" s="19"/>
-      <c r="D107" s="20"/>
-      <c r="E107" s="21"/>
-      <c r="F107" s="22"/>
+      <c r="A107" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="B107" s="18">
+        <v>35</v>
+      </c>
+      <c r="C107" s="19">
+        <v>2.6</v>
+      </c>
+      <c r="D107" s="20">
+        <f t="shared" si="0"/>
+        <v>91</v>
+      </c>
+      <c r="E107" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="F107" s="22">
+        <v>36</v>
+      </c>
       <c r="G107" s="49"/>
-      <c r="H107" s="23"/>
-      <c r="I107" s="57"/>
-      <c r="J107" s="34"/>
+      <c r="H107" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I107" s="57" t="s">
+        <v>93</v>
+      </c>
+      <c r="J107" s="34">
+        <f>F107-B107</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="108" spans="1:11" ht="35.15" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="A108" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TOTAL</t>
-        </is>
+      <c r="A108" s="24" t="s">
+        <v>12</v>
       </c>
       <c r="B108" s="25">
-        <v>500</v>
+        <f>SUM(B13:B107)</f>
+        <v>31496</v>
       </c>
       <c r="C108" s="26"/>
       <c r="D108" s="27">
-        <v>0</v>
-      </c>
-      <c r="E108" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TOTAL</t>
-        </is>
+        <f>SUM(D13:D107)</f>
+        <v>326577.60000000003</v>
+      </c>
+      <c r="E108" s="28" t="s">
+        <v>12</v>
       </c>
       <c r="F108" s="29">
-        <v>500</v>
+        <f>SUM(F13:F107)</f>
+        <v>30965</v>
       </c>
       <c r="G108" s="26"/>
       <c r="H108" s="26">
+        <f>SUM(H13:H107)</f>
         <v>0</v>
       </c>
       <c r="I108" s="12"/>
-      <c r="J108" s="35"/>
+      <c r="J108" s="35">
+        <f>SUM(J13:J107)</f>
+        <v>-531</v>
+      </c>
     </row>
     <row r="109" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A109" s="4"/>
@@ -3797,49 +4756,41 @@
       <c r="G109" s="6"/>
       <c r="H109" s="6"/>
       <c r="I109" s="15"/>
-      <c r="J109"/>
     </row>
     <row r="111" spans="1:11" ht="35.15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="E111" s="85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Actual value</t>
-        </is>
+      <c r="E111" s="85" t="s">
+        <v>3</v>
       </c>
       <c r="F111" s="86"/>
       <c r="G111" s="86"/>
       <c r="H111" s="87">
+        <f>H108</f>
         <v>0</v>
       </c>
       <c r="I111" s="88"/>
-      <c r="J111"/>
     </row>
     <row r="112" spans="1:11" ht="35.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="E112" s="68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Provisonal Payment ( 90% )</t>
-        </is>
+      <c r="E112" s="68" t="s">
+        <v>14</v>
       </c>
       <c r="F112" s="69"/>
       <c r="G112" s="69"/>
       <c r="H112" s="70">
-        <v>0</v>
+        <v>293919.84000000003</v>
       </c>
       <c r="I112" s="71"/>
-      <c r="J112"/>
     </row>
     <row r="113" spans="1:11" ht="35.15" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="E113" s="72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Balance</t>
-        </is>
+      <c r="E113" s="72" t="s">
+        <v>4</v>
       </c>
       <c r="F113" s="73"/>
       <c r="G113" s="73"/>
       <c r="H113" s="74">
-        <v>0</v>
+        <f>H111-H112</f>
+        <v>-293919.84000000003</v>
       </c>
       <c r="I113" s="75"/>
-      <c r="J113"/>
     </row>
     <row r="114" spans="1:11" s="13" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I114" s="42"/>
@@ -3860,7 +4811,6 @@
       <c r="G115" s="17"/>
       <c r="H115" s="17"/>
       <c r="I115" s="43"/>
-      <c r="J115"/>
     </row>
     <row r="116" spans="1:11" ht="26.15" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="117" spans="1:11" ht="26.15" customHeight="1" x14ac:dyDescent="0.45"/>
@@ -3919,9 +4869,6 @@
     <row r="154" ht="26.15" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="155" ht="26.15" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="156" ht="26.15" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="110">
-      <c r="J110"/>
-    </row>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="E112:G112"/>
@@ -3938,7 +4885,7 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait" r:id="rId1" fitToWidth="1"/>
+  <pageSetup paperSize="9" scale="54" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="115" max="16383" man="1"/>
   </rowBreaks>
@@ -3951,14 +4898,14 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:J156"/>
+  <dimension ref="A2:K125"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="5" width="16.08203125" style="1" customWidth="1"/>
     <col min="6" max="6" width="15.5" style="1" customWidth="1"/>
     <col min="7" max="8" width="16.08203125" style="1" customWidth="1"/>
     <col min="9" max="9" width="19.58203125" style="2" customWidth="1"/>
-    <col min="10" max="10" width="4" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.58203125" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.58203125" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="16384" width="9" style="1"/>
   </cols>
@@ -3992,10 +4939,8 @@
       <c r="A5" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">donald</t>
-        </is>
+      <c r="B5" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
@@ -4004,40 +4949,46 @@
         <v>1</v>
       </c>
       <c r="G5" s="11">
-        <v>46245</v>
+        <v>46185</v>
       </c>
       <c r="I5" s="41"/>
     </row>
     <row r="6" spans="1:10" s="9" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
+      <c r="B6" s="8" t="s">
+        <v>15</v>
+      </c>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
       <c r="F6" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="8"/>
+      <c r="G6" s="8" t="s">
+        <v>28</v>
+      </c>
       <c r="I6" s="41"/>
     </row>
     <row r="7" spans="1:10" s="9" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
+      <c r="B7" s="8" t="s">
+        <v>16</v>
+      </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
       <c r="F7" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">s01234</t>
-        </is>
+      <c r="G7" s="8" t="s">
+        <v>29</v>
       </c>
       <c r="I7" s="41"/>
     </row>
     <row r="8" spans="1:10" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B8" s="1"/>
+      <c r="B8" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="F8" s="3"/>
     </row>
     <row r="9" spans="1:10" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.45">
@@ -4087,50 +5038,58 @@
       <c r="I12" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="J12" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">사진</t>
-        </is>
-      </c>
     </row>
     <row r="13" spans="1:10" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">718 solids</t>
-        </is>
+      <c r="A13" s="21" t="s">
+        <v>30</v>
       </c>
       <c r="B13" s="18">
-        <v>500</v>
-      </c>
-      <c r="C13" s="19"/>
+        <v>10934</v>
+      </c>
+      <c r="C13" s="19">
+        <v>12</v>
+      </c>
       <c r="D13" s="20">
-        <v>0</v>
-      </c>
-      <c r="E13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NI · IN 718 · VS</t>
-        </is>
+        <f t="shared" ref="D13:D76" si="0">B13*C13</f>
+        <v>131208</v>
+      </c>
+      <c r="E13" s="21" t="s">
+        <v>30</v>
       </c>
       <c r="F13" s="22">
-        <v>500</v>
-      </c>
-      <c r="G13" s="49"/>
+        <v>10501</v>
+      </c>
+      <c r="G13" s="49">
+        <v>12</v>
+      </c>
       <c r="H13" s="23">
-        <v>0</v>
+        <f t="shared" ref="H13:H76" si="1">F13*G13</f>
+        <v>126012</v>
       </c>
       <c r="I13" s="38"/>
-      <c r="J13" s="38"/>
+      <c r="J13" s="34"/>
     </row>
     <row r="14" spans="1:10" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="21"/>
       <c r="B14" s="18"/>
       <c r="C14" s="19"/>
       <c r="D14" s="20"/>
-      <c r="E14" s="63"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="49"/>
-      <c r="H14" s="23"/>
-      <c r="I14" s="64"/>
+      <c r="E14" s="63" t="s">
+        <v>44</v>
+      </c>
+      <c r="F14" s="22">
+        <v>107</v>
+      </c>
+      <c r="G14" s="49">
+        <v>5.5</v>
+      </c>
+      <c r="H14" s="23">
+        <f t="shared" si="1"/>
+        <v>588.5</v>
+      </c>
+      <c r="I14" s="64" t="s">
+        <v>45</v>
+      </c>
       <c r="J14" s="34"/>
     </row>
     <row r="15" spans="1:10" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
@@ -4138,10 +5097,19 @@
       <c r="B15" s="18"/>
       <c r="C15" s="19"/>
       <c r="D15" s="20"/>
-      <c r="E15" s="21"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="49"/>
-      <c r="H15" s="23"/>
+      <c r="E15" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="F15" s="22">
+        <v>34</v>
+      </c>
+      <c r="G15" s="49">
+        <v>12.6</v>
+      </c>
+      <c r="H15" s="23">
+        <f t="shared" si="1"/>
+        <v>428.4</v>
+      </c>
       <c r="I15" s="64"/>
       <c r="J15" s="34"/>
     </row>
@@ -4150,10 +5118,19 @@
       <c r="B16" s="18"/>
       <c r="C16" s="19"/>
       <c r="D16" s="20"/>
-      <c r="E16" s="21"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="49"/>
-      <c r="H16" s="23"/>
+      <c r="E16" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="F16" s="22">
+        <v>12</v>
+      </c>
+      <c r="G16" s="49">
+        <v>8.5</v>
+      </c>
+      <c r="H16" s="23">
+        <f t="shared" si="1"/>
+        <v>102</v>
+      </c>
       <c r="I16" s="64"/>
       <c r="J16" s="34"/>
     </row>
@@ -4162,22 +5139,47 @@
       <c r="B17" s="18"/>
       <c r="C17" s="19"/>
       <c r="D17" s="20"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="22"/>
+      <c r="E17" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="F17" s="22">
+        <v>2</v>
+      </c>
       <c r="G17" s="49"/>
       <c r="H17" s="23"/>
       <c r="I17" s="64"/>
-      <c r="J17" s="34"/>
+      <c r="J17" s="34">
+        <f>SUM(F13:F17)-B13</f>
+        <v>-278</v>
+      </c>
     </row>
     <row r="18" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="21"/>
-      <c r="B18" s="18"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="49"/>
-      <c r="H18" s="23"/>
+      <c r="A18" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="B18" s="18">
+        <v>1551</v>
+      </c>
+      <c r="C18" s="19">
+        <v>12.6</v>
+      </c>
+      <c r="D18" s="20">
+        <f t="shared" si="0"/>
+        <v>19542.599999999999</v>
+      </c>
+      <c r="E18" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="F18" s="22">
+        <v>754</v>
+      </c>
+      <c r="G18" s="49">
+        <v>12.6</v>
+      </c>
+      <c r="H18" s="23">
+        <f t="shared" si="1"/>
+        <v>9500.4</v>
+      </c>
       <c r="I18" s="64"/>
       <c r="J18" s="34"/>
       <c r="K18" s="37"/>
@@ -4187,11 +5189,22 @@
       <c r="B19" s="18"/>
       <c r="C19" s="19"/>
       <c r="D19" s="20"/>
-      <c r="E19" s="63"/>
-      <c r="F19" s="22"/>
-      <c r="G19" s="49"/>
-      <c r="H19" s="23"/>
-      <c r="I19" s="64"/>
+      <c r="E19" s="63" t="s">
+        <v>31</v>
+      </c>
+      <c r="F19" s="22">
+        <v>530</v>
+      </c>
+      <c r="G19" s="49">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="H19" s="23">
+        <f t="shared" si="1"/>
+        <v>4664</v>
+      </c>
+      <c r="I19" s="64" t="s">
+        <v>121</v>
+      </c>
       <c r="J19" s="34"/>
       <c r="K19" s="37"/>
     </row>
@@ -4200,11 +5213,22 @@
       <c r="B20" s="18"/>
       <c r="C20" s="19"/>
       <c r="D20" s="20"/>
-      <c r="E20" s="63"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="49"/>
-      <c r="H20" s="23"/>
-      <c r="I20" s="64"/>
+      <c r="E20" s="63" t="s">
+        <v>31</v>
+      </c>
+      <c r="F20" s="22">
+        <v>103</v>
+      </c>
+      <c r="G20" s="49">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="H20" s="23">
+        <f t="shared" si="1"/>
+        <v>906.40000000000009</v>
+      </c>
+      <c r="I20" s="64" t="s">
+        <v>119</v>
+      </c>
       <c r="J20" s="34"/>
       <c r="K20" s="37"/>
     </row>
@@ -4213,11 +5237,22 @@
       <c r="B21" s="18"/>
       <c r="C21" s="19"/>
       <c r="D21" s="20"/>
-      <c r="E21" s="63"/>
-      <c r="F21" s="22"/>
-      <c r="G21" s="49"/>
-      <c r="H21" s="23"/>
-      <c r="I21" s="64"/>
+      <c r="E21" s="63" t="s">
+        <v>58</v>
+      </c>
+      <c r="F21" s="22">
+        <v>38</v>
+      </c>
+      <c r="G21" s="49">
+        <v>4.5</v>
+      </c>
+      <c r="H21" s="23">
+        <f t="shared" si="1"/>
+        <v>171</v>
+      </c>
+      <c r="I21" s="64" t="s">
+        <v>120</v>
+      </c>
       <c r="J21" s="34"/>
       <c r="K21" s="37"/>
     </row>
@@ -4226,23 +5261,53 @@
       <c r="B22" s="18"/>
       <c r="C22" s="19"/>
       <c r="D22" s="20"/>
-      <c r="E22" s="63"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="49"/>
-      <c r="H22" s="23"/>
+      <c r="E22" s="63" t="s">
+        <v>60</v>
+      </c>
+      <c r="F22" s="22">
+        <v>60</v>
+      </c>
+      <c r="G22" s="49">
+        <v>6.5</v>
+      </c>
+      <c r="H22" s="23">
+        <f t="shared" si="1"/>
+        <v>390</v>
+      </c>
       <c r="I22" s="65"/>
-      <c r="J22" s="34"/>
+      <c r="J22" s="34">
+        <f>SUM(F18:F22)-B18</f>
+        <v>-66</v>
+      </c>
       <c r="K22" s="37"/>
     </row>
     <row r="23" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="21"/>
-      <c r="B23" s="18"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="22"/>
-      <c r="G23" s="49"/>
-      <c r="H23" s="23"/>
+      <c r="A23" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" s="18">
+        <v>2511</v>
+      </c>
+      <c r="C23" s="19">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="D23" s="20">
+        <f t="shared" si="0"/>
+        <v>22096.800000000003</v>
+      </c>
+      <c r="E23" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="F23" s="22">
+        <v>2408</v>
+      </c>
+      <c r="G23" s="49">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="H23" s="23">
+        <f t="shared" si="1"/>
+        <v>21190.400000000001</v>
+      </c>
       <c r="I23" s="38"/>
       <c r="J23" s="34"/>
     </row>
@@ -4251,22 +5316,52 @@
       <c r="B24" s="18"/>
       <c r="C24" s="19"/>
       <c r="D24" s="20"/>
-      <c r="E24" s="21"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="49"/>
-      <c r="H24" s="23"/>
+      <c r="E24" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="F24" s="22">
+        <v>99</v>
+      </c>
+      <c r="G24" s="49">
+        <v>12.6</v>
+      </c>
+      <c r="H24" s="23">
+        <f t="shared" si="1"/>
+        <v>1247.3999999999999</v>
+      </c>
       <c r="I24" s="40"/>
-      <c r="J24" s="34"/>
+      <c r="J24" s="34">
+        <f>SUM(F23:F24)-B23</f>
+        <v>-4</v>
+      </c>
     </row>
     <row r="25" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="21"/>
-      <c r="B25" s="18"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="21"/>
-      <c r="F25" s="22"/>
-      <c r="G25" s="49"/>
-      <c r="H25" s="23"/>
+      <c r="A25" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25" s="18">
+        <v>244</v>
+      </c>
+      <c r="C25" s="19">
+        <v>12</v>
+      </c>
+      <c r="D25" s="20">
+        <f t="shared" si="0"/>
+        <v>2928</v>
+      </c>
+      <c r="E25" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="F25" s="22">
+        <v>1</v>
+      </c>
+      <c r="G25" s="49">
+        <v>12</v>
+      </c>
+      <c r="H25" s="23">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
       <c r="I25" s="38"/>
       <c r="J25" s="34"/>
     </row>
@@ -4275,10 +5370,19 @@
       <c r="B26" s="18"/>
       <c r="C26" s="19"/>
       <c r="D26" s="20"/>
-      <c r="E26" s="21"/>
-      <c r="F26" s="22"/>
-      <c r="G26" s="49"/>
-      <c r="H26" s="23"/>
+      <c r="E26" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="F26" s="22">
+        <v>1</v>
+      </c>
+      <c r="G26" s="49">
+        <v>12</v>
+      </c>
+      <c r="H26" s="23">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
       <c r="I26" s="38"/>
       <c r="J26" s="34"/>
     </row>
@@ -4287,10 +5391,19 @@
       <c r="B27" s="18"/>
       <c r="C27" s="19"/>
       <c r="D27" s="20"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="22"/>
-      <c r="G27" s="49"/>
-      <c r="H27" s="23"/>
+      <c r="E27" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="F27" s="22">
+        <v>1</v>
+      </c>
+      <c r="G27" s="49">
+        <v>12</v>
+      </c>
+      <c r="H27" s="23">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
       <c r="I27" s="38"/>
       <c r="J27" s="34"/>
     </row>
@@ -4299,10 +5412,19 @@
       <c r="B28" s="18"/>
       <c r="C28" s="19"/>
       <c r="D28" s="20"/>
-      <c r="E28" s="21"/>
-      <c r="F28" s="22"/>
-      <c r="G28" s="49"/>
-      <c r="H28" s="23"/>
+      <c r="E28" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="F28" s="22">
+        <v>9</v>
+      </c>
+      <c r="G28" s="49">
+        <v>12</v>
+      </c>
+      <c r="H28" s="23">
+        <f t="shared" si="1"/>
+        <v>108</v>
+      </c>
       <c r="I28" s="38"/>
       <c r="J28" s="34"/>
     </row>
@@ -4311,10 +5433,19 @@
       <c r="B29" s="18"/>
       <c r="C29" s="19"/>
       <c r="D29" s="20"/>
-      <c r="E29" s="21"/>
-      <c r="F29" s="22"/>
-      <c r="G29" s="49"/>
-      <c r="H29" s="23"/>
+      <c r="E29" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="F29" s="22">
+        <v>1</v>
+      </c>
+      <c r="G29" s="49">
+        <v>12</v>
+      </c>
+      <c r="H29" s="23">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
       <c r="I29" s="38"/>
       <c r="J29" s="34"/>
     </row>
@@ -4323,10 +5454,19 @@
       <c r="B30" s="18"/>
       <c r="C30" s="19"/>
       <c r="D30" s="20"/>
-      <c r="E30" s="21"/>
-      <c r="F30" s="22"/>
-      <c r="G30" s="49"/>
-      <c r="H30" s="23"/>
+      <c r="E30" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="F30" s="22">
+        <v>6</v>
+      </c>
+      <c r="G30" s="49">
+        <v>12</v>
+      </c>
+      <c r="H30" s="23">
+        <f t="shared" si="1"/>
+        <v>72</v>
+      </c>
       <c r="I30" s="39"/>
       <c r="J30" s="34"/>
     </row>
@@ -4335,10 +5475,19 @@
       <c r="B31" s="18"/>
       <c r="C31" s="19"/>
       <c r="D31" s="20"/>
-      <c r="E31" s="21"/>
-      <c r="F31" s="22"/>
-      <c r="G31" s="49"/>
-      <c r="H31" s="23"/>
+      <c r="E31" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="F31" s="22">
+        <v>1</v>
+      </c>
+      <c r="G31" s="49">
+        <v>12</v>
+      </c>
+      <c r="H31" s="23">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
       <c r="I31" s="38"/>
       <c r="J31" s="34"/>
     </row>
@@ -4347,10 +5496,19 @@
       <c r="B32" s="18"/>
       <c r="C32" s="19"/>
       <c r="D32" s="20"/>
-      <c r="E32" s="21"/>
-      <c r="F32" s="22"/>
-      <c r="G32" s="49"/>
-      <c r="H32" s="23"/>
+      <c r="E32" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="F32" s="22">
+        <v>1</v>
+      </c>
+      <c r="G32" s="49">
+        <v>12</v>
+      </c>
+      <c r="H32" s="23">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
       <c r="I32" s="38"/>
       <c r="J32" s="34"/>
     </row>
@@ -4359,10 +5517,19 @@
       <c r="B33" s="18"/>
       <c r="C33" s="19"/>
       <c r="D33" s="20"/>
-      <c r="E33" s="21"/>
-      <c r="F33" s="22"/>
-      <c r="G33" s="49"/>
-      <c r="H33" s="23"/>
+      <c r="E33" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="F33" s="22">
+        <v>227</v>
+      </c>
+      <c r="G33" s="49">
+        <v>12</v>
+      </c>
+      <c r="H33" s="23">
+        <f t="shared" si="1"/>
+        <v>2724</v>
+      </c>
       <c r="I33" s="38"/>
       <c r="J33" s="34"/>
     </row>
@@ -4371,10 +5538,19 @@
       <c r="B34" s="18"/>
       <c r="C34" s="19"/>
       <c r="D34" s="20"/>
-      <c r="E34" s="21"/>
-      <c r="F34" s="22"/>
-      <c r="G34" s="49"/>
-      <c r="H34" s="23"/>
+      <c r="E34" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="F34" s="22">
+        <v>2</v>
+      </c>
+      <c r="G34" s="49">
+        <v>12</v>
+      </c>
+      <c r="H34" s="23">
+        <f t="shared" si="1"/>
+        <v>24</v>
+      </c>
       <c r="I34" s="38"/>
       <c r="J34" s="34"/>
     </row>
@@ -4383,22 +5559,52 @@
       <c r="B35" s="18"/>
       <c r="C35" s="19"/>
       <c r="D35" s="20"/>
-      <c r="E35" s="21"/>
-      <c r="F35" s="22"/>
-      <c r="G35" s="49"/>
-      <c r="H35" s="23"/>
+      <c r="E35" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="F35" s="22">
+        <v>4</v>
+      </c>
+      <c r="G35" s="49">
+        <v>12</v>
+      </c>
+      <c r="H35" s="23">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
       <c r="I35" s="38"/>
-      <c r="J35" s="34"/>
+      <c r="J35" s="34">
+        <f>SUM(F25:F35)-B25</f>
+        <v>10</v>
+      </c>
     </row>
     <row r="36" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="21"/>
-      <c r="B36" s="18"/>
-      <c r="C36" s="19"/>
-      <c r="D36" s="20"/>
-      <c r="E36" s="21"/>
-      <c r="F36" s="22"/>
-      <c r="G36" s="49"/>
-      <c r="H36" s="23"/>
+      <c r="A36" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B36" s="18">
+        <v>4731</v>
+      </c>
+      <c r="C36" s="19">
+        <v>11.2</v>
+      </c>
+      <c r="D36" s="20">
+        <f t="shared" si="0"/>
+        <v>52987.199999999997</v>
+      </c>
+      <c r="E36" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="F36" s="22">
+        <v>2762</v>
+      </c>
+      <c r="G36" s="49">
+        <v>11.2</v>
+      </c>
+      <c r="H36" s="23">
+        <f>F36*G36</f>
+        <v>30934.399999999998</v>
+      </c>
       <c r="I36" s="38"/>
       <c r="J36" s="34"/>
       <c r="K36" s="45"/>
@@ -4408,49 +5614,126 @@
       <c r="B37" s="18"/>
       <c r="C37" s="19"/>
       <c r="D37" s="20"/>
-      <c r="E37" s="63"/>
-      <c r="F37" s="22"/>
-      <c r="G37" s="49"/>
-      <c r="H37" s="23"/>
-      <c r="I37" s="64"/>
-      <c r="J37" s="34"/>
+      <c r="E37" s="63" t="s">
+        <v>52</v>
+      </c>
+      <c r="F37" s="22">
+        <v>1779</v>
+      </c>
+      <c r="G37" s="49">
+        <v>6</v>
+      </c>
+      <c r="H37" s="23">
+        <f t="shared" ref="H37:H38" si="2">F37*G37</f>
+        <v>10674</v>
+      </c>
+      <c r="I37" s="64" t="s">
+        <v>128</v>
+      </c>
+      <c r="J37" s="34">
+        <f>F36+F37-B36</f>
+        <v>-190</v>
+      </c>
       <c r="K37" s="45"/>
     </row>
     <row r="38" spans="1:11" s="4" customFormat="1" ht="63" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="21"/>
-      <c r="B38" s="18"/>
-      <c r="C38" s="19"/>
-      <c r="D38" s="20"/>
-      <c r="E38" s="21"/>
-      <c r="F38" s="22"/>
-      <c r="G38" s="49"/>
-      <c r="H38" s="23"/>
-      <c r="I38" s="64"/>
-      <c r="J38" s="34"/>
+      <c r="A38" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="B38" s="18">
+        <v>1609</v>
+      </c>
+      <c r="C38" s="19">
+        <v>6</v>
+      </c>
+      <c r="D38" s="20">
+        <f>B38*C38</f>
+        <v>9654</v>
+      </c>
+      <c r="E38" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="F38" s="22">
+        <v>1609</v>
+      </c>
+      <c r="G38" s="49">
+        <v>6</v>
+      </c>
+      <c r="H38" s="23">
+        <f t="shared" si="2"/>
+        <v>9654</v>
+      </c>
+      <c r="I38" s="64" t="s">
+        <v>128</v>
+      </c>
+      <c r="J38" s="34">
+        <f>F38-B38</f>
+        <v>0</v>
+      </c>
       <c r="K38" s="47"/>
     </row>
     <row r="39" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A39" s="21"/>
-      <c r="B39" s="18"/>
-      <c r="C39" s="19"/>
-      <c r="D39" s="20"/>
-      <c r="E39" s="21"/>
-      <c r="F39" s="22"/>
-      <c r="G39" s="49"/>
-      <c r="H39" s="23"/>
+      <c r="A39" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="B39" s="18">
+        <v>481</v>
+      </c>
+      <c r="C39" s="19">
+        <v>0.1</v>
+      </c>
+      <c r="D39" s="20">
+        <f t="shared" si="0"/>
+        <v>48.1</v>
+      </c>
+      <c r="E39" s="21" t="str">
+        <f>A39</f>
+        <v>Ni Powder</v>
+      </c>
+      <c r="F39" s="22">
+        <v>478</v>
+      </c>
+      <c r="G39" s="49">
+        <v>0.1</v>
+      </c>
+      <c r="H39" s="23">
+        <f>F39*G39</f>
+        <v>47.800000000000004</v>
+      </c>
       <c r="I39" s="64"/>
-      <c r="J39" s="34"/>
+      <c r="J39" s="34">
+        <f>F39-B39</f>
+        <v>-3</v>
+      </c>
       <c r="K39" s="47"/>
     </row>
     <row r="40" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A40" s="21"/>
-      <c r="B40" s="18"/>
-      <c r="C40" s="19"/>
-      <c r="D40" s="20"/>
-      <c r="E40" s="21"/>
-      <c r="F40" s="22"/>
-      <c r="G40" s="49"/>
-      <c r="H40" s="23"/>
+      <c r="A40" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="B40" s="18">
+        <v>295</v>
+      </c>
+      <c r="C40" s="19">
+        <v>13.6</v>
+      </c>
+      <c r="D40" s="20">
+        <f t="shared" si="0"/>
+        <v>4012</v>
+      </c>
+      <c r="E40" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="F40" s="22">
+        <v>146</v>
+      </c>
+      <c r="G40" s="49">
+        <v>13.6</v>
+      </c>
+      <c r="H40" s="23">
+        <f t="shared" ref="H40:H52" si="3">F40*G40</f>
+        <v>1985.6</v>
+      </c>
       <c r="I40" s="64"/>
       <c r="J40" s="34"/>
       <c r="K40" s="1"/>
@@ -4460,10 +5743,19 @@
       <c r="B41" s="18"/>
       <c r="C41" s="19"/>
       <c r="D41" s="20"/>
-      <c r="E41" s="21"/>
-      <c r="F41" s="22"/>
-      <c r="G41" s="49"/>
-      <c r="H41" s="23"/>
+      <c r="E41" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F41" s="22">
+        <v>35</v>
+      </c>
+      <c r="G41" s="49">
+        <v>14.2</v>
+      </c>
+      <c r="H41" s="23">
+        <f t="shared" si="3"/>
+        <v>497</v>
+      </c>
       <c r="I41" s="64"/>
       <c r="J41" s="34"/>
       <c r="K41" s="1"/>
@@ -4473,10 +5765,19 @@
       <c r="B42" s="18"/>
       <c r="C42" s="19"/>
       <c r="D42" s="20"/>
-      <c r="E42" s="21"/>
-      <c r="F42" s="22"/>
-      <c r="G42" s="49"/>
-      <c r="H42" s="23"/>
+      <c r="E42" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="F42" s="22">
+        <v>1</v>
+      </c>
+      <c r="G42" s="49">
+        <v>10</v>
+      </c>
+      <c r="H42" s="23">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
       <c r="I42" s="64"/>
       <c r="J42" s="34"/>
       <c r="K42" s="1"/>
@@ -4486,10 +5787,19 @@
       <c r="B43" s="18"/>
       <c r="C43" s="19"/>
       <c r="D43" s="20"/>
-      <c r="E43" s="21"/>
-      <c r="F43" s="22"/>
-      <c r="G43" s="49"/>
-      <c r="H43" s="23"/>
+      <c r="E43" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="F43" s="22">
+        <v>1</v>
+      </c>
+      <c r="G43" s="49">
+        <v>10</v>
+      </c>
+      <c r="H43" s="23">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
       <c r="I43" s="64"/>
       <c r="J43" s="34"/>
       <c r="K43" s="1"/>
@@ -4499,10 +5809,19 @@
       <c r="B44" s="18"/>
       <c r="C44" s="19"/>
       <c r="D44" s="20"/>
-      <c r="E44" s="21"/>
-      <c r="F44" s="22"/>
-      <c r="G44" s="49"/>
-      <c r="H44" s="23"/>
+      <c r="E44" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="F44" s="22">
+        <v>1</v>
+      </c>
+      <c r="G44" s="49">
+        <v>10</v>
+      </c>
+      <c r="H44" s="23">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
       <c r="I44" s="64"/>
       <c r="J44" s="34"/>
       <c r="K44" s="1"/>
@@ -4512,11 +5831,22 @@
       <c r="B45" s="18"/>
       <c r="C45" s="19"/>
       <c r="D45" s="20"/>
-      <c r="E45" s="21"/>
-      <c r="F45" s="22"/>
-      <c r="G45" s="49"/>
-      <c r="H45" s="23"/>
-      <c r="I45" s="64"/>
+      <c r="E45" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="F45" s="22">
+        <v>16</v>
+      </c>
+      <c r="G45" s="49">
+        <v>6</v>
+      </c>
+      <c r="H45" s="23">
+        <f t="shared" si="3"/>
+        <v>96</v>
+      </c>
+      <c r="I45" s="64" t="s">
+        <v>129</v>
+      </c>
       <c r="J45" s="34"/>
       <c r="K45" s="1"/>
     </row>
@@ -4525,11 +5855,22 @@
       <c r="B46" s="18"/>
       <c r="C46" s="19"/>
       <c r="D46" s="20"/>
-      <c r="E46" s="21"/>
-      <c r="F46" s="22"/>
-      <c r="G46" s="49"/>
-      <c r="H46" s="23"/>
-      <c r="I46" s="65"/>
+      <c r="E46" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="F46" s="22">
+        <v>12</v>
+      </c>
+      <c r="G46" s="49">
+        <v>3</v>
+      </c>
+      <c r="H46" s="23">
+        <f t="shared" si="3"/>
+        <v>36</v>
+      </c>
+      <c r="I46" s="65" t="s">
+        <v>122</v>
+      </c>
       <c r="J46" s="34"/>
       <c r="K46" s="1"/>
     </row>
@@ -4538,11 +5879,22 @@
       <c r="B47" s="18"/>
       <c r="C47" s="19"/>
       <c r="D47" s="20"/>
-      <c r="E47" s="21"/>
-      <c r="F47" s="22"/>
-      <c r="G47" s="49"/>
-      <c r="H47" s="23"/>
-      <c r="I47" s="64"/>
+      <c r="E47" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="F47" s="22">
+        <v>7</v>
+      </c>
+      <c r="G47" s="49">
+        <v>3</v>
+      </c>
+      <c r="H47" s="23">
+        <f t="shared" si="3"/>
+        <v>21</v>
+      </c>
+      <c r="I47" s="64" t="s">
+        <v>123</v>
+      </c>
       <c r="J47" s="34"/>
       <c r="K47" s="1"/>
     </row>
@@ -4551,11 +5903,22 @@
       <c r="B48" s="18"/>
       <c r="C48" s="19"/>
       <c r="D48" s="20"/>
-      <c r="E48" s="21"/>
-      <c r="F48" s="22"/>
-      <c r="G48" s="49"/>
-      <c r="H48" s="23"/>
-      <c r="I48" s="64"/>
+      <c r="E48" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="F48" s="22">
+        <v>25</v>
+      </c>
+      <c r="G48" s="49">
+        <v>3</v>
+      </c>
+      <c r="H48" s="23">
+        <f t="shared" si="3"/>
+        <v>75</v>
+      </c>
+      <c r="I48" s="64" t="s">
+        <v>124</v>
+      </c>
       <c r="J48" s="34"/>
       <c r="K48" s="1"/>
     </row>
@@ -4564,11 +5927,22 @@
       <c r="B49" s="18"/>
       <c r="C49" s="19"/>
       <c r="D49" s="20"/>
-      <c r="E49" s="21"/>
-      <c r="F49" s="22"/>
-      <c r="G49" s="49"/>
-      <c r="H49" s="23"/>
-      <c r="I49" s="64"/>
+      <c r="E49" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="F49" s="22">
+        <v>18</v>
+      </c>
+      <c r="G49" s="49">
+        <v>1.5</v>
+      </c>
+      <c r="H49" s="23">
+        <f t="shared" si="3"/>
+        <v>27</v>
+      </c>
+      <c r="I49" s="64" t="s">
+        <v>125</v>
+      </c>
       <c r="J49" s="34"/>
       <c r="K49" s="1"/>
     </row>
@@ -4577,11 +5951,22 @@
       <c r="B50" s="18"/>
       <c r="C50" s="19"/>
       <c r="D50" s="20"/>
-      <c r="E50" s="21"/>
-      <c r="F50" s="22"/>
-      <c r="G50" s="49"/>
-      <c r="H50" s="23"/>
-      <c r="I50" s="64"/>
+      <c r="E50" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="F50" s="22">
+        <v>5</v>
+      </c>
+      <c r="G50" s="49">
+        <v>1.5</v>
+      </c>
+      <c r="H50" s="23">
+        <f t="shared" si="3"/>
+        <v>7.5</v>
+      </c>
+      <c r="I50" s="64" t="s">
+        <v>126</v>
+      </c>
       <c r="J50" s="34"/>
       <c r="K50" s="1"/>
     </row>
@@ -4590,10 +5975,19 @@
       <c r="B51" s="18"/>
       <c r="C51" s="19"/>
       <c r="D51" s="20"/>
-      <c r="E51" s="21"/>
-      <c r="F51" s="22"/>
-      <c r="G51" s="49"/>
-      <c r="H51" s="23"/>
+      <c r="E51" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="F51" s="22">
+        <v>7</v>
+      </c>
+      <c r="G51" s="49">
+        <v>1.2</v>
+      </c>
+      <c r="H51" s="23">
+        <f t="shared" si="3"/>
+        <v>8.4</v>
+      </c>
       <c r="I51" s="64"/>
       <c r="J51" s="34"/>
       <c r="K51" s="1"/>
@@ -4603,23 +5997,53 @@
       <c r="B52" s="18"/>
       <c r="C52" s="19"/>
       <c r="D52" s="20"/>
-      <c r="E52" s="21"/>
-      <c r="F52" s="22"/>
-      <c r="G52" s="49"/>
-      <c r="H52" s="23"/>
+      <c r="E52" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="F52" s="22">
+        <v>8</v>
+      </c>
+      <c r="G52" s="49">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="H52" s="23">
+        <f t="shared" si="3"/>
+        <v>17.600000000000001</v>
+      </c>
       <c r="I52" s="64"/>
-      <c r="J52" s="34"/>
+      <c r="J52" s="34">
+        <f>SUM(F40:F52)-B40</f>
+        <v>-13</v>
+      </c>
       <c r="K52" s="1"/>
     </row>
     <row r="53" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A53" s="21"/>
-      <c r="B53" s="18"/>
-      <c r="C53" s="19"/>
-      <c r="D53" s="20"/>
-      <c r="E53" s="21"/>
-      <c r="F53" s="22"/>
-      <c r="G53" s="49"/>
-      <c r="H53" s="23"/>
+      <c r="A53" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="B53" s="18">
+        <v>2532</v>
+      </c>
+      <c r="C53" s="19">
+        <v>13.1</v>
+      </c>
+      <c r="D53" s="20">
+        <f t="shared" si="0"/>
+        <v>33169.199999999997</v>
+      </c>
+      <c r="E53" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="F53" s="22">
+        <v>2469</v>
+      </c>
+      <c r="G53" s="49">
+        <v>13.1</v>
+      </c>
+      <c r="H53" s="23">
+        <f t="shared" si="1"/>
+        <v>32343.899999999998</v>
+      </c>
       <c r="I53" s="64"/>
       <c r="J53" s="34"/>
       <c r="K53" s="1"/>
@@ -4629,23 +6053,51 @@
       <c r="B54" s="18"/>
       <c r="C54" s="19"/>
       <c r="D54" s="20"/>
-      <c r="E54" s="21"/>
-      <c r="F54" s="22"/>
+      <c r="E54" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="F54" s="22">
+        <v>10</v>
+      </c>
       <c r="G54" s="49"/>
-      <c r="H54" s="23"/>
+      <c r="H54" s="23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="I54" s="64"/>
-      <c r="J54" s="34"/>
+      <c r="J54" s="34">
+        <f>SUM(F53:F54)-B53</f>
+        <v>-53</v>
+      </c>
       <c r="K54" s="1"/>
     </row>
     <row r="55" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A55" s="21"/>
-      <c r="B55" s="18"/>
-      <c r="C55" s="19"/>
-      <c r="D55" s="20"/>
-      <c r="E55" s="21"/>
-      <c r="F55" s="22"/>
-      <c r="G55" s="49"/>
-      <c r="H55" s="23"/>
+      <c r="A55" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B55" s="18">
+        <v>287</v>
+      </c>
+      <c r="C55" s="19">
+        <v>14.2</v>
+      </c>
+      <c r="D55" s="20">
+        <f t="shared" si="0"/>
+        <v>4075.3999999999996</v>
+      </c>
+      <c r="E55" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="F55" s="22">
+        <v>270</v>
+      </c>
+      <c r="G55" s="49">
+        <v>14.2</v>
+      </c>
+      <c r="H55" s="23">
+        <f t="shared" si="1"/>
+        <v>3834</v>
+      </c>
       <c r="I55" s="64"/>
       <c r="J55" s="34"/>
       <c r="K55" s="46"/>
@@ -4655,10 +6107,19 @@
       <c r="B56" s="18"/>
       <c r="C56" s="19"/>
       <c r="D56" s="20"/>
-      <c r="E56" s="21"/>
-      <c r="F56" s="22"/>
-      <c r="G56" s="49"/>
-      <c r="H56" s="23"/>
+      <c r="E56" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="F56" s="22">
+        <v>40</v>
+      </c>
+      <c r="G56" s="49">
+        <v>13.6</v>
+      </c>
+      <c r="H56" s="23">
+        <f t="shared" si="1"/>
+        <v>544</v>
+      </c>
       <c r="I56" s="64"/>
       <c r="J56" s="34"/>
       <c r="K56" s="46"/>
@@ -4668,23 +6129,56 @@
       <c r="B57" s="18"/>
       <c r="C57" s="19"/>
       <c r="D57" s="20"/>
-      <c r="E57" s="21"/>
-      <c r="F57" s="22"/>
-      <c r="G57" s="49"/>
-      <c r="H57" s="23"/>
-      <c r="I57" s="64"/>
-      <c r="J57" s="34"/>
+      <c r="E57" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="F57" s="22">
+        <v>52</v>
+      </c>
+      <c r="G57" s="49">
+        <v>6</v>
+      </c>
+      <c r="H57" s="23">
+        <f t="shared" si="1"/>
+        <v>312</v>
+      </c>
+      <c r="I57" s="64" t="s">
+        <v>127</v>
+      </c>
+      <c r="J57" s="34">
+        <f>SUM(F55:F57)-B55</f>
+        <v>75</v>
+      </c>
       <c r="K57" s="46"/>
     </row>
     <row r="58" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A58" s="21"/>
-      <c r="B58" s="18"/>
-      <c r="C58" s="19"/>
-      <c r="D58" s="20"/>
-      <c r="E58" s="21"/>
-      <c r="F58" s="22"/>
-      <c r="G58" s="49"/>
-      <c r="H58" s="23"/>
+      <c r="A58" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B58" s="18">
+        <v>1171</v>
+      </c>
+      <c r="C58" s="19">
+        <v>13.6</v>
+      </c>
+      <c r="D58" s="20">
+        <f t="shared" si="0"/>
+        <v>15925.6</v>
+      </c>
+      <c r="E58" s="21" t="str">
+        <f>A58</f>
+        <v>625 Solid</v>
+      </c>
+      <c r="F58" s="22">
+        <v>1144</v>
+      </c>
+      <c r="G58" s="49">
+        <v>13.6</v>
+      </c>
+      <c r="H58" s="23">
+        <f t="shared" si="1"/>
+        <v>15558.4</v>
+      </c>
       <c r="I58" s="64"/>
       <c r="J58" s="34"/>
       <c r="K58" s="1"/>
@@ -4694,47 +6188,120 @@
       <c r="B59" s="18"/>
       <c r="C59" s="19"/>
       <c r="D59" s="20"/>
-      <c r="E59" s="21"/>
-      <c r="F59" s="22"/>
-      <c r="G59" s="49"/>
-      <c r="H59" s="23"/>
+      <c r="E59" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="F59" s="22">
+        <v>18</v>
+      </c>
+      <c r="G59" s="49">
+        <v>12</v>
+      </c>
+      <c r="H59" s="23">
+        <f t="shared" si="1"/>
+        <v>216</v>
+      </c>
       <c r="I59" s="64"/>
-      <c r="J59" s="34"/>
+      <c r="J59" s="34">
+        <f>F58+F59-B58</f>
+        <v>-9</v>
+      </c>
       <c r="K59" s="1"/>
     </row>
     <row r="60" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A60" s="21"/>
-      <c r="B60" s="18"/>
-      <c r="C60" s="19"/>
-      <c r="D60" s="20"/>
-      <c r="E60" s="21"/>
-      <c r="F60" s="22"/>
-      <c r="G60" s="49"/>
-      <c r="H60" s="23"/>
+      <c r="A60" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="B60" s="18">
+        <v>95</v>
+      </c>
+      <c r="C60" s="19">
+        <v>12</v>
+      </c>
+      <c r="D60" s="20">
+        <f t="shared" si="0"/>
+        <v>1140</v>
+      </c>
+      <c r="E60" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="F60" s="22">
+        <v>92</v>
+      </c>
+      <c r="G60" s="49">
+        <v>12</v>
+      </c>
+      <c r="H60" s="23">
+        <f t="shared" si="1"/>
+        <v>1104</v>
+      </c>
       <c r="I60" s="64"/>
-      <c r="J60" s="34"/>
+      <c r="J60" s="34">
+        <f>F60-B60</f>
+        <v>-3</v>
+      </c>
     </row>
     <row r="61" spans="1:11" s="4" customFormat="1" ht="35.15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A61" s="21"/>
-      <c r="B61" s="18"/>
-      <c r="C61" s="19"/>
-      <c r="D61" s="20"/>
-      <c r="E61" s="21"/>
-      <c r="F61" s="22"/>
-      <c r="G61" s="49"/>
-      <c r="H61" s="23"/>
+      <c r="A61" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="B61" s="18">
+        <v>496</v>
+      </c>
+      <c r="C61" s="19">
+        <v>9</v>
+      </c>
+      <c r="D61" s="20">
+        <f t="shared" si="0"/>
+        <v>4464</v>
+      </c>
+      <c r="E61" s="21" t="str">
+        <f>A61</f>
+        <v>713 Mix Blade</v>
+      </c>
+      <c r="F61" s="22">
+        <v>502</v>
+      </c>
+      <c r="G61" s="49">
+        <v>9</v>
+      </c>
+      <c r="H61" s="23">
+        <f t="shared" si="1"/>
+        <v>4518</v>
+      </c>
       <c r="I61" s="65"/>
-      <c r="J61" s="34"/>
+      <c r="J61" s="34">
+        <f>F61-B61</f>
+        <v>6</v>
+      </c>
     </row>
     <row r="62" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A62" s="21"/>
-      <c r="B62" s="18"/>
-      <c r="C62" s="19"/>
-      <c r="D62" s="20"/>
-      <c r="E62" s="21"/>
-      <c r="F62" s="22"/>
-      <c r="G62" s="49"/>
-      <c r="H62" s="23"/>
+      <c r="A62" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="B62" s="18">
+        <v>58</v>
+      </c>
+      <c r="C62" s="19">
+        <v>35</v>
+      </c>
+      <c r="D62" s="20">
+        <f t="shared" si="0"/>
+        <v>2030</v>
+      </c>
+      <c r="E62" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="F62" s="22">
+        <v>7</v>
+      </c>
+      <c r="G62" s="49">
+        <v>10.5</v>
+      </c>
+      <c r="H62" s="23">
+        <f t="shared" si="1"/>
+        <v>73.5</v>
+      </c>
       <c r="I62" s="65"/>
       <c r="J62" s="34"/>
       <c r="K62" s="48"/>
@@ -4744,10 +6311,19 @@
       <c r="B63" s="18"/>
       <c r="C63" s="19"/>
       <c r="D63" s="20"/>
-      <c r="E63" s="21"/>
-      <c r="F63" s="22"/>
-      <c r="G63" s="49"/>
-      <c r="H63" s="23"/>
+      <c r="E63" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="F63" s="22">
+        <v>1</v>
+      </c>
+      <c r="G63" s="49">
+        <v>10.5</v>
+      </c>
+      <c r="H63" s="23">
+        <f t="shared" si="1"/>
+        <v>10.5</v>
+      </c>
       <c r="I63" s="65"/>
       <c r="J63" s="34"/>
       <c r="K63" s="48"/>
@@ -4757,10 +6333,19 @@
       <c r="B64" s="18"/>
       <c r="C64" s="19"/>
       <c r="D64" s="20"/>
-      <c r="E64" s="63"/>
-      <c r="F64" s="22"/>
-      <c r="G64" s="49"/>
-      <c r="H64" s="23"/>
+      <c r="E64" s="63" t="s">
+        <v>109</v>
+      </c>
+      <c r="F64" s="22">
+        <v>14</v>
+      </c>
+      <c r="G64" s="49">
+        <v>6</v>
+      </c>
+      <c r="H64" s="23">
+        <f t="shared" si="1"/>
+        <v>84</v>
+      </c>
       <c r="I64" s="65"/>
       <c r="J64" s="34"/>
       <c r="K64" s="48"/>
@@ -4770,10 +6355,19 @@
       <c r="B65" s="18"/>
       <c r="C65" s="19"/>
       <c r="D65" s="20"/>
-      <c r="E65" s="21"/>
-      <c r="F65" s="22"/>
-      <c r="G65" s="49"/>
-      <c r="H65" s="23"/>
+      <c r="E65" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="F65" s="22">
+        <v>14</v>
+      </c>
+      <c r="G65" s="49">
+        <v>35</v>
+      </c>
+      <c r="H65" s="23">
+        <f t="shared" si="1"/>
+        <v>490</v>
+      </c>
       <c r="I65" s="65"/>
       <c r="J65" s="34"/>
       <c r="K65" s="48"/>
@@ -4783,10 +6377,19 @@
       <c r="B66" s="18"/>
       <c r="C66" s="19"/>
       <c r="D66" s="20"/>
-      <c r="E66" s="21"/>
-      <c r="F66" s="22"/>
-      <c r="G66" s="49"/>
-      <c r="H66" s="23"/>
+      <c r="E66" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="F66" s="22">
+        <v>6</v>
+      </c>
+      <c r="G66" s="49">
+        <v>35</v>
+      </c>
+      <c r="H66" s="23">
+        <f t="shared" si="1"/>
+        <v>210</v>
+      </c>
       <c r="I66" s="65"/>
       <c r="J66" s="34"/>
       <c r="K66" s="48"/>
@@ -4796,10 +6399,19 @@
       <c r="B67" s="18"/>
       <c r="C67" s="19"/>
       <c r="D67" s="20"/>
-      <c r="E67" s="21"/>
-      <c r="F67" s="22"/>
-      <c r="G67" s="49"/>
-      <c r="H67" s="23"/>
+      <c r="E67" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="F67" s="22">
+        <v>2</v>
+      </c>
+      <c r="G67" s="49">
+        <v>10.5</v>
+      </c>
+      <c r="H67" s="23">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
       <c r="I67" s="65"/>
       <c r="J67" s="34"/>
       <c r="K67" s="48"/>
@@ -4809,10 +6421,19 @@
       <c r="B68" s="18"/>
       <c r="C68" s="19"/>
       <c r="D68" s="20"/>
-      <c r="E68" s="21"/>
-      <c r="F68" s="22"/>
-      <c r="G68" s="49"/>
-      <c r="H68" s="23"/>
+      <c r="E68" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="F68" s="22">
+        <v>1</v>
+      </c>
+      <c r="G68" s="49">
+        <v>10.5</v>
+      </c>
+      <c r="H68" s="23">
+        <f t="shared" si="1"/>
+        <v>10.5</v>
+      </c>
       <c r="I68" s="65"/>
       <c r="J68" s="34"/>
     </row>
@@ -4821,23 +6442,54 @@
       <c r="B69" s="18"/>
       <c r="C69" s="19"/>
       <c r="D69" s="20"/>
-      <c r="E69" s="21"/>
-      <c r="F69" s="22"/>
-      <c r="G69" s="49"/>
-      <c r="H69" s="23"/>
+      <c r="E69" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="F69" s="22">
+        <v>11</v>
+      </c>
+      <c r="G69" s="49">
+        <v>10.5</v>
+      </c>
+      <c r="H69" s="23">
+        <f t="shared" si="1"/>
+        <v>115.5</v>
+      </c>
       <c r="I69" s="65"/>
-      <c r="J69" s="34"/>
+      <c r="J69" s="34">
+        <f>SUM(F62:F69)-B62</f>
+        <v>-2</v>
+      </c>
       <c r="K69" s="48"/>
     </row>
     <row r="70" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A70" s="21"/>
-      <c r="B70" s="18"/>
-      <c r="C70" s="19"/>
-      <c r="D70" s="20"/>
-      <c r="E70" s="21"/>
-      <c r="F70" s="22"/>
-      <c r="G70" s="49"/>
-      <c r="H70" s="23"/>
+      <c r="A70" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B70" s="18">
+        <v>202</v>
+      </c>
+      <c r="C70" s="19">
+        <v>10.5</v>
+      </c>
+      <c r="D70" s="20">
+        <f t="shared" si="0"/>
+        <v>2121</v>
+      </c>
+      <c r="E70" s="21" t="str">
+        <f>A70</f>
+        <v>Rene77 Blade</v>
+      </c>
+      <c r="F70" s="22">
+        <v>133</v>
+      </c>
+      <c r="G70" s="49">
+        <v>10.5</v>
+      </c>
+      <c r="H70" s="23">
+        <f t="shared" si="1"/>
+        <v>1396.5</v>
+      </c>
       <c r="I70" s="65"/>
       <c r="J70" s="34"/>
       <c r="K70" s="1"/>
@@ -4847,48 +6499,124 @@
       <c r="B71" s="18"/>
       <c r="C71" s="19"/>
       <c r="D71" s="20"/>
-      <c r="E71" s="63"/>
-      <c r="F71" s="22"/>
-      <c r="G71" s="49"/>
-      <c r="H71" s="23"/>
-      <c r="I71" s="66"/>
-      <c r="J71" s="34"/>
+      <c r="E71" s="63" t="s">
+        <v>109</v>
+      </c>
+      <c r="F71" s="22">
+        <v>64</v>
+      </c>
+      <c r="G71" s="49">
+        <v>6</v>
+      </c>
+      <c r="H71" s="23">
+        <f t="shared" si="1"/>
+        <v>384</v>
+      </c>
+      <c r="I71" s="66" t="s">
+        <v>130</v>
+      </c>
+      <c r="J71" s="34">
+        <f>F70+F71-B70</f>
+        <v>-5</v>
+      </c>
       <c r="K71" s="1"/>
     </row>
     <row r="72" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A72" s="21"/>
-      <c r="B72" s="18"/>
-      <c r="C72" s="19"/>
-      <c r="D72" s="20"/>
-      <c r="E72" s="21"/>
-      <c r="F72" s="22"/>
-      <c r="G72" s="49"/>
-      <c r="H72" s="23"/>
+      <c r="A72" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="B72" s="18">
+        <v>1443</v>
+      </c>
+      <c r="C72" s="19">
+        <v>3.3</v>
+      </c>
+      <c r="D72" s="20">
+        <f t="shared" si="0"/>
+        <v>4761.8999999999996</v>
+      </c>
+      <c r="E72" s="21" t="str">
+        <f>A72</f>
+        <v>Wco with SKD</v>
+      </c>
+      <c r="F72" s="22">
+        <v>1456</v>
+      </c>
+      <c r="G72" s="49">
+        <v>3.3</v>
+      </c>
+      <c r="H72" s="23">
+        <f t="shared" si="1"/>
+        <v>4804.8</v>
+      </c>
       <c r="I72" s="67"/>
-      <c r="J72" s="34"/>
+      <c r="J72" s="34">
+        <f>F72-B72</f>
+        <v>13</v>
+      </c>
       <c r="K72" s="48"/>
     </row>
     <row r="73" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A73" s="21"/>
-      <c r="B73" s="18"/>
-      <c r="C73" s="19"/>
-      <c r="D73" s="20"/>
-      <c r="E73" s="21"/>
-      <c r="F73" s="22"/>
-      <c r="G73" s="49"/>
-      <c r="H73" s="23"/>
+      <c r="A73" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="B73" s="18">
+        <v>2609</v>
+      </c>
+      <c r="C73" s="19">
+        <v>5.2</v>
+      </c>
+      <c r="D73" s="20">
+        <f t="shared" si="0"/>
+        <v>13566.800000000001</v>
+      </c>
+      <c r="E73" s="21" t="str">
+        <f>A73</f>
+        <v>Ni-B Turning</v>
+      </c>
+      <c r="F73" s="22">
+        <v>2605</v>
+      </c>
+      <c r="G73" s="49">
+        <v>5.2</v>
+      </c>
+      <c r="H73" s="23">
+        <f t="shared" si="1"/>
+        <v>13546</v>
+      </c>
       <c r="I73" s="65"/>
-      <c r="J73" s="34"/>
+      <c r="J73" s="34">
+        <f>F73-B73</f>
+        <v>-4</v>
+      </c>
     </row>
     <row r="74" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A74" s="21"/>
-      <c r="B74" s="18"/>
-      <c r="C74" s="19"/>
-      <c r="D74" s="20"/>
-      <c r="E74" s="21"/>
-      <c r="F74" s="22"/>
-      <c r="G74" s="49"/>
-      <c r="H74" s="23"/>
+      <c r="A74" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B74" s="18">
+        <v>212</v>
+      </c>
+      <c r="C74" s="19">
+        <v>13</v>
+      </c>
+      <c r="D74" s="20">
+        <f t="shared" si="0"/>
+        <v>2756</v>
+      </c>
+      <c r="E74" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="F74" s="22">
+        <v>150</v>
+      </c>
+      <c r="G74" s="49">
+        <v>13</v>
+      </c>
+      <c r="H74" s="23">
+        <f t="shared" si="1"/>
+        <v>1950</v>
+      </c>
       <c r="I74" s="65"/>
       <c r="J74" s="34"/>
     </row>
@@ -4897,52 +6625,90 @@
       <c r="B75" s="18"/>
       <c r="C75" s="19"/>
       <c r="D75" s="20"/>
-      <c r="E75" s="21"/>
-      <c r="F75" s="22"/>
-      <c r="G75" s="49"/>
-      <c r="H75" s="23"/>
-      <c r="I75" s="65"/>
-      <c r="J75" s="34"/>
+      <c r="E75" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="F75" s="22">
+        <v>56</v>
+      </c>
+      <c r="G75" s="49">
+        <v>5.5</v>
+      </c>
+      <c r="H75" s="23">
+        <f t="shared" si="1"/>
+        <v>308</v>
+      </c>
+      <c r="I75" s="65" t="s">
+        <v>50</v>
+      </c>
+      <c r="J75" s="34">
+        <f>SUM(F74:F75)-B74</f>
+        <v>-6</v>
+      </c>
     </row>
     <row r="76" spans="1:11" s="4" customFormat="1" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A76" s="21"/>
-      <c r="B76" s="18"/>
-      <c r="C76" s="19"/>
-      <c r="D76" s="20"/>
-      <c r="E76" s="21"/>
-      <c r="F76" s="22"/>
-      <c r="G76" s="49"/>
-      <c r="H76" s="23"/>
+      <c r="A76" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="B76" s="18">
+        <v>35</v>
+      </c>
+      <c r="C76" s="19">
+        <v>2.6</v>
+      </c>
+      <c r="D76" s="20">
+        <f t="shared" si="0"/>
+        <v>91</v>
+      </c>
+      <c r="E76" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="F76" s="22">
+        <v>36</v>
+      </c>
+      <c r="G76" s="49">
+        <v>2.6</v>
+      </c>
+      <c r="H76" s="23">
+        <f t="shared" si="1"/>
+        <v>93.600000000000009</v>
+      </c>
       <c r="I76" s="65"/>
-      <c r="J76" s="34"/>
+      <c r="J76" s="34">
+        <f>F76-B76</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="77" spans="1:11" ht="35.15" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="A77" s="24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TOTAL</t>
-        </is>
+      <c r="A77" s="24" t="s">
+        <v>12</v>
       </c>
       <c r="B77" s="25">
-        <v>500</v>
+        <f>SUM(B13:B76)</f>
+        <v>31496</v>
       </c>
       <c r="C77" s="26"/>
       <c r="D77" s="27">
-        <v>0</v>
-      </c>
-      <c r="E77" s="28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TOTAL</t>
-        </is>
+        <f>SUM(D13:D76)</f>
+        <v>326577.60000000003</v>
+      </c>
+      <c r="E77" s="28" t="s">
+        <v>12</v>
       </c>
       <c r="F77" s="29">
-        <v>500</v>
+        <f>SUM(F13:F76)</f>
+        <v>30965</v>
       </c>
       <c r="G77" s="26"/>
       <c r="H77" s="26">
-        <v>0</v>
+        <f>SUM(H13:H76)</f>
+        <v>304287.99999999994</v>
       </c>
       <c r="I77" s="12"/>
-      <c r="J77" s="35"/>
+      <c r="J77" s="35">
+        <f>SUM(J13:J76)</f>
+        <v>-531</v>
+      </c>
     </row>
     <row r="78" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A78" s="4"/>
@@ -4954,49 +6720,41 @@
       <c r="G78" s="6"/>
       <c r="H78" s="6"/>
       <c r="I78" s="15"/>
-      <c r="J78"/>
     </row>
     <row r="80" spans="1:11" ht="35.15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="E80" s="85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Actual value</t>
-        </is>
+      <c r="E80" s="85" t="s">
+        <v>3</v>
       </c>
       <c r="F80" s="86"/>
       <c r="G80" s="86"/>
       <c r="H80" s="87">
-        <v>0</v>
+        <f>H77</f>
+        <v>304287.99999999994</v>
       </c>
       <c r="I80" s="88"/>
-      <c r="J80"/>
     </row>
     <row r="81" spans="1:11" ht="35.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="E81" s="68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Provisonal Payment ( 90% )</t>
-        </is>
+      <c r="E81" s="68" t="s">
+        <v>14</v>
       </c>
       <c r="F81" s="69"/>
       <c r="G81" s="69"/>
       <c r="H81" s="70">
-        <v>0</v>
+        <v>293919.84000000003</v>
       </c>
       <c r="I81" s="71"/>
-      <c r="J81"/>
     </row>
     <row r="82" spans="1:11" ht="35.15" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="E82" s="72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Balance</t>
-        </is>
+      <c r="E82" s="72" t="s">
+        <v>4</v>
       </c>
       <c r="F82" s="73"/>
       <c r="G82" s="73"/>
       <c r="H82" s="74">
-        <v>0</v>
+        <f>H80-H81</f>
+        <v>10368.159999999916</v>
       </c>
       <c r="I82" s="75"/>
-      <c r="J82"/>
     </row>
     <row r="83" spans="1:11" s="13" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="I83" s="42"/>
@@ -5017,7 +6775,6 @@
       <c r="G84" s="17"/>
       <c r="H84" s="17"/>
       <c r="I84" s="43"/>
-      <c r="J84"/>
     </row>
     <row r="85" spans="1:11" ht="26.15" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="86" spans="1:11" ht="26.15" customHeight="1" x14ac:dyDescent="0.45"/>
@@ -5076,9 +6833,6 @@
     <row r="123" ht="26.15" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="124" ht="26.15" customHeight="1" x14ac:dyDescent="0.45"/>
     <row r="125" ht="26.15" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="79">
-      <c r="J79"/>
-    </row>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A2:D2"/>
@@ -5095,7 +6849,7 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="portrait" r:id="rId1" fitToWidth="1"/>
+  <pageSetup paperSize="9" scale="61" fitToHeight="0" orientation="portrait" r:id="rId1"/>
   <rowBreaks count="3" manualBreakCount="3">
     <brk id="35" max="8" man="1"/>
     <brk id="61" max="8" man="1"/>
